--- a/Post GE14.xlsx
+++ b/Post GE14.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a960143ed076ae3/Desktop/Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1662" documentId="8_{186D12AC-41E3-418E-AADE-7BB523F94D2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67CE2B53-DE71-4AF2-8E61-BE3C22EB0BA9}"/>
+  <xr:revisionPtr revIDLastSave="1671" documentId="8_{186D12AC-41E3-418E-AADE-7BB523F94D2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42BF7BBF-F4D9-468B-AF29-5ED9970F8347}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{41795AD5-B7F1-475B-99F5-B3B6FD9E37DE}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="685">
   <si>
     <t>PH gov trying to implement reforms while PAS and UMNO trying to plan things from behind the scene. Prosecute Najib and many corruption allegation from other politicians</t>
   </si>
@@ -4651,6 +4651,31 @@
 The current competition to win the hearts and minds of the community leaders should not be prolonged. Instead, there should be cooperation. Contending political parties should not make use of the service of the leaders of longhouse/village communities in Sarawak for their own purposes, if they are seriously concerned about the adverse impact on these communities.
 The living allowances that the community leaders are getting must be regarded as a financial token for their public service similar to the service rendered by the apolitical civil servants in Sarawak. In fact, this was the original intention of the state government until the 2000s, when there was a policy change. In an election campaign in my hometown, a federal minister campaigning for the late Datuk Adenan Satem, announced this federal government’s assistance to the local community leaders gathered in a community hall. Several among them whom I met afterwards were in two minds: yes and no. Two TK said it would be fair for Prentah (government) to help the ketua kampong with saguhati (ex-gratia payment); two others were opposed – ‘Tu meli kitai tu (this is buying).’
 The conflict of authority over the appointment and payment of allowances to the community leaders has caused embarrassment to the leaders, giving the impression that they are easy pawns in the political game between the two governments. Some are willing pawns, others are unwitting pawns, naïve and trusting, I have to say.</t>
+  </si>
+  <si>
+    <t>https://www.malaymail.com/news/malaysia/2019/07/24/dewan-negara-passes-amendment-bill-to-reduce-youth-age-cap-to-30/1774495</t>
+  </si>
+  <si>
+    <t>Dewan Negara passes Amendment Bill to reduce youth age cap to 30</t>
+  </si>
+  <si>
+    <t>KUALA LUMPUR, July 24 — The Youth Societies and Youth Development (Amendment) Bill 2019 which seeks to, among others, reduce the age cap for the definition of youth from 40 to 30, was approved by the Senate today.
+It was passed in the session chaired by Senate Deputy President Datuk Seri Abd Halim Abd Samad after 14 senators took part in the debate session.
+Deputy Youth and Sports Deputy Minister Steven Sim Chee Keong, when tabling the Bill for second reading, said it was aimed at ensuring youth development was in line with the Malaysian Youth Policy as well as existing government policies in strengthening the roles and responsibilities of youth in the country.
+“Based on the statistics from the Department of Statistics Malaysia, the number of youths in 2018 is 15.1 million, which is 46.64 per cent of the total population in the country.
+“By the year 2030 it is estimated that youths will the majority group who will determine Malaysia’s future leadership,” he said.
+The Amendment Bill approved by the Dewan Rakyat on July 3 also provides for a minimum and maximum age for office-bearers of registered youth societies, which is not less than 18 years and not more than 30 years, as on the date of appointment.
+When winding up the debate, Youth and Sports Minister Syed Saddiq Syed Abdul Rahman said the transition plan on the age cap would only officially begin by the end of December 2021.
+“It means that we have another two years. At the same time, if the election of an organisation is held, for example in November 2021, those (over 30 years old) can still play a role in the youth societies until the next election cycle.
+“For example if a person is 34 years old in November 2021 and competes in the election and win, the individual will not lose his post and can continue to serve until the next election,” he said.
+The Dewan Negara sitting continues tomorrow. — Bernama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">syed saddiq policies
+(https://www.sinardaily.my/article/214107/focus/new-youth-limit-to-enhance-their-maturity-level---experts)
+New youth limit to enhance their maturity level - Experts
+(https://www.nst.com.my/sports/others/2025/07/1243149/hannah-yeoh-youth-age-cap-30-take-effect-jan-1-next-year)
+Hannah Yeoh: Youth age cap of 30 to take effect Jan 1 next year </t>
   </si>
 </sst>
 </file>
@@ -5033,7 +5058,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C8237E3-DA57-49D7-B827-78ACC8405853}">
-  <dimension ref="A1:H564"/>
+  <dimension ref="A1:H565"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23.28515625" customWidth="1"/>
@@ -5544,76 +5569,76 @@
     <row r="32" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="2"/>
       <c r="C32" s="3">
-        <v>43672</v>
+        <v>43670</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>55</v>
+        <v>681</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>56</v>
+        <v>682</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>4</v>
+        <v>683</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>684</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="2"/>
       <c r="C33" s="3">
+        <v>43672</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="2"/>
+      <c r="C34" s="3">
         <v>43690</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D34" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E34" s="4" t="s">
         <v>571</v>
       </c>
-      <c r="F33" s="2" t="s">
+      <c r="F34" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G34" s="1" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B34" s="2" t="s">
+    <row r="35" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B35" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F34" s="2"/>
-    </row>
-    <row r="35" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="2"/>
-      <c r="C35" s="3">
-        <v>43792</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F35" s="2"/>
+    </row>
+    <row r="36" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="2"/>
       <c r="C36" s="3">
-        <v>43795</v>
+        <v>43792</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>111</v>
+        <v>387</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>112</v>
+        <v>388</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>113</v>
+        <v>389</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>4</v>
@@ -5622,16 +5647,16 @@
     <row r="37" spans="1:7" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="2"/>
       <c r="C37" s="3">
-        <v>43801</v>
+        <v>43795</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>311</v>
+        <v>111</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>312</v>
+        <v>112</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>313</v>
+        <v>113</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>4</v>
@@ -5640,16 +5665,16 @@
     <row r="38" spans="1:7" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="2"/>
       <c r="C38" s="3">
-        <v>43802</v>
+        <v>43801</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>390</v>
+        <v>311</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>391</v>
+        <v>312</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>392</v>
+        <v>313</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>4</v>
@@ -5658,52 +5683,52 @@
     <row r="39" spans="1:7" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="2"/>
       <c r="C39" s="3">
-        <v>43805</v>
+        <v>43802</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>277</v>
+        <v>390</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>278</v>
+        <v>391</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>279</v>
+        <v>392</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>280</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="2"/>
       <c r="C40" s="3">
-        <v>43806</v>
+        <v>43805</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>656</v>
+        <v>277</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>657</v>
+        <v>278</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>658</v>
+        <v>279</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>4</v>
+        <v>280</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="2"/>
       <c r="C41" s="3">
-        <v>43812</v>
+        <v>43806</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>164</v>
+        <v>656</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>165</v>
+        <v>657</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>166</v>
+        <v>658</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>4</v>
@@ -5712,16 +5737,16 @@
     <row r="42" spans="1:7" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="2"/>
       <c r="C42" s="3">
-        <v>43813</v>
+        <v>43812</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>346</v>
+        <v>164</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>345</v>
+        <v>165</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>344</v>
+        <v>166</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>4</v>
@@ -5730,82 +5755,81 @@
     <row r="43" spans="1:7" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="2"/>
       <c r="C43" s="3">
+        <v>43813</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="2"/>
+      <c r="C44" s="3">
         <v>43820</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D44" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="E44" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="F43" s="2" t="s">
+      <c r="F44" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="G43" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="1">
+      <c r="G44" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
         <v>2020</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B45" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="2"/>
-    </row>
-    <row r="45" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="1"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="3">
-        <v>43835</v>
-      </c>
-      <c r="D45" t="s">
-        <v>467</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F45" s="2"/>
+    </row>
+    <row r="46" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="2"/>
       <c r="C46" s="3">
-        <v>43836</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>393</v>
+        <v>43835</v>
+      </c>
+      <c r="D46" t="s">
+        <v>467</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>394</v>
+        <v>468</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>395</v>
+        <v>469</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="2"/>
       <c r="C47" s="3">
-        <v>43837</v>
+        <v>43836</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>35</v>
+        <v>393</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>38</v>
+        <v>394</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>36</v>
+        <v>395</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>4</v>
@@ -5815,16 +5839,16 @@
       <c r="A48" s="1"/>
       <c r="B48" s="2"/>
       <c r="C48" s="3">
-        <v>43839</v>
+        <v>43837</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>432</v>
+        <v>35</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>433</v>
+        <v>38</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>434</v>
+        <v>36</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>4</v>
@@ -5834,16 +5858,16 @@
       <c r="A49" s="1"/>
       <c r="B49" s="2"/>
       <c r="C49" s="3">
-        <v>43843</v>
+        <v>43839</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>99</v>
+        <v>432</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>100</v>
+        <v>433</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>101</v>
+        <v>434</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>4</v>
@@ -5853,16 +5877,16 @@
       <c r="A50" s="1"/>
       <c r="B50" s="2"/>
       <c r="C50" s="3">
-        <v>43846</v>
+        <v>43843</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>4</v>
@@ -5872,54 +5896,54 @@
       <c r="A51" s="1"/>
       <c r="B51" s="2"/>
       <c r="C51" s="3">
-        <v>43852</v>
-      </c>
-      <c r="D51" t="s">
-        <v>502</v>
+        <v>43846</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>503</v>
+        <v>103</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>504</v>
+        <v>104</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>350</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" s="2"/>
       <c r="C52" s="3">
-        <v>43860</v>
+        <v>43852</v>
       </c>
       <c r="D52" t="s">
-        <v>539</v>
+        <v>502</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>540</v>
+        <v>503</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>541</v>
+        <v>504</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>4</v>
+        <v>350</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="B53" s="2"/>
       <c r="C53" s="3">
-        <v>43863</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>405</v>
+        <v>43860</v>
+      </c>
+      <c r="D53" t="s">
+        <v>539</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>406</v>
+        <v>540</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>407</v>
+        <v>541</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>4</v>
@@ -5929,38 +5953,38 @@
       <c r="A54" s="1"/>
       <c r="B54" s="2"/>
       <c r="C54" s="3">
-        <v>43885</v>
+        <v>43863</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>266</v>
+        <v>405</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>267</v>
+        <v>406</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>269</v>
+        <v>407</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="B55" s="2"/>
       <c r="C55" s="3">
-        <v>43887</v>
+        <v>43885</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>381</v>
+        <v>266</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>383</v>
+        <v>267</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>4</v>
+        <v>268</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -5970,13 +5994,13 @@
         <v>43887</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>417</v>
+        <v>381</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>418</v>
+        <v>383</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>419</v>
+        <v>382</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>4</v>
@@ -5986,54 +6010,54 @@
       <c r="A57" s="1"/>
       <c r="B57" s="2"/>
       <c r="C57" s="3">
-        <v>43893</v>
+        <v>43887</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>231</v>
+        <v>417</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>232</v>
+        <v>418</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>233</v>
+        <v>419</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>241</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="B58" s="2"/>
       <c r="C58" s="3">
-        <v>43895</v>
+        <v>43893</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>493</v>
+        <v>231</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>494</v>
+        <v>232</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>495</v>
+        <v>233</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>4</v>
+        <v>241</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="B59" s="2"/>
       <c r="C59" s="3">
-        <v>43913</v>
+        <v>43895</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>96</v>
+        <v>493</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>97</v>
+        <v>494</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>98</v>
+        <v>495</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>4</v>
@@ -6043,16 +6067,16 @@
       <c r="A60" s="1"/>
       <c r="B60" s="2"/>
       <c r="C60" s="3">
-        <v>43916</v>
+        <v>43913</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>499</v>
+        <v>96</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>500</v>
+        <v>97</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>501</v>
+        <v>98</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>4</v>
@@ -6062,99 +6086,99 @@
       <c r="A61" s="1"/>
       <c r="B61" s="2"/>
       <c r="C61" s="3">
+        <v>43916</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="1"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="3">
         <v>43921</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="D62" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="E61" s="1" t="s">
+      <c r="E62" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="F61" s="2" t="s">
+      <c r="F62" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="G61" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="1"/>
-      <c r="B62" s="2" t="s">
+      <c r="G62" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="1"/>
+      <c r="B63" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F62" s="2"/>
-    </row>
-    <row r="63" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="1"/>
-      <c r="B63" s="2"/>
-      <c r="C63" s="3">
-        <v>43932</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="F63" s="2"/>
     </row>
     <row r="64" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="B64" s="2"/>
       <c r="C64" s="3">
-        <v>43950</v>
+        <v>43932</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>626</v>
+        <v>524</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>627</v>
+        <v>525</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>628</v>
+        <v>526</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="B65" s="2"/>
       <c r="C65" s="3">
-        <v>43964</v>
+        <v>43950</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>402</v>
+        <v>626</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>403</v>
+        <v>627</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>404</v>
+        <v>628</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>4</v>
+        <v>350</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="B66" s="2"/>
       <c r="C66" s="3">
-        <v>43968</v>
+        <v>43964</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>536</v>
+        <v>402</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>537</v>
+        <v>403</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>538</v>
+        <v>404</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>4</v>
@@ -6164,16 +6188,16 @@
       <c r="A67" s="1"/>
       <c r="B67" s="2"/>
       <c r="C67" s="3">
-        <v>43978</v>
+        <v>43968</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>4</v>
@@ -6183,16 +6207,16 @@
       <c r="A68" s="1"/>
       <c r="B68" s="2"/>
       <c r="C68" s="3">
-        <v>43981</v>
+        <v>43978</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>637</v>
+        <v>527</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>636</v>
+        <v>528</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>635</v>
+        <v>529</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>4</v>
@@ -6202,16 +6226,16 @@
       <c r="A69" s="1"/>
       <c r="B69" s="2"/>
       <c r="C69" s="3">
-        <v>43984</v>
+        <v>43981</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>351</v>
+        <v>637</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>352</v>
+        <v>636</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>353</v>
+        <v>635</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>4</v>
@@ -6221,73 +6245,73 @@
       <c r="A70" s="1"/>
       <c r="B70" s="2"/>
       <c r="C70" s="3">
-        <v>43986</v>
+        <v>43984</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="B71" s="2"/>
       <c r="C71" s="3">
-        <v>43993</v>
+        <v>43986</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>350</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="B72" s="2"/>
       <c r="C72" s="3">
-        <v>44007</v>
+        <v>43993</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>629</v>
+        <v>347</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>630</v>
+        <v>348</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>631</v>
+        <v>349</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>4</v>
+        <v>350</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="B73" s="2"/>
       <c r="C73" s="3">
-        <v>44010</v>
+        <v>44007</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>596</v>
+        <v>629</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>597</v>
+        <v>630</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>598</v>
+        <v>631</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>4</v>
@@ -6297,16 +6321,16 @@
       <c r="A74" s="1"/>
       <c r="B74" s="2"/>
       <c r="C74" s="3">
-        <v>44012</v>
+        <v>44010</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>384</v>
+        <v>596</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>385</v>
+        <v>597</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>386</v>
+        <v>598</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>4</v>
@@ -6319,77 +6343,77 @@
         <v>44012</v>
       </c>
       <c r="D75" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="1"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="3">
+        <v>44012</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="E75" s="1" t="s">
+      <c r="E76" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="F75" s="2" t="s">
+      <c r="F76" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="G75" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="1"/>
-      <c r="B76" s="2" t="s">
+      <c r="G76" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="1"/>
+      <c r="B77" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F76" s="2"/>
-    </row>
-    <row r="77" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="1"/>
-      <c r="B77" s="2"/>
-      <c r="C77" s="3">
-        <v>44013</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>668</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>669</v>
-      </c>
-      <c r="F77" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F77" s="2"/>
+    </row>
+    <row r="78" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="2"/>
       <c r="C78" s="3">
-        <v>44015</v>
+        <v>44013</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>599</v>
+        <v>668</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>600</v>
+        <v>669</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>601</v>
+        <v>670</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="2"/>
       <c r="C79" s="3">
-        <v>44016</v>
+        <v>44015</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>214</v>
+        <v>599</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>215</v>
+        <v>600</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>216</v>
+        <v>601</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>4</v>
@@ -6399,16 +6423,16 @@
       <c r="A80" s="1"/>
       <c r="B80" s="2"/>
       <c r="C80" s="3">
-        <v>44018</v>
+        <v>44016</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>641</v>
+        <v>214</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>642</v>
+        <v>215</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>643</v>
+        <v>216</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>4</v>
@@ -6437,54 +6461,54 @@
       <c r="A82" s="1"/>
       <c r="B82" s="2"/>
       <c r="C82" s="3">
-        <v>44022</v>
+        <v>44018</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>479</v>
+        <v>641</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>480</v>
+        <v>642</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>481</v>
+        <v>643</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>482</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="B83" s="2"/>
       <c r="C83" s="3">
-        <v>44025</v>
+        <v>44022</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>605</v>
+        <v>479</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>606</v>
+        <v>480</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>607</v>
+        <v>481</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>4</v>
+        <v>482</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="2"/>
       <c r="C84" s="3">
-        <v>44031</v>
+        <v>44025</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>357</v>
+        <v>605</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>358</v>
+        <v>606</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>359</v>
+        <v>607</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>4</v>
@@ -6493,17 +6517,17 @@
     <row r="85" spans="1:7" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="2"/>
-      <c r="C85" s="8">
-        <v>44051</v>
+      <c r="C85" s="3">
+        <v>44031</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>4</v>
@@ -6513,16 +6537,16 @@
       <c r="A86" s="1"/>
       <c r="B86" s="2"/>
       <c r="C86" s="8">
-        <v>44060</v>
+        <v>44051</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>202</v>
+        <v>360</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>203</v>
+        <v>361</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>204</v>
+        <v>362</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>4</v>
@@ -6532,16 +6556,16 @@
       <c r="A87" s="1"/>
       <c r="B87" s="2"/>
       <c r="C87" s="8">
-        <v>44065</v>
+        <v>44060</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>429</v>
+        <v>202</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>430</v>
+        <v>203</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>431</v>
+        <v>204</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>4</v>
@@ -6551,16 +6575,16 @@
       <c r="A88" s="1"/>
       <c r="B88" s="2"/>
       <c r="C88" s="8">
-        <v>44069</v>
+        <v>44065</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>220</v>
+        <v>429</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>221</v>
+        <v>430</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>222</v>
+        <v>431</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>4</v>
@@ -6570,95 +6594,95 @@
       <c r="A89" s="1"/>
       <c r="B89" s="2"/>
       <c r="C89" s="8">
-        <v>44072</v>
+        <v>44069</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="G89" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="2"/>
       <c r="C90" s="8">
         <v>44072</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>340</v>
+        <v>208</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>341</v>
+        <v>209</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>342</v>
+        <v>210</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>343</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="2"/>
       <c r="C91" s="8">
-        <v>44076</v>
+        <v>44072</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>205</v>
+        <v>340</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>206</v>
+        <v>341</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>207</v>
+        <v>342</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>4</v>
+        <v>343</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="2"/>
-      <c r="C92" s="3">
-        <v>44078</v>
+      <c r="C92" s="8">
+        <v>44076</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>445</v>
+        <v>205</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>446</v>
+        <v>206</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>447</v>
+        <v>207</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>448</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="2"/>
       <c r="C93" s="3">
-        <v>44084</v>
+        <v>44078</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>143</v>
+        <v>445</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>144</v>
+        <v>446</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>145</v>
+        <v>447</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>4</v>
+        <v>448</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -6668,13 +6692,13 @@
         <v>44084</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>372</v>
+        <v>143</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>373</v>
+        <v>144</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>374</v>
+        <v>145</v>
       </c>
       <c r="G94" s="1" t="s">
         <v>4</v>
@@ -6683,17 +6707,17 @@
     <row r="95" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="2"/>
-      <c r="C95" s="8">
-        <v>44085</v>
+      <c r="C95" s="3">
+        <v>44084</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>213</v>
+        <v>372</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>373</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>212</v>
+        <v>374</v>
       </c>
       <c r="G95" s="1" t="s">
         <v>4</v>
@@ -6703,141 +6727,141 @@
       <c r="A96" s="1"/>
       <c r="B96" s="2"/>
       <c r="C96" s="8">
-        <v>44087</v>
+        <v>44085</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>223</v>
+        <v>4</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="2"/>
       <c r="C97" s="8">
-        <v>44090</v>
+        <v>44087</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>245</v>
+        <v>217</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>246</v>
+        <v>218</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>247</v>
+        <v>219</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>248</v>
+        <v>223</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="2"/>
       <c r="C98" s="8">
+        <v>44090</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="1"/>
+      <c r="B99" s="2"/>
+      <c r="C99" s="8">
         <v>44096</v>
       </c>
-      <c r="D98" s="1" t="s">
+      <c r="D99" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="E98" s="2" t="s">
+      <c r="E99" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="F98" s="2" t="s">
+      <c r="F99" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="G98" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A99" s="1"/>
-      <c r="B99" s="2" t="s">
+      <c r="G99" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A100" s="1"/>
+      <c r="B100" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F99" s="2"/>
-    </row>
-    <row r="100" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="1"/>
-      <c r="B100" s="2"/>
+      <c r="F100" s="2"/>
     </row>
     <row r="101" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="2"/>
-      <c r="C101" s="3">
-        <v>44089</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="G101" s="1" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="102" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="2"/>
       <c r="C102" s="3">
-        <v>44106</v>
+        <v>44089</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>545</v>
+        <v>521</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>546</v>
+        <v>522</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>547</v>
+        <v>523</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="2"/>
       <c r="C103" s="3">
-        <v>44115</v>
+        <v>44106</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>87</v>
+        <v>545</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>88</v>
+        <v>546</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>89</v>
+        <v>547</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>4</v>
+        <v>350</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="2"/>
       <c r="C104" s="3">
-        <v>44117</v>
+        <v>44115</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>435</v>
+        <v>87</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>436</v>
+        <v>88</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>437</v>
+        <v>89</v>
       </c>
       <c r="G104" s="1" t="s">
         <v>4</v>
@@ -6847,16 +6871,16 @@
       <c r="A105" s="1"/>
       <c r="B105" s="2"/>
       <c r="C105" s="3">
-        <v>44152</v>
+        <v>44117</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>75</v>
+        <v>435</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>76</v>
+        <v>436</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>77</v>
+        <v>437</v>
       </c>
       <c r="G105" s="1" t="s">
         <v>4</v>
@@ -6866,16 +6890,16 @@
       <c r="A106" s="1"/>
       <c r="B106" s="2"/>
       <c r="C106" s="3">
-        <v>44153</v>
+        <v>44152</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>414</v>
+        <v>75</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>415</v>
+        <v>76</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>416</v>
+        <v>77</v>
       </c>
       <c r="G106" s="1" t="s">
         <v>4</v>
@@ -6885,16 +6909,16 @@
       <c r="A107" s="1"/>
       <c r="B107" s="2"/>
       <c r="C107" s="3">
-        <v>44154</v>
+        <v>44153</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>168</v>
+        <v>414</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>169</v>
+        <v>415</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>170</v>
+        <v>416</v>
       </c>
       <c r="G107" s="1" t="s">
         <v>4</v>
@@ -6904,16 +6928,16 @@
       <c r="A108" s="1"/>
       <c r="B108" s="2"/>
       <c r="C108" s="3">
-        <v>44161</v>
+        <v>44154</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>551</v>
+        <v>168</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>552</v>
+        <v>169</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>553</v>
+        <v>170</v>
       </c>
       <c r="G108" s="1" t="s">
         <v>4</v>
@@ -6923,16 +6947,16 @@
       <c r="A109" s="1"/>
       <c r="B109" s="2"/>
       <c r="C109" s="3">
-        <v>44163</v>
+        <v>44161</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="G109" s="1" t="s">
         <v>4</v>
@@ -6942,16 +6966,16 @@
       <c r="A110" s="1"/>
       <c r="B110" s="2"/>
       <c r="C110" s="3">
-        <v>44168</v>
+        <v>44163</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>122</v>
+        <v>548</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>123</v>
+        <v>549</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>124</v>
+        <v>550</v>
       </c>
       <c r="G110" s="1" t="s">
         <v>4</v>
@@ -6961,35 +6985,35 @@
       <c r="A111" s="1"/>
       <c r="B111" s="2"/>
       <c r="C111" s="3">
-        <v>44172</v>
+        <v>44168</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>665</v>
+        <v>122</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>666</v>
+        <v>123</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>667</v>
+        <v>124</v>
       </c>
       <c r="G111" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="2"/>
       <c r="C112" s="3">
-        <v>44179</v>
+        <v>44172</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>333</v>
+        <v>665</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>334</v>
+        <v>666</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>335</v>
+        <v>667</v>
       </c>
       <c r="G112" s="1" t="s">
         <v>4</v>
@@ -6999,85 +7023,85 @@
       <c r="A113" s="1"/>
       <c r="B113" s="2"/>
       <c r="C113" s="3">
-        <v>44187</v>
+        <v>44179</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>67</v>
+        <v>333</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>68</v>
+        <v>334</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>69</v>
+        <v>335</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="2"/>
       <c r="C114" s="3">
+        <v>44187</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="1"/>
+      <c r="B115" s="2"/>
+      <c r="C115" s="3">
         <v>44189</v>
       </c>
-      <c r="D114" s="1" t="s">
+      <c r="D115" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="E114" s="1" t="s">
+      <c r="E115" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="F114" s="2" t="s">
+      <c r="F115" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="G114" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A115" s="1">
+      <c r="G115" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A116" s="1">
         <v>2021</v>
       </c>
-      <c r="B115" s="2" t="s">
+      <c r="B116" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="116" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="1"/>
-      <c r="B116" s="2"/>
     </row>
     <row r="117" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="2"/>
-      <c r="C117" s="3">
-        <v>44220</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="F117" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="G117" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="118" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="2"/>
       <c r="C118" s="3">
-        <v>44225</v>
+        <v>44220</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>296</v>
+        <v>461</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>297</v>
+        <v>462</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>298</v>
+        <v>463</v>
       </c>
       <c r="G118" s="1" t="s">
         <v>4</v>
@@ -7087,16 +7111,16 @@
       <c r="A119" s="1"/>
       <c r="B119" s="2"/>
       <c r="C119" s="3">
-        <v>44229</v>
-      </c>
-      <c r="D119" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E119" s="2" t="s">
-        <v>74</v>
+        <v>44225</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>297</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>22</v>
+        <v>298</v>
       </c>
       <c r="G119" s="1" t="s">
         <v>4</v>
@@ -7106,35 +7130,35 @@
       <c r="A120" s="1"/>
       <c r="B120" s="2"/>
       <c r="C120" s="3">
-        <v>44244</v>
+        <v>44229</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>180</v>
+        <v>21</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>181</v>
+        <v>74</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>182</v>
+        <v>22</v>
       </c>
       <c r="G120" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="2"/>
       <c r="C121" s="3">
-        <v>44247</v>
+        <v>44244</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G121" s="1" t="s">
         <v>4</v>
@@ -7144,182 +7168,182 @@
       <c r="A122" s="1"/>
       <c r="B122" s="2"/>
       <c r="C122" s="3">
-        <v>44248</v>
+        <v>44247</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>441</v>
+        <v>177</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>442</v>
+        <v>178</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>443</v>
+        <v>179</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>444</v>
+        <v>4</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="2"/>
       <c r="C123" s="3">
+        <v>44248</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="1"/>
+      <c r="B124" s="2"/>
+      <c r="C124" s="3">
         <v>44277</v>
       </c>
-      <c r="D123" s="2" t="s">
+      <c r="D124" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E123" s="2" t="s">
+      <c r="E124" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F123" s="2" t="s">
+      <c r="F124" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="G123" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="1"/>
-      <c r="B124" s="2" t="s">
+      <c r="G124" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="1"/>
+      <c r="B125" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C124" s="3">
+      <c r="C125" s="3">
         <v>44301</v>
       </c>
-      <c r="D124" s="1" t="s">
+      <c r="D125" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E124" s="1" t="s">
+      <c r="E125" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="F124" s="2" t="s">
+      <c r="F125" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="G124" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A125" s="1"/>
-      <c r="B125" s="2"/>
-      <c r="C125" s="3">
-        <v>44311</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F125" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="G125" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="2"/>
       <c r="C126" s="3">
-        <v>44319</v>
+        <v>44311</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>140</v>
+        <v>12</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>141</v>
+        <v>13</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>142</v>
+        <v>4</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="2"/>
       <c r="C127" s="3">
-        <v>44361</v>
+        <v>44319</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>632</v>
+        <v>139</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>633</v>
+        <v>140</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>634</v>
+        <v>141</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>4</v>
+        <v>142</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="B128" s="2"/>
       <c r="C128" s="3">
-        <v>44368</v>
+        <v>44361</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>308</v>
+        <v>632</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>309</v>
+        <v>633</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>310</v>
+        <v>634</v>
       </c>
       <c r="G128" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="2"/>
       <c r="C129" s="3">
+        <v>44368</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="G129" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A130" s="1"/>
+      <c r="B130" s="2"/>
+      <c r="C130" s="3">
         <v>44375</v>
       </c>
-      <c r="D129" s="1" t="s">
+      <c r="D130" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F129" s="2" t="s">
+      <c r="F130" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G129" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A130" s="1"/>
-      <c r="B130" s="2" t="s">
+      <c r="G130" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A131" s="1"/>
+      <c r="B131" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C130" s="3">
+      <c r="C131" s="3">
         <v>44390</v>
       </c>
-      <c r="D130" s="1" t="s">
+      <c r="D131" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F130" s="1" t="s">
+      <c r="F131" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="G130" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="1"/>
-      <c r="B131" s="2"/>
-      <c r="C131" s="3">
-        <v>44398</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="F131" s="2" t="s">
-        <v>454</v>
       </c>
       <c r="G131" s="1" t="s">
         <v>4</v>
@@ -7329,35 +7353,35 @@
       <c r="A132" s="1"/>
       <c r="B132" s="2"/>
       <c r="C132" s="3">
-        <v>44408</v>
+        <v>44398</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="G132" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133" s="2"/>
       <c r="C133" s="3">
-        <v>44411</v>
+        <v>44408</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>369</v>
+        <v>455</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>370</v>
+        <v>456</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>371</v>
+        <v>457</v>
       </c>
       <c r="G133" s="1" t="s">
         <v>4</v>
@@ -7370,32 +7394,32 @@
         <v>44411</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>476</v>
+        <v>369</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>477</v>
+        <v>370</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>478</v>
+        <v>371</v>
       </c>
       <c r="G134" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="135" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="B135" s="2"/>
       <c r="C135" s="3">
-        <v>44413</v>
+        <v>44411</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>78</v>
+        <v>476</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>79</v>
+        <v>477</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>80</v>
+        <v>478</v>
       </c>
       <c r="G135" s="1" t="s">
         <v>4</v>
@@ -7405,16 +7429,16 @@
       <c r="A136" s="1"/>
       <c r="B136" s="2"/>
       <c r="C136" s="3">
-        <v>44422</v>
+        <v>44413</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>650</v>
+        <v>78</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>651</v>
+        <v>79</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>652</v>
+        <v>80</v>
       </c>
       <c r="G136" s="1" t="s">
         <v>4</v>
@@ -7424,16 +7448,16 @@
       <c r="A137" s="1"/>
       <c r="B137" s="2"/>
       <c r="C137" s="3">
-        <v>44443</v>
+        <v>44422</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>487</v>
+        <v>650</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>488</v>
+        <v>651</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>489</v>
+        <v>652</v>
       </c>
       <c r="G137" s="1" t="s">
         <v>4</v>
@@ -7443,44 +7467,44 @@
       <c r="A138" s="1"/>
       <c r="B138" s="2"/>
       <c r="C138" s="3">
+        <v>44443</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="1"/>
+      <c r="B139" s="2"/>
+      <c r="C139" s="3">
         <v>44454</v>
       </c>
-      <c r="D138" s="1" t="s">
+      <c r="D139" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="E138" s="1" t="s">
+      <c r="E139" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="F138" s="2" t="s">
+      <c r="F139" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="G138" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="1"/>
-      <c r="B139" s="2" t="s">
-        <v>8</v>
+      <c r="G139" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="140" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
-      <c r="B140" s="2"/>
-      <c r="C140" s="3">
-        <v>44473</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="F140" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="G140" s="1" t="s">
-        <v>4</v>
+      <c r="B140" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="141" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7490,89 +7514,89 @@
         <v>44473</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="B142" s="2"/>
       <c r="C142" s="3">
-        <v>44477</v>
+        <v>44473</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>81</v>
+        <v>227</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>82</v>
+        <v>228</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>83</v>
+        <v>229</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>4</v>
+        <v>230</v>
       </c>
     </row>
     <row r="143" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="2"/>
       <c r="C143" s="3">
-        <v>44488</v>
+        <v>44477</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>234</v>
+        <v>81</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>235</v>
+        <v>82</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>236</v>
+        <v>83</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>240</v>
+        <v>4</v>
       </c>
     </row>
     <row r="144" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="2"/>
       <c r="C144" s="3">
-        <v>44497</v>
+        <v>44488</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>174</v>
+        <v>234</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>175</v>
+        <v>235</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>176</v>
+        <v>236</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>4</v>
+        <v>240</v>
       </c>
     </row>
     <row r="145" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="B145" s="2"/>
       <c r="C145" s="3">
-        <v>44501</v>
+        <v>44497</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>644</v>
+        <v>174</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>645</v>
+        <v>175</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>646</v>
+        <v>176</v>
       </c>
       <c r="G145" s="1" t="s">
         <v>4</v>
@@ -7582,16 +7606,16 @@
       <c r="A146" s="1"/>
       <c r="B146" s="2"/>
       <c r="C146" s="3">
-        <v>44509</v>
+        <v>44501</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>293</v>
+        <v>644</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>294</v>
+        <v>645</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>295</v>
+        <v>646</v>
       </c>
       <c r="G146" s="1" t="s">
         <v>4</v>
@@ -7601,54 +7625,54 @@
       <c r="A147" s="1"/>
       <c r="B147" s="2"/>
       <c r="C147" s="3">
-        <v>44510</v>
+        <v>44509</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>289</v>
+        <v>4</v>
       </c>
     </row>
     <row r="148" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="B148" s="2"/>
       <c r="C148" s="3">
-        <v>44515</v>
+        <v>44510</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>171</v>
+        <v>286</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>172</v>
+        <v>287</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>173</v>
+        <v>288</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>4</v>
+        <v>289</v>
       </c>
     </row>
     <row r="149" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="B149" s="2"/>
       <c r="C149" s="3">
-        <v>44518</v>
+        <v>44515</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>242</v>
+        <v>171</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>243</v>
+        <v>172</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>244</v>
+        <v>173</v>
       </c>
       <c r="G149" s="1" t="s">
         <v>4</v>
@@ -7658,54 +7682,54 @@
       <c r="A150" s="1"/>
       <c r="B150" s="2"/>
       <c r="C150" s="3">
-        <v>44519</v>
+        <v>44518</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>155</v>
+        <v>242</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>156</v>
+        <v>243</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>157</v>
+        <v>244</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>281</v>
+        <v>4</v>
       </c>
     </row>
     <row r="151" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="B151" s="2"/>
       <c r="C151" s="3">
-        <v>44524</v>
+        <v>44519</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>659</v>
+        <v>155</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>660</v>
+        <v>156</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>661</v>
+        <v>157</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>4</v>
+        <v>281</v>
       </c>
     </row>
     <row r="152" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="B152" s="2"/>
       <c r="C152" s="3">
-        <v>44525</v>
+        <v>44524</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>558</v>
+        <v>659</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>559</v>
+        <v>660</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>560</v>
+        <v>661</v>
       </c>
       <c r="G152" s="1" t="s">
         <v>4</v>
@@ -7715,16 +7739,16 @@
       <c r="A153" s="1"/>
       <c r="B153" s="2"/>
       <c r="C153" s="3">
-        <v>44527</v>
+        <v>44525</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>647</v>
+        <v>558</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>648</v>
+        <v>559</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>649</v>
+        <v>560</v>
       </c>
       <c r="G153" s="1" t="s">
         <v>4</v>
@@ -7734,16 +7758,16 @@
       <c r="A154" s="1"/>
       <c r="B154" s="2"/>
       <c r="C154" s="3">
-        <v>44529</v>
+        <v>44527</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>458</v>
+        <v>647</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>459</v>
+        <v>648</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>460</v>
+        <v>649</v>
       </c>
       <c r="G154" s="1" t="s">
         <v>4</v>
@@ -7753,54 +7777,54 @@
       <c r="A155" s="1"/>
       <c r="B155" s="2"/>
       <c r="C155" s="3">
-        <v>44532</v>
+        <v>44529</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>423</v>
+        <v>458</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>424</v>
+        <v>459</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>425</v>
+        <v>460</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>350</v>
+        <v>4</v>
       </c>
     </row>
     <row r="156" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="B156" s="2"/>
       <c r="C156" s="3">
-        <v>44543</v>
+        <v>44532</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>490</v>
+        <v>423</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>491</v>
+        <v>424</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>492</v>
+        <v>425</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>4</v>
+        <v>350</v>
       </c>
     </row>
     <row r="157" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="B157" s="2"/>
       <c r="C157" s="3">
-        <v>44550</v>
+        <v>44543</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>470</v>
+        <v>490</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>472</v>
+        <v>492</v>
       </c>
       <c r="G157" s="1" t="s">
         <v>4</v>
@@ -7810,84 +7834,84 @@
       <c r="A158" s="1"/>
       <c r="B158" s="2"/>
       <c r="C158" s="3">
+        <v>44550</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="F158" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="G158" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="1"/>
+      <c r="B159" s="2"/>
+      <c r="C159" s="3">
         <v>44557</v>
       </c>
-      <c r="D158" s="1" t="s">
+      <c r="D159" s="1" t="s">
         <v>620</v>
       </c>
-      <c r="E158" s="1" t="s">
+      <c r="E159" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="F158" s="2" t="s">
+      <c r="F159" s="2" t="s">
         <v>622</v>
       </c>
-      <c r="G158" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="1">
+      <c r="G159" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="1">
         <v>2022</v>
       </c>
     </row>
-    <row r="160" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="1"/>
-      <c r="B160" s="2" t="s">
+    <row r="161" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="1"/>
+      <c r="B161" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="161" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="1"/>
-      <c r="B161" s="2"/>
-      <c r="C161" s="3">
-        <v>44566</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>617</v>
-      </c>
-      <c r="E161" s="1" t="s">
-        <v>618</v>
-      </c>
-      <c r="F161" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="G161" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="B162" s="2"/>
       <c r="C162" s="3">
-        <v>44569</v>
+        <v>44566</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>464</v>
+        <v>617</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>465</v>
+        <v>618</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>466</v>
+        <v>619</v>
       </c>
       <c r="G162" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="163" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="B163" s="2"/>
       <c r="C163" s="3">
-        <v>44577</v>
+        <v>44569</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>29</v>
+        <v>464</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>511</v>
+        <v>465</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>30</v>
+        <v>466</v>
       </c>
       <c r="G163" s="1" t="s">
         <v>4</v>
@@ -7900,13 +7924,13 @@
         <v>44577</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>513</v>
+        <v>29</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>514</v>
+        <v>30</v>
       </c>
       <c r="G164" s="1" t="s">
         <v>4</v>
@@ -7916,16 +7940,16 @@
       <c r="A165" s="1"/>
       <c r="B165" s="2"/>
       <c r="C165" s="3">
-        <v>44582</v>
+        <v>44577</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="G165" s="1" t="s">
         <v>4</v>
@@ -7935,35 +7959,35 @@
       <c r="A166" s="1"/>
       <c r="B166" s="2"/>
       <c r="C166" s="3">
-        <v>44588</v>
+        <v>44582</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>542</v>
+        <v>515</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>543</v>
+        <v>516</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>544</v>
+        <v>517</v>
       </c>
       <c r="G166" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="167" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="B167" s="2"/>
       <c r="C167" s="3">
-        <v>44595</v>
+        <v>44588</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="E167" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="F167" s="5" t="s">
-        <v>160</v>
+        <v>542</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>544</v>
       </c>
       <c r="G167" s="1" t="s">
         <v>4</v>
@@ -7973,16 +7997,16 @@
       <c r="A168" s="1"/>
       <c r="B168" s="2"/>
       <c r="C168" s="3">
-        <v>44605</v>
+        <v>44595</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G168" s="1" t="s">
         <v>4</v>
@@ -7992,19 +8016,19 @@
       <c r="A169" s="1"/>
       <c r="B169" s="2"/>
       <c r="C169" s="3">
-        <v>44623</v>
+        <v>44605</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>336</v>
+        <v>161</v>
       </c>
       <c r="E169" s="6" t="s">
-        <v>337</v>
+        <v>162</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>338</v>
+        <v>163</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>339</v>
+        <v>4</v>
       </c>
     </row>
     <row r="170" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8014,70 +8038,70 @@
         <v>44623</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>420</v>
+        <v>336</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>421</v>
+        <v>337</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>422</v>
+        <v>338</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>4</v>
+        <v>339</v>
       </c>
     </row>
     <row r="171" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="B171" s="2"/>
       <c r="C171" s="3">
-        <v>44634</v>
+        <v>44623</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>674</v>
+        <v>420</v>
       </c>
       <c r="E171" s="6" t="s">
-        <v>675</v>
+        <v>421</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>676</v>
+        <v>422</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>677</v>
+        <v>4</v>
       </c>
     </row>
     <row r="172" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="B172" s="2"/>
       <c r="C172" s="3">
-        <v>44635</v>
+        <v>44634</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>574</v>
+        <v>674</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>575</v>
+        <v>675</v>
       </c>
       <c r="F172" s="5" t="s">
-        <v>576</v>
+        <v>676</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="B173" s="2"/>
       <c r="C173" s="3">
         <v>44635</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E173" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F173" s="2" t="s">
-        <v>44</v>
+        <v>574</v>
+      </c>
+      <c r="E173" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="F173" s="5" t="s">
+        <v>576</v>
       </c>
       <c r="G173" s="1" t="s">
         <v>4</v>
@@ -8087,54 +8111,54 @@
       <c r="A174" s="1"/>
       <c r="B174" s="2"/>
       <c r="C174" s="3">
-        <v>44639</v>
+        <v>44635</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>282</v>
+        <v>42</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>283</v>
+        <v>43</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>284</v>
+        <v>44</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>285</v>
+        <v>4</v>
       </c>
     </row>
     <row r="175" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="B175" s="2"/>
       <c r="C175" s="3">
-        <v>44640</v>
+        <v>44639</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>302</v>
+        <v>282</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>304</v>
+        <v>284</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="B176" s="2"/>
       <c r="C176" s="3">
-        <v>44641</v>
+        <v>44640</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>39</v>
+        <v>302</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>40</v>
+        <v>303</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>41</v>
+        <v>304</v>
       </c>
       <c r="G176" s="1" t="s">
         <v>4</v>
@@ -8147,51 +8171,51 @@
         <v>44641</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>290</v>
+        <v>39</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>291</v>
+        <v>40</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>292</v>
+        <v>41</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>557</v>
+        <v>4</v>
       </c>
     </row>
     <row r="178" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="B178" s="2"/>
       <c r="C178" s="3">
-        <v>44642</v>
+        <v>44641</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>554</v>
+        <v>290</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>555</v>
+        <v>291</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>556</v>
+        <v>292</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>4</v>
+        <v>557</v>
       </c>
     </row>
     <row r="179" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="B179" s="2"/>
       <c r="C179" s="3">
-        <v>44645</v>
+        <v>44642</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E179" s="4" t="s">
-        <v>46</v>
+        <v>554</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>555</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>47</v>
+        <v>556</v>
       </c>
       <c r="G179" s="1" t="s">
         <v>4</v>
@@ -8201,58 +8225,59 @@
       <c r="A180" s="1"/>
       <c r="B180" s="2"/>
       <c r="C180" s="3">
+        <v>44645</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E180" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F180" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G180" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A181" s="1"/>
+      <c r="B181" s="2"/>
+      <c r="C181" s="3">
         <v>44651</v>
       </c>
-      <c r="D180" s="1" t="s">
+      <c r="D181" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="E180" s="4" t="s">
+      <c r="E181" s="4" t="s">
         <v>609</v>
       </c>
-      <c r="F180" s="2" t="s">
+      <c r="F181" s="2" t="s">
         <v>610</v>
       </c>
-      <c r="G180" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B181" s="2" t="s">
+      <c r="G181" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B182" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E181" s="3"/>
-    </row>
-    <row r="182" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B182" s="2"/>
-      <c r="C182" s="3">
-        <v>44666</v>
-      </c>
-      <c r="D182" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="E182" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="F182" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="G182" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="E182" s="3"/>
     </row>
     <row r="183" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B183" s="2"/>
       <c r="C183" s="3">
-        <v>44675</v>
+        <v>44666</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>399</v>
+        <v>263</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>400</v>
+        <v>264</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>401</v>
+        <v>265</v>
       </c>
       <c r="G183" s="1" t="s">
         <v>4</v>
@@ -8261,34 +8286,37 @@
     <row r="184" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B184" s="2"/>
       <c r="C184" s="3">
-        <v>44677</v>
+        <v>44675</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>135</v>
+        <v>399</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>136</v>
+        <v>400</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>137</v>
+        <v>401</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>138</v>
+        <v>4</v>
       </c>
     </row>
     <row r="185" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B185" s="2"/>
       <c r="C185" s="3">
-        <v>44682</v>
+        <v>44677</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F185" s="1" t="s">
-        <v>20</v>
+        <v>135</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F185" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>4</v>
+        <v>138</v>
       </c>
     </row>
     <row r="186" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -8297,13 +8325,10 @@
         <v>44682</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="E186" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="F186" s="2" t="s">
-        <v>226</v>
+        <v>19</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="G186" s="1" t="s">
         <v>4</v>
@@ -8312,16 +8337,16 @@
     <row r="187" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B187" s="2"/>
       <c r="C187" s="3">
-        <v>44692</v>
-      </c>
-      <c r="D187" t="s">
-        <v>249</v>
+        <v>44682</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>224</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>251</v>
+        <v>226</v>
       </c>
       <c r="G187" s="1" t="s">
         <v>4</v>
@@ -8333,13 +8358,13 @@
         <v>44692</v>
       </c>
       <c r="D188" t="s">
-        <v>583</v>
+        <v>249</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>584</v>
+        <v>250</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>585</v>
+        <v>251</v>
       </c>
       <c r="G188" s="1" t="s">
         <v>4</v>
@@ -8348,16 +8373,16 @@
     <row r="189" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B189" s="2"/>
       <c r="C189" s="3">
-        <v>44695</v>
+        <v>44692</v>
       </c>
       <c r="D189" t="s">
-        <v>257</v>
+        <v>583</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>258</v>
+        <v>584</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>259</v>
+        <v>585</v>
       </c>
       <c r="G189" s="1" t="s">
         <v>4</v>
@@ -8366,52 +8391,52 @@
     <row r="190" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B190" s="2"/>
       <c r="C190" s="3">
-        <v>44696</v>
-      </c>
-      <c r="D190" s="1" t="s">
-        <v>198</v>
+        <v>44695</v>
+      </c>
+      <c r="D190" t="s">
+        <v>257</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>199</v>
+        <v>258</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="G190" s="7" t="s">
-        <v>201</v>
+        <v>259</v>
+      </c>
+      <c r="G190" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="191" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B191" s="2"/>
       <c r="C191" s="3">
-        <v>44701</v>
+        <v>44696</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>564</v>
+        <v>198</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>565</v>
+        <v>199</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="G191" s="1" t="s">
-        <v>4</v>
+        <v>200</v>
+      </c>
+      <c r="G191" s="7" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="192" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B192" s="2"/>
       <c r="C192" s="3">
-        <v>44708</v>
+        <v>44701</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>510</v>
+        <v>564</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>509</v>
+        <v>565</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>508</v>
+        <v>566</v>
       </c>
       <c r="G192" s="1" t="s">
         <v>4</v>
@@ -8420,16 +8445,16 @@
     <row r="193" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B193" s="2"/>
       <c r="C193" s="3">
-        <v>44710</v>
+        <v>44708</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>580</v>
+        <v>510</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>581</v>
+        <v>509</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>582</v>
+        <v>508</v>
       </c>
       <c r="G193" s="1" t="s">
         <v>4</v>
@@ -8438,52 +8463,52 @@
     <row r="194" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B194" s="2"/>
       <c r="C194" s="3">
-        <v>44712</v>
+        <v>44710</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>561</v>
+        <v>580</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>562</v>
+        <v>581</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>563</v>
+        <v>582</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>285</v>
+        <v>4</v>
       </c>
     </row>
     <row r="195" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B195" s="2"/>
       <c r="C195" s="3">
-        <v>44717</v>
+        <v>44712</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>662</v>
+        <v>561</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>663</v>
+        <v>562</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>664</v>
+        <v>563</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>4</v>
+        <v>285</v>
       </c>
     </row>
     <row r="196" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B196" s="2"/>
       <c r="C196" s="3">
-        <v>44724</v>
+        <v>44717</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>577</v>
+        <v>662</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>578</v>
+        <v>663</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>579</v>
+        <v>664</v>
       </c>
       <c r="G196" s="1" t="s">
         <v>4</v>
@@ -8492,69 +8517,70 @@
     <row r="197" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B197" s="2"/>
       <c r="C197" s="3">
+        <v>44724</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="E197" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="F197" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="G197" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="198" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B198" s="2"/>
+      <c r="C198" s="3">
         <v>44734</v>
       </c>
-      <c r="D197" s="1" t="s">
+      <c r="D198" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="E197" s="1" t="s">
+      <c r="E198" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="F197" s="2" t="s">
+      <c r="F198" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="G197" s="1" t="s">
+      <c r="G198" s="1" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="198" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C198" s="3">
+    <row r="199" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C199" s="3">
         <v>44736</v>
       </c>
-      <c r="D198" s="1" t="s">
+      <c r="D199" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E198" s="1" t="s">
+      <c r="E199" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F198" s="1" t="s">
+      <c r="F199" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G198" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="199" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B199" s="2" t="s">
+      <c r="G199" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="200" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B200" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="200" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C200" s="3">
-        <v>44753</v>
-      </c>
-      <c r="D200" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F200" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G200" s="1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="201" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C201" s="3">
-        <v>44756</v>
+        <v>44753</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="E201" s="1" t="s">
-        <v>379</v>
+        <v>25</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>380</v>
+        <v>26</v>
       </c>
       <c r="G201" s="1" t="s">
         <v>4</v>
@@ -8562,16 +8588,16 @@
     </row>
     <row r="202" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C202" s="3">
-        <v>44760</v>
+        <v>44756</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>125</v>
+        <v>378</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>126</v>
+        <v>379</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>127</v>
+        <v>380</v>
       </c>
       <c r="G202" s="1" t="s">
         <v>4</v>
@@ -8579,16 +8605,16 @@
     </row>
     <row r="203" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C203" s="3">
-        <v>44763</v>
+        <v>44760</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>614</v>
+        <v>125</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>615</v>
+        <v>126</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>616</v>
+        <v>127</v>
       </c>
       <c r="G203" s="1" t="s">
         <v>4</v>
@@ -8596,50 +8622,50 @@
     </row>
     <row r="204" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C204" s="3">
+        <v>44763</v>
+      </c>
+      <c r="D204" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="F204" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="G204" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="205" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C205" s="3">
         <v>44764</v>
       </c>
-      <c r="D204" s="1" t="s">
+      <c r="D205" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="E204" s="1" t="s">
+      <c r="E205" s="1" t="s">
         <v>612</v>
       </c>
-      <c r="F204" s="2" t="s">
+      <c r="F205" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="G204" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="205" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C205" s="9" t="s">
+      <c r="G205" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="206" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C206" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="D205" s="1" t="s">
+      <c r="D206" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E205" s="1" t="s">
+      <c r="E206" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F205" s="2" t="s">
+      <c r="F206" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="G205" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="206" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C206" s="9">
-        <v>44789</v>
-      </c>
-      <c r="D206" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="E206" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="F206" s="2" t="s">
-        <v>535</v>
       </c>
       <c r="G206" s="1" t="s">
         <v>4</v>
@@ -8647,16 +8673,16 @@
     </row>
     <row r="207" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C207" s="9">
-        <v>44796</v>
+        <v>44789</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>438</v>
+        <v>533</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>439</v>
+        <v>534</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>440</v>
+        <v>535</v>
       </c>
       <c r="G207" s="1" t="s">
         <v>4</v>
@@ -8664,16 +8690,16 @@
     </row>
     <row r="208" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C208" s="9">
-        <v>44798</v>
+        <v>44796</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>396</v>
+        <v>438</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>397</v>
+        <v>439</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>398</v>
+        <v>440</v>
       </c>
       <c r="G208" s="1" t="s">
         <v>4</v>
@@ -8681,67 +8707,67 @@
     </row>
     <row r="209" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C209" s="9">
+        <v>44798</v>
+      </c>
+      <c r="D209" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="F209" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="G209" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="210" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C210" s="9">
         <v>44799</v>
       </c>
-      <c r="D209" s="1" t="s">
+      <c r="D210" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="E209" s="1" t="s">
+      <c r="E210" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="F209" s="2" t="s">
+      <c r="F210" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="G209" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="210" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C210" s="3">
+      <c r="G210" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C211" s="3">
         <v>44783</v>
       </c>
-      <c r="D210" s="1" t="s">
+      <c r="D211" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E210" s="1" t="s">
+      <c r="E211" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F210" s="2" t="s">
+      <c r="F211" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="G210" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="211" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C211" s="3">
-        <v>44789</v>
-      </c>
-      <c r="D211" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E211" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F211" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="G211" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="212" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C212" s="3">
         <v>44789</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>117</v>
+        <v>48</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>118</v>
+        <v>49</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>119</v>
+        <v>50</v>
       </c>
       <c r="G212" s="1" t="s">
         <v>4</v>
@@ -8749,16 +8775,16 @@
     </row>
     <row r="213" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C213" s="3">
-        <v>44797</v>
+        <v>44789</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>408</v>
+        <v>117</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>409</v>
+        <v>118</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>410</v>
+        <v>119</v>
       </c>
       <c r="G213" s="1" t="s">
         <v>4</v>
@@ -8766,16 +8792,16 @@
     </row>
     <row r="214" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C214" s="3">
-        <v>44823</v>
+        <v>44797</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>363</v>
+        <v>408</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>364</v>
+        <v>409</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>365</v>
+        <v>410</v>
       </c>
       <c r="G214" s="1" t="s">
         <v>4</v>
@@ -8786,61 +8812,60 @@
         <v>44823</v>
       </c>
       <c r="D215" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="E215" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="F215" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="G215" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="216" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C216" s="3">
+        <v>44823</v>
+      </c>
+      <c r="D216" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="E215" s="1" t="s">
+      <c r="E216" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="F215" s="2" t="s">
+      <c r="F216" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="G215" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="216" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B216" s="2" t="s">
+      <c r="G216" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="217" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B217" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C216" s="3"/>
-      <c r="D216" s="2"/>
-      <c r="E216" s="2"/>
-      <c r="F216" s="2"/>
-    </row>
-    <row r="217" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B217" s="2"/>
+      <c r="C217" s="3"/>
+      <c r="D217" s="2"/>
+      <c r="E217" s="2"/>
+      <c r="F217" s="2"/>
     </row>
     <row r="218" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B218" s="2"/>
-      <c r="C218" s="3">
-        <v>44852</v>
-      </c>
-      <c r="D218" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="E218" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="F218" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="G218" s="1" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="219" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B219" s="2"/>
       <c r="C219" s="3">
-        <v>44856</v>
+        <v>44852</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="G219" s="1" t="s">
         <v>4</v>
@@ -8852,13 +8877,13 @@
         <v>44856</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>567</v>
+        <v>317</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>568</v>
+        <v>318</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>569</v>
+        <v>319</v>
       </c>
       <c r="G220" s="1" t="s">
         <v>4</v>
@@ -8867,16 +8892,16 @@
     <row r="221" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B221" s="2"/>
       <c r="C221" s="3">
-        <v>44858</v>
+        <v>44856</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>105</v>
+        <v>567</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>106</v>
+        <v>568</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>107</v>
+        <v>569</v>
       </c>
       <c r="G221" s="1" t="s">
         <v>4</v>
@@ -8885,16 +8910,16 @@
     <row r="222" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B222" s="2"/>
       <c r="C222" s="3">
-        <v>44859</v>
+        <v>44858</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G222" s="1" t="s">
         <v>4</v>
@@ -8903,16 +8928,16 @@
     <row r="223" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B223" s="2"/>
       <c r="C223" s="3">
-        <v>44862</v>
+        <v>44859</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E223" t="s">
-        <v>120</v>
+      <c r="E223" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="G223" s="1" t="s">
         <v>4</v>
@@ -8921,16 +8946,16 @@
     <row r="224" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B224" s="2"/>
       <c r="C224" s="3">
-        <v>44864</v>
+        <v>44862</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="E224" s="2" t="s">
-        <v>253</v>
+        <v>108</v>
+      </c>
+      <c r="E224" t="s">
+        <v>120</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>254</v>
+        <v>121</v>
       </c>
       <c r="G224" s="1" t="s">
         <v>4</v>
@@ -8939,16 +8964,16 @@
     <row r="225" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B225" s="2"/>
       <c r="C225" s="3">
-        <v>44866</v>
+        <v>44864</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>31</v>
+        <v>252</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>32</v>
+        <v>253</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G225" s="1" t="s">
         <v>4</v>
@@ -8960,13 +8985,13 @@
         <v>44866</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>149</v>
+        <v>31</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>150</v>
+        <v>32</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>151</v>
+        <v>255</v>
       </c>
       <c r="G226" s="1" t="s">
         <v>4</v>
@@ -8975,16 +9000,16 @@
     <row r="227" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B227" s="2"/>
       <c r="C227" s="3">
-        <v>44868</v>
-      </c>
-      <c r="D227" s="1" t="s">
-        <v>90</v>
+        <v>44866</v>
+      </c>
+      <c r="D227" s="2" t="s">
+        <v>149</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>91</v>
+        <v>150</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>92</v>
+        <v>151</v>
       </c>
       <c r="G227" s="1" t="s">
         <v>4</v>
@@ -8993,16 +9018,16 @@
     <row r="228" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B228" s="2"/>
       <c r="C228" s="3">
-        <v>44870</v>
+        <v>44868</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>375</v>
+        <v>90</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>376</v>
+        <v>91</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>377</v>
+        <v>92</v>
       </c>
       <c r="G228" s="1" t="s">
         <v>4</v>
@@ -9011,16 +9036,16 @@
     <row r="229" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B229" s="2"/>
       <c r="C229" s="3">
-        <v>44873</v>
+        <v>44870</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>505</v>
+        <v>375</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>506</v>
+        <v>376</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>507</v>
+        <v>377</v>
       </c>
       <c r="G229" s="1" t="s">
         <v>4</v>
@@ -9029,16 +9054,16 @@
     <row r="230" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B230" s="2"/>
       <c r="C230" s="3">
-        <v>44874</v>
-      </c>
-      <c r="D230" s="2" t="s">
-        <v>33</v>
+        <v>44873</v>
+      </c>
+      <c r="D230" s="1" t="s">
+        <v>505</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>34</v>
+        <v>506</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>256</v>
+        <v>507</v>
       </c>
       <c r="G230" s="1" t="s">
         <v>4</v>
@@ -9047,16 +9072,16 @@
     <row r="231" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B231" s="2"/>
       <c r="C231" s="3">
-        <v>44875</v>
+        <v>44874</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>94</v>
+        <v>34</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>95</v>
+        <v>256</v>
       </c>
       <c r="G231" s="1" t="s">
         <v>4</v>
@@ -9065,16 +9090,16 @@
     <row r="232" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B232" s="2"/>
       <c r="C232" s="3">
-        <v>44876</v>
+        <v>44875</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>305</v>
+        <v>93</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>306</v>
+        <v>94</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>307</v>
+        <v>95</v>
       </c>
       <c r="G232" s="1" t="s">
         <v>4</v>
@@ -9083,16 +9108,16 @@
     <row r="233" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B233" s="2"/>
       <c r="C233" s="3">
-        <v>44880</v>
+        <v>44876</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>327</v>
+        <v>305</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>328</v>
+        <v>306</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>329</v>
+        <v>307</v>
       </c>
       <c r="G233" s="1" t="s">
         <v>4</v>
@@ -9101,16 +9126,16 @@
     <row r="234" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B234" s="2"/>
       <c r="C234" s="3">
-        <v>44883</v>
+        <v>44880</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>152</v>
+        <v>327</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>153</v>
+        <v>328</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>154</v>
+        <v>329</v>
       </c>
       <c r="G234" s="1" t="s">
         <v>4</v>
@@ -9119,69 +9144,70 @@
     <row r="235" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B235" s="2"/>
       <c r="C235" s="3">
-        <v>44885</v>
+        <v>44883</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>320</v>
+        <v>152</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>321</v>
+        <v>153</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="G235" s="2" t="s">
-        <v>323</v>
+        <v>154</v>
+      </c>
+      <c r="G235" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="236" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B236" s="2"/>
       <c r="C236" s="3">
-        <v>44886</v>
+        <v>44885</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>189</v>
+        <v>320</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>190</v>
+        <v>321</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="G236" s="1" t="s">
-        <v>4</v>
+        <v>322</v>
+      </c>
+      <c r="G236" s="2" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="237" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B237" s="2"/>
       <c r="C237" s="3">
-        <v>44887</v>
+        <v>44886</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="G237" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="238" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B238" s="2"/>
       <c r="C238" s="3">
         <v>44887</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>411</v>
+        <v>192</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>412</v>
+        <v>193</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>413</v>
+        <v>194</v>
       </c>
       <c r="G238" s="1" t="s">
         <v>4</v>
@@ -9189,16 +9215,16 @@
     </row>
     <row r="239" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C239" s="3">
-        <v>44889</v>
+        <v>44887</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>28</v>
+        <v>411</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>27</v>
+        <v>412</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>167</v>
+        <v>413</v>
       </c>
       <c r="G239" s="1" t="s">
         <v>4</v>
@@ -9206,16 +9232,16 @@
     </row>
     <row r="240" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C240" s="3">
-        <v>44894</v>
+        <v>44889</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>473</v>
+        <v>28</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>474</v>
+        <v>27</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>475</v>
+        <v>167</v>
       </c>
       <c r="G240" s="1" t="s">
         <v>4</v>
@@ -9223,39 +9249,52 @@
     </row>
     <row r="241" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C241" s="3">
+        <v>44894</v>
+      </c>
+      <c r="D241" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="E241" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="F241" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="G241" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="242" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C242" s="3">
         <v>44906</v>
       </c>
-      <c r="D241" s="1" t="s">
+      <c r="D242" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E241" s="1" t="s">
+      <c r="E242" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="F241" s="2" t="s">
+      <c r="F242" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="G241" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="242" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="G242" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
     <row r="243" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="244" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="245" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="246" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B247" s="1"/>
-    </row>
+    <row r="247" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="248" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B248" s="1"/>
-      <c r="C248" s="3"/>
     </row>
     <row r="249" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B249" s="1"/>
+      <c r="C249" s="3"/>
     </row>
     <row r="250" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B250" s="1"/>
-      <c r="C250" s="3"/>
     </row>
     <row r="251" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B251" s="1"/>
@@ -9267,15 +9306,18 @@
     </row>
     <row r="253" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B253" s="1"/>
+      <c r="C253" s="3"/>
     </row>
     <row r="254" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B254" s="1"/>
-      <c r="C254" s="3"/>
     </row>
     <row r="255" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B255" s="1"/>
-    </row>
-    <row r="256" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="C255" s="3"/>
+    </row>
+    <row r="256" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B256" s="1"/>
+    </row>
     <row r="257" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="258" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="259" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9584,6 +9626,7 @@
     <row r="562" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="563" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="564" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Post GE14.xlsx
+++ b/Post GE14.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a960143ed076ae3/Desktop/Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1671" documentId="8_{186D12AC-41E3-418E-AADE-7BB523F94D2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42BF7BBF-F4D9-468B-AF29-5ED9970F8347}"/>
+  <xr:revisionPtr revIDLastSave="1685" documentId="8_{186D12AC-41E3-418E-AADE-7BB523F94D2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74788708-BDA9-4A75-B8E0-37842F7D905D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{41795AD5-B7F1-475B-99F5-B3B6FD9E37DE}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="685">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="691">
   <si>
     <t>PH gov trying to implement reforms while PAS and UMNO trying to plan things from behind the scene. Prosecute Najib and many corruption allegation from other politicians</t>
   </si>
@@ -4676,6 +4676,45 @@
 New youth limit to enhance their maturity level - Experts
 (https://www.nst.com.my/sports/others/2025/07/1243149/hannah-yeoh-youth-age-cap-30-take-effect-jan-1-next-year)
 Hannah Yeoh: Youth age cap of 30 to take effect Jan 1 next year </t>
+  </si>
+  <si>
+    <t>https://www.sinardaily.my/article/177878/focus/national/pm-is-warning-parties-trying-to-withdraw-support-for-govt---analyst</t>
+  </si>
+  <si>
+    <t>PM is warning parties trying to withdraw support for govt - Analyst</t>
+  </si>
+  <si>
+    <t>SHAH ALAM - The statement by Prime Minister Datuk Seri Ismail Sabri Yaakob that the 15th General Election (GE15) would be held at any time, is regarded as a warning to parties trying to threaten to withdraw their support for the government.
+Sociopolitical analyst Datuk M.Periasamy said Bersatu was trying to pressure Ismail Sabri to appoint a Deputy Prime Minister from the party and the Prime Minister did not apppoint a deputy, they will withdraw their support.
+"If it happens, it will reduce the support of the majority in Parliament and the Prime Minister will have no other choice but to dissolve Parliament.
+"It should be the opposition demanding for the dissolution of Parliament. But today, Bersatu, which is a component of the government, wants to withdraw their support. He has the right, but this is not mature democracy. "So when the Prime Minister said they are always ready, including to hold GE15 early, it is clearly a form of warning to those who are trying to threaten to withdraw support," he told Sinar Harian on Sunday.
+On Saturday, Ismail Sabri said the government under his leadership was always prepared to face any possibilities, including to hold GE15 sooner, should Perikatan Nasional (PN) wish to withdraw support for the government. Periasamy said he was of the view that Barisan Nasional (BN) and Umno were indeed prepared to face GE15.
+However, it was not what the people want right now. "This is because the government still needs to continue its efforts to restore the economy, giving aid and so on. There are many other things that needed to be resolved, so GE15 is not a priority right now," he said.
+Periasamy added that withdrawing support for the government when the country's economy was almost “drowning” reflected the immature democracy.
+He said the action will undermine the political stability in Malaysia in the eyes of investors and foreign countries.
+"Supporting and not supporting are characteristics of democracy. But a mature democracy means that we have to be patient and attentive to the people.
+"The government is trying to restore the economy which was affected due to the Covid-19 pandemic. In fact, the opposition also urged the Prime Minister to continue his administration (the PN government) for the sake of the country and the people.
+"All parties should support Ismail Sabri's efforts to manage the country which is also well received by majority of the people," he said.</t>
+  </si>
+  <si>
+    <t>https://malaysiagazette.com/2022/06/02/isu-noh-tak-ada-sampai-kena-pantau-azhari-shaari/</t>
+  </si>
+  <si>
+    <t>Isu Noh: Tak ada sampai kena pantau – Azhari Shaari</t>
+  </si>
+  <si>
+    <t>KUALA LUMPUR – Hubungan dalam kalangan pucuk pimpinan Badan Perhubungan UMNO Selangor masih harmoni, jauh sekali berantakan hanya kerana parti itu masih bekerjasama dengan Pas dalam Muafakat Nasional (MN).
+Ketua UMNO Bahagian Shah Alam, Datuk Azhari Shaari berkata, bukan sahaja hubungan baik masih terjalin bahkan UMNO Bahagian Shah Alam sendiri melakukan aktiviti secara bersama sehingga ke hari ini.
+“Tak ada sampai nak kena pantau, saya rasa tiadalah, ini banyak cerita-cerita orang luar yang nak memecahbelahkan UMNO Selangor.
+“Tiada pula (pantau dan kecil hati), kita jalan macam biasa sahaja, tapi Alhamdulillah kita (hubungan) masih utuh dengan Pengerusi dan Timbalan kita.
+“Perpaduan UMNO Selangor masih kukuh sehingga ke hari ini,” katanya kepada MalaysiaGazette, baru-baru ini.
+Beliau mengulas laporan sebuah portal 25 Mei lalu yang mendakwa tingkah laku Pengerusi Badan Perhubungan UMNO Selangor, Tan Sri Noh Omar di Selangor akhir-akhir ini kurang disenangi malah menyebabkan sesetengah pemimpin tertinggi parti itu berkecil hati.
+Menurut laporan itu, beberapa sumber dalaman UMNO terdekat dengan kepemimpinan negeri dan pusat mendakwa, Noh sedang dipantau kerana tidak disenangi selepas mengadakan perbincangan dengan parti lain di luar Barisan Nasional (BN).
+Lapor portal itu, menurut sumber yang dekat dengan Presiden UMNO, Datuk Seri Dr Ahmad Zahid Hamidi, Noh selaku Ahli Parlimen Tanjung Karang bertindak mengikut pertimbangan sendiri.
+Dalam pada itu, Azhari menyerahkan masa depan UMNO dan Pas dalam MN kepada pucuk pimpinan parti walaupun hubungan UMNO Selangor masih baik dengan Pas.
+“Setakat ini kita di peringkat Shah Alam hubungan kita masih baik, kukuh, majlis dia pun datang, majlis kami pun datang. Jadi masa depan kami ini kita serahkan kepada pucuk pimpinan parti.
+“Seperti mana Pengerusi Perhubungan telah katakan akhirnya nanti tertakluk kepada keputusan di pucuk pimpinan.
+“Sehingga ke hari ini, hubungan kami dengan pihak Pas di bawah MN masih okay lagi, kukuh malah kami masih bersama melaksanakan apa juga program,” katanya. – MalaysiaGazette</t>
   </si>
 </sst>
 </file>
@@ -5058,7 +5097,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C8237E3-DA57-49D7-B827-78ACC8405853}">
-  <dimension ref="A1:H565"/>
+  <dimension ref="A1:H567"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23.28515625" customWidth="1"/>
@@ -6556,16 +6595,16 @@
       <c r="A87" s="1"/>
       <c r="B87" s="2"/>
       <c r="C87" s="8">
-        <v>44060</v>
+        <v>44051</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>202</v>
+        <v>685</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>203</v>
+        <v>686</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>204</v>
+        <v>687</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>4</v>
@@ -6575,16 +6614,16 @@
       <c r="A88" s="1"/>
       <c r="B88" s="2"/>
       <c r="C88" s="8">
-        <v>44065</v>
+        <v>44060</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>429</v>
+        <v>202</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>430</v>
+        <v>203</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>431</v>
+        <v>204</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>4</v>
@@ -6594,16 +6633,16 @@
       <c r="A89" s="1"/>
       <c r="B89" s="2"/>
       <c r="C89" s="8">
-        <v>44069</v>
+        <v>44065</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>220</v>
+        <v>429</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>221</v>
+        <v>430</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>222</v>
+        <v>431</v>
       </c>
       <c r="G89" s="1" t="s">
         <v>4</v>
@@ -6613,95 +6652,95 @@
       <c r="A90" s="1"/>
       <c r="B90" s="2"/>
       <c r="C90" s="8">
-        <v>44072</v>
+        <v>44069</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="2"/>
       <c r="C91" s="8">
         <v>44072</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>340</v>
+        <v>208</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>341</v>
+        <v>209</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>342</v>
+        <v>210</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>343</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="2"/>
       <c r="C92" s="8">
-        <v>44076</v>
+        <v>44072</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>205</v>
+        <v>340</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>206</v>
+        <v>341</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>207</v>
+        <v>342</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>4</v>
+        <v>343</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="2"/>
-      <c r="C93" s="3">
-        <v>44078</v>
+      <c r="C93" s="8">
+        <v>44076</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>445</v>
+        <v>205</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>446</v>
+        <v>206</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>447</v>
+        <v>207</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>448</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="2"/>
       <c r="C94" s="3">
-        <v>44084</v>
+        <v>44078</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>143</v>
+        <v>445</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>144</v>
+        <v>446</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>145</v>
+        <v>447</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>4</v>
+        <v>448</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -6711,13 +6750,13 @@
         <v>44084</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>372</v>
+        <v>143</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>373</v>
+        <v>144</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>374</v>
+        <v>145</v>
       </c>
       <c r="G95" s="1" t="s">
         <v>4</v>
@@ -6726,17 +6765,17 @@
     <row r="96" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="2"/>
-      <c r="C96" s="8">
-        <v>44085</v>
+      <c r="C96" s="3">
+        <v>44084</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>213</v>
+        <v>372</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>373</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>212</v>
+        <v>374</v>
       </c>
       <c r="G96" s="1" t="s">
         <v>4</v>
@@ -6746,141 +6785,141 @@
       <c r="A97" s="1"/>
       <c r="B97" s="2"/>
       <c r="C97" s="8">
-        <v>44087</v>
+        <v>44085</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>223</v>
+        <v>4</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="2"/>
       <c r="C98" s="8">
-        <v>44090</v>
+        <v>44087</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>245</v>
+        <v>217</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>246</v>
+        <v>218</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>247</v>
+        <v>219</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>248</v>
+        <v>223</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="2"/>
       <c r="C99" s="8">
+        <v>44090</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="1"/>
+      <c r="B100" s="2"/>
+      <c r="C100" s="8">
         <v>44096</v>
       </c>
-      <c r="D99" s="1" t="s">
+      <c r="D100" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="E99" s="2" t="s">
+      <c r="E100" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="F99" s="2" t="s">
+      <c r="F100" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="G99" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A100" s="1"/>
-      <c r="B100" s="2" t="s">
+      <c r="G100" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A101" s="1"/>
+      <c r="B101" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F100" s="2"/>
-    </row>
-    <row r="101" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="1"/>
-      <c r="B101" s="2"/>
+      <c r="F101" s="2"/>
     </row>
     <row r="102" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="2"/>
-      <c r="C102" s="3">
-        <v>44089</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="G102" s="1" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="103" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="2"/>
       <c r="C103" s="3">
-        <v>44106</v>
+        <v>44089</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>545</v>
+        <v>521</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>546</v>
+        <v>522</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>547</v>
+        <v>523</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="2"/>
       <c r="C104" s="3">
-        <v>44115</v>
+        <v>44106</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>87</v>
+        <v>545</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>88</v>
+        <v>546</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>89</v>
+        <v>547</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>4</v>
+        <v>350</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="2"/>
       <c r="C105" s="3">
-        <v>44117</v>
+        <v>44115</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>435</v>
+        <v>87</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>436</v>
+        <v>88</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>437</v>
+        <v>89</v>
       </c>
       <c r="G105" s="1" t="s">
         <v>4</v>
@@ -6890,16 +6929,16 @@
       <c r="A106" s="1"/>
       <c r="B106" s="2"/>
       <c r="C106" s="3">
-        <v>44152</v>
+        <v>44117</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>75</v>
+        <v>435</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>76</v>
+        <v>436</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>77</v>
+        <v>437</v>
       </c>
       <c r="G106" s="1" t="s">
         <v>4</v>
@@ -6909,16 +6948,16 @@
       <c r="A107" s="1"/>
       <c r="B107" s="2"/>
       <c r="C107" s="3">
-        <v>44153</v>
+        <v>44152</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>414</v>
+        <v>75</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>415</v>
+        <v>76</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>416</v>
+        <v>77</v>
       </c>
       <c r="G107" s="1" t="s">
         <v>4</v>
@@ -6928,16 +6967,16 @@
       <c r="A108" s="1"/>
       <c r="B108" s="2"/>
       <c r="C108" s="3">
-        <v>44154</v>
+        <v>44153</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>168</v>
+        <v>414</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>169</v>
+        <v>415</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>170</v>
+        <v>416</v>
       </c>
       <c r="G108" s="1" t="s">
         <v>4</v>
@@ -6947,16 +6986,16 @@
       <c r="A109" s="1"/>
       <c r="B109" s="2"/>
       <c r="C109" s="3">
-        <v>44161</v>
+        <v>44154</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>551</v>
+        <v>168</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>552</v>
+        <v>169</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>553</v>
+        <v>170</v>
       </c>
       <c r="G109" s="1" t="s">
         <v>4</v>
@@ -6966,16 +7005,16 @@
       <c r="A110" s="1"/>
       <c r="B110" s="2"/>
       <c r="C110" s="3">
-        <v>44163</v>
+        <v>44161</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="G110" s="1" t="s">
         <v>4</v>
@@ -6985,16 +7024,16 @@
       <c r="A111" s="1"/>
       <c r="B111" s="2"/>
       <c r="C111" s="3">
-        <v>44168</v>
+        <v>44163</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>122</v>
+        <v>548</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>123</v>
+        <v>549</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>124</v>
+        <v>550</v>
       </c>
       <c r="G111" s="1" t="s">
         <v>4</v>
@@ -7004,35 +7043,35 @@
       <c r="A112" s="1"/>
       <c r="B112" s="2"/>
       <c r="C112" s="3">
-        <v>44172</v>
+        <v>44168</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>665</v>
+        <v>122</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>666</v>
+        <v>123</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>667</v>
+        <v>124</v>
       </c>
       <c r="G112" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="113" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="2"/>
       <c r="C113" s="3">
-        <v>44179</v>
+        <v>44172</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>333</v>
+        <v>665</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>334</v>
+        <v>666</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>335</v>
+        <v>667</v>
       </c>
       <c r="G113" s="1" t="s">
         <v>4</v>
@@ -7042,85 +7081,85 @@
       <c r="A114" s="1"/>
       <c r="B114" s="2"/>
       <c r="C114" s="3">
-        <v>44187</v>
+        <v>44179</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>67</v>
+        <v>333</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>68</v>
+        <v>334</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>69</v>
+        <v>335</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="2"/>
       <c r="C115" s="3">
+        <v>44187</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="1"/>
+      <c r="B116" s="2"/>
+      <c r="C116" s="3">
         <v>44189</v>
       </c>
-      <c r="D115" s="1" t="s">
+      <c r="D116" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="E115" s="1" t="s">
+      <c r="E116" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="F115" s="2" t="s">
+      <c r="F116" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="G115" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A116" s="1">
+      <c r="G116" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A117" s="1">
         <v>2021</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="B117" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="117" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="1"/>
-      <c r="B117" s="2"/>
     </row>
     <row r="118" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="2"/>
-      <c r="C118" s="3">
-        <v>44220</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="F118" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="G118" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="119" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="2"/>
       <c r="C119" s="3">
-        <v>44225</v>
+        <v>44220</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>296</v>
+        <v>461</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>297</v>
+        <v>462</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>298</v>
+        <v>463</v>
       </c>
       <c r="G119" s="1" t="s">
         <v>4</v>
@@ -7130,16 +7169,16 @@
       <c r="A120" s="1"/>
       <c r="B120" s="2"/>
       <c r="C120" s="3">
-        <v>44229</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E120" s="2" t="s">
-        <v>74</v>
+        <v>44225</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>297</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>22</v>
+        <v>298</v>
       </c>
       <c r="G120" s="1" t="s">
         <v>4</v>
@@ -7149,35 +7188,35 @@
       <c r="A121" s="1"/>
       <c r="B121" s="2"/>
       <c r="C121" s="3">
-        <v>44244</v>
+        <v>44229</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>180</v>
+        <v>21</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>181</v>
+        <v>74</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>182</v>
+        <v>22</v>
       </c>
       <c r="G121" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="122" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="2"/>
       <c r="C122" s="3">
-        <v>44247</v>
+        <v>44244</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G122" s="1" t="s">
         <v>4</v>
@@ -7187,182 +7226,182 @@
       <c r="A123" s="1"/>
       <c r="B123" s="2"/>
       <c r="C123" s="3">
-        <v>44248</v>
+        <v>44247</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>441</v>
+        <v>177</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>442</v>
+        <v>178</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>443</v>
+        <v>179</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>444</v>
+        <v>4</v>
       </c>
     </row>
     <row r="124" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="2"/>
       <c r="C124" s="3">
+        <v>44248</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="1"/>
+      <c r="B125" s="2"/>
+      <c r="C125" s="3">
         <v>44277</v>
       </c>
-      <c r="D124" s="2" t="s">
+      <c r="D125" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E124" s="2" t="s">
+      <c r="E125" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F124" s="2" t="s">
+      <c r="F125" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="G124" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="1"/>
-      <c r="B125" s="2" t="s">
+      <c r="G125" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="1"/>
+      <c r="B126" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C125" s="3">
+      <c r="C126" s="3">
         <v>44301</v>
       </c>
-      <c r="D125" s="1" t="s">
+      <c r="D126" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E125" s="1" t="s">
+      <c r="E126" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="F125" s="2" t="s">
+      <c r="F126" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="G125" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A126" s="1"/>
-      <c r="B126" s="2"/>
-      <c r="C126" s="3">
-        <v>44311</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F126" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="G126" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="127" spans="1:7" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="2"/>
       <c r="C127" s="3">
-        <v>44319</v>
+        <v>44311</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>140</v>
+        <v>12</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>141</v>
+        <v>13</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>142</v>
+        <v>4</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="B128" s="2"/>
       <c r="C128" s="3">
-        <v>44361</v>
+        <v>44319</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>632</v>
+        <v>139</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>633</v>
+        <v>140</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>634</v>
+        <v>141</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>4</v>
+        <v>142</v>
       </c>
     </row>
     <row r="129" spans="1:7" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="2"/>
       <c r="C129" s="3">
-        <v>44368</v>
+        <v>44361</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>308</v>
+        <v>632</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>309</v>
+        <v>633</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>310</v>
+        <v>634</v>
       </c>
       <c r="G129" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="B130" s="2"/>
       <c r="C130" s="3">
+        <v>44368</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A131" s="1"/>
+      <c r="B131" s="2"/>
+      <c r="C131" s="3">
         <v>44375</v>
       </c>
-      <c r="D130" s="1" t="s">
+      <c r="D131" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F130" s="2" t="s">
+      <c r="F131" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G130" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A131" s="1"/>
-      <c r="B131" s="2" t="s">
+      <c r="G131" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A132" s="1"/>
+      <c r="B132" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C131" s="3">
+      <c r="C132" s="3">
         <v>44390</v>
       </c>
-      <c r="D131" s="1" t="s">
+      <c r="D132" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F131" s="1" t="s">
+      <c r="F132" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="G131" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="1"/>
-      <c r="B132" s="2"/>
-      <c r="C132" s="3">
-        <v>44398</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="F132" s="2" t="s">
-        <v>454</v>
       </c>
       <c r="G132" s="1" t="s">
         <v>4</v>
@@ -7372,35 +7411,35 @@
       <c r="A133" s="1"/>
       <c r="B133" s="2"/>
       <c r="C133" s="3">
-        <v>44408</v>
+        <v>44398</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="G133" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="B134" s="2"/>
       <c r="C134" s="3">
-        <v>44411</v>
+        <v>44408</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>369</v>
+        <v>455</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>370</v>
+        <v>456</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>371</v>
+        <v>457</v>
       </c>
       <c r="G134" s="1" t="s">
         <v>4</v>
@@ -7413,32 +7452,32 @@
         <v>44411</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>476</v>
+        <v>369</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>477</v>
+        <v>370</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>478</v>
+        <v>371</v>
       </c>
       <c r="G135" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="136" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="B136" s="2"/>
       <c r="C136" s="3">
-        <v>44413</v>
+        <v>44411</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>78</v>
+        <v>476</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>79</v>
+        <v>477</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>80</v>
+        <v>478</v>
       </c>
       <c r="G136" s="1" t="s">
         <v>4</v>
@@ -7448,16 +7487,16 @@
       <c r="A137" s="1"/>
       <c r="B137" s="2"/>
       <c r="C137" s="3">
-        <v>44422</v>
+        <v>44413</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>650</v>
+        <v>78</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>651</v>
+        <v>79</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>652</v>
+        <v>80</v>
       </c>
       <c r="G137" s="1" t="s">
         <v>4</v>
@@ -7467,16 +7506,16 @@
       <c r="A138" s="1"/>
       <c r="B138" s="2"/>
       <c r="C138" s="3">
-        <v>44443</v>
+        <v>44422</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>487</v>
+        <v>650</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>488</v>
+        <v>651</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>489</v>
+        <v>652</v>
       </c>
       <c r="G138" s="1" t="s">
         <v>4</v>
@@ -7486,44 +7525,44 @@
       <c r="A139" s="1"/>
       <c r="B139" s="2"/>
       <c r="C139" s="3">
+        <v>44443</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="1"/>
+      <c r="B140" s="2"/>
+      <c r="C140" s="3">
         <v>44454</v>
       </c>
-      <c r="D139" s="1" t="s">
+      <c r="D140" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="E139" s="1" t="s">
+      <c r="E140" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="F139" s="2" t="s">
+      <c r="F140" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="G139" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="1"/>
-      <c r="B140" s="2" t="s">
-        <v>8</v>
+      <c r="G140" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="141" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
-      <c r="B141" s="2"/>
-      <c r="C141" s="3">
-        <v>44473</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="F141" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="G141" s="1" t="s">
-        <v>4</v>
+      <c r="B141" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="142" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7533,89 +7572,89 @@
         <v>44473</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="2"/>
       <c r="C143" s="3">
-        <v>44477</v>
+        <v>44473</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>81</v>
+        <v>227</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>82</v>
+        <v>228</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>83</v>
+        <v>229</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>4</v>
+        <v>230</v>
       </c>
     </row>
     <row r="144" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="2"/>
       <c r="C144" s="3">
-        <v>44488</v>
+        <v>44477</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>234</v>
+        <v>81</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>235</v>
+        <v>82</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>236</v>
+        <v>83</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>240</v>
+        <v>4</v>
       </c>
     </row>
     <row r="145" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="B145" s="2"/>
       <c r="C145" s="3">
-        <v>44497</v>
+        <v>44488</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>174</v>
+        <v>234</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>175</v>
+        <v>235</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>176</v>
+        <v>236</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>4</v>
+        <v>240</v>
       </c>
     </row>
     <row r="146" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="B146" s="2"/>
       <c r="C146" s="3">
-        <v>44501</v>
+        <v>44497</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>644</v>
+        <v>174</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>645</v>
+        <v>175</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>646</v>
+        <v>176</v>
       </c>
       <c r="G146" s="1" t="s">
         <v>4</v>
@@ -7625,16 +7664,16 @@
       <c r="A147" s="1"/>
       <c r="B147" s="2"/>
       <c r="C147" s="3">
-        <v>44509</v>
+        <v>44501</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>293</v>
+        <v>644</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>294</v>
+        <v>645</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>295</v>
+        <v>646</v>
       </c>
       <c r="G147" s="1" t="s">
         <v>4</v>
@@ -7644,54 +7683,54 @@
       <c r="A148" s="1"/>
       <c r="B148" s="2"/>
       <c r="C148" s="3">
-        <v>44510</v>
+        <v>44509</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>289</v>
+        <v>4</v>
       </c>
     </row>
     <row r="149" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="B149" s="2"/>
       <c r="C149" s="3">
-        <v>44515</v>
+        <v>44510</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>171</v>
+        <v>286</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>172</v>
+        <v>287</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>173</v>
+        <v>288</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>4</v>
+        <v>289</v>
       </c>
     </row>
     <row r="150" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="B150" s="2"/>
       <c r="C150" s="3">
-        <v>44518</v>
+        <v>44515</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>242</v>
+        <v>171</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>243</v>
+        <v>172</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>244</v>
+        <v>173</v>
       </c>
       <c r="G150" s="1" t="s">
         <v>4</v>
@@ -7701,54 +7740,54 @@
       <c r="A151" s="1"/>
       <c r="B151" s="2"/>
       <c r="C151" s="3">
-        <v>44519</v>
+        <v>44518</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>155</v>
+        <v>242</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>156</v>
+        <v>243</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>157</v>
+        <v>244</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>281</v>
+        <v>4</v>
       </c>
     </row>
     <row r="152" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="B152" s="2"/>
       <c r="C152" s="3">
-        <v>44524</v>
+        <v>44519</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>659</v>
+        <v>155</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>660</v>
+        <v>156</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>661</v>
+        <v>157</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>4</v>
+        <v>281</v>
       </c>
     </row>
     <row r="153" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="B153" s="2"/>
       <c r="C153" s="3">
-        <v>44525</v>
+        <v>44524</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>558</v>
+        <v>659</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>559</v>
+        <v>660</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>560</v>
+        <v>661</v>
       </c>
       <c r="G153" s="1" t="s">
         <v>4</v>
@@ -7758,16 +7797,16 @@
       <c r="A154" s="1"/>
       <c r="B154" s="2"/>
       <c r="C154" s="3">
-        <v>44527</v>
+        <v>44525</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>647</v>
+        <v>558</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>648</v>
+        <v>559</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>649</v>
+        <v>560</v>
       </c>
       <c r="G154" s="1" t="s">
         <v>4</v>
@@ -7777,16 +7816,16 @@
       <c r="A155" s="1"/>
       <c r="B155" s="2"/>
       <c r="C155" s="3">
-        <v>44529</v>
+        <v>44527</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>458</v>
+        <v>647</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>459</v>
+        <v>648</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>460</v>
+        <v>649</v>
       </c>
       <c r="G155" s="1" t="s">
         <v>4</v>
@@ -7796,54 +7835,54 @@
       <c r="A156" s="1"/>
       <c r="B156" s="2"/>
       <c r="C156" s="3">
-        <v>44532</v>
+        <v>44529</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>423</v>
+        <v>458</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>424</v>
+        <v>459</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>425</v>
+        <v>460</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>350</v>
+        <v>4</v>
       </c>
     </row>
     <row r="157" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="B157" s="2"/>
       <c r="C157" s="3">
-        <v>44543</v>
+        <v>44532</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>490</v>
+        <v>423</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>491</v>
+        <v>424</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>492</v>
+        <v>425</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>4</v>
+        <v>350</v>
       </c>
     </row>
     <row r="158" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="B158" s="2"/>
       <c r="C158" s="3">
-        <v>44550</v>
+        <v>44543</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>470</v>
+        <v>490</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>472</v>
+        <v>492</v>
       </c>
       <c r="G158" s="1" t="s">
         <v>4</v>
@@ -7853,84 +7892,84 @@
       <c r="A159" s="1"/>
       <c r="B159" s="2"/>
       <c r="C159" s="3">
+        <v>44550</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="F159" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="G159" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="1"/>
+      <c r="B160" s="2"/>
+      <c r="C160" s="3">
         <v>44557</v>
       </c>
-      <c r="D159" s="1" t="s">
+      <c r="D160" s="1" t="s">
         <v>620</v>
       </c>
-      <c r="E159" s="1" t="s">
+      <c r="E160" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="F159" s="2" t="s">
+      <c r="F160" s="2" t="s">
         <v>622</v>
       </c>
-      <c r="G159" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="1">
+      <c r="G160" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="1">
         <v>2022</v>
       </c>
     </row>
-    <row r="161" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="1"/>
-      <c r="B161" s="2" t="s">
+    <row r="162" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="1"/>
+      <c r="B162" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="162" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="1"/>
-      <c r="B162" s="2"/>
-      <c r="C162" s="3">
-        <v>44566</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>617</v>
-      </c>
-      <c r="E162" s="1" t="s">
-        <v>618</v>
-      </c>
-      <c r="F162" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="G162" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="B163" s="2"/>
       <c r="C163" s="3">
-        <v>44569</v>
+        <v>44566</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>464</v>
+        <v>617</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>465</v>
+        <v>618</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>466</v>
+        <v>619</v>
       </c>
       <c r="G163" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="164" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="B164" s="2"/>
       <c r="C164" s="3">
-        <v>44577</v>
+        <v>44569</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>29</v>
+        <v>464</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>511</v>
+        <v>465</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>30</v>
+        <v>466</v>
       </c>
       <c r="G164" s="1" t="s">
         <v>4</v>
@@ -7943,13 +7982,13 @@
         <v>44577</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>513</v>
+        <v>29</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>514</v>
+        <v>30</v>
       </c>
       <c r="G165" s="1" t="s">
         <v>4</v>
@@ -7959,16 +7998,16 @@
       <c r="A166" s="1"/>
       <c r="B166" s="2"/>
       <c r="C166" s="3">
-        <v>44582</v>
+        <v>44577</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="G166" s="1" t="s">
         <v>4</v>
@@ -7978,35 +8017,35 @@
       <c r="A167" s="1"/>
       <c r="B167" s="2"/>
       <c r="C167" s="3">
-        <v>44588</v>
+        <v>44582</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>542</v>
+        <v>515</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>543</v>
+        <v>516</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>544</v>
+        <v>517</v>
       </c>
       <c r="G167" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="168" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="B168" s="2"/>
       <c r="C168" s="3">
-        <v>44595</v>
+        <v>44588</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="E168" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="F168" s="5" t="s">
-        <v>160</v>
+        <v>542</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="F168" s="2" t="s">
+        <v>544</v>
       </c>
       <c r="G168" s="1" t="s">
         <v>4</v>
@@ -8016,16 +8055,16 @@
       <c r="A169" s="1"/>
       <c r="B169" s="2"/>
       <c r="C169" s="3">
-        <v>44605</v>
+        <v>44595</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E169" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G169" s="1" t="s">
         <v>4</v>
@@ -8035,19 +8074,19 @@
       <c r="A170" s="1"/>
       <c r="B170" s="2"/>
       <c r="C170" s="3">
-        <v>44623</v>
+        <v>44605</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>336</v>
+        <v>161</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>337</v>
+        <v>162</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>338</v>
+        <v>163</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>339</v>
+        <v>4</v>
       </c>
     </row>
     <row r="171" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8057,70 +8096,70 @@
         <v>44623</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>420</v>
+        <v>336</v>
       </c>
       <c r="E171" s="6" t="s">
-        <v>421</v>
+        <v>337</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>422</v>
+        <v>338</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>4</v>
+        <v>339</v>
       </c>
     </row>
     <row r="172" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="B172" s="2"/>
       <c r="C172" s="3">
-        <v>44634</v>
+        <v>44623</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>674</v>
+        <v>420</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>675</v>
+        <v>421</v>
       </c>
       <c r="F172" s="5" t="s">
-        <v>676</v>
+        <v>422</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>677</v>
+        <v>4</v>
       </c>
     </row>
     <row r="173" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="B173" s="2"/>
       <c r="C173" s="3">
-        <v>44635</v>
+        <v>44634</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>574</v>
+        <v>674</v>
       </c>
       <c r="E173" s="6" t="s">
-        <v>575</v>
+        <v>675</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>576</v>
+        <v>676</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="B174" s="2"/>
       <c r="C174" s="3">
         <v>44635</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E174" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F174" s="2" t="s">
-        <v>44</v>
+        <v>574</v>
+      </c>
+      <c r="E174" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="F174" s="5" t="s">
+        <v>576</v>
       </c>
       <c r="G174" s="1" t="s">
         <v>4</v>
@@ -8130,54 +8169,54 @@
       <c r="A175" s="1"/>
       <c r="B175" s="2"/>
       <c r="C175" s="3">
-        <v>44639</v>
+        <v>44635</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>282</v>
+        <v>42</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>283</v>
+        <v>43</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>284</v>
+        <v>44</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>285</v>
+        <v>4</v>
       </c>
     </row>
     <row r="176" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="B176" s="2"/>
       <c r="C176" s="3">
-        <v>44640</v>
+        <v>44639</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>302</v>
+        <v>282</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>304</v>
+        <v>284</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="B177" s="2"/>
       <c r="C177" s="3">
-        <v>44641</v>
+        <v>44640</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>39</v>
+        <v>302</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>40</v>
+        <v>303</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>41</v>
+        <v>304</v>
       </c>
       <c r="G177" s="1" t="s">
         <v>4</v>
@@ -8190,51 +8229,51 @@
         <v>44641</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>290</v>
+        <v>39</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>291</v>
+        <v>40</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>292</v>
+        <v>41</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>557</v>
+        <v>4</v>
       </c>
     </row>
     <row r="179" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="B179" s="2"/>
       <c r="C179" s="3">
-        <v>44642</v>
+        <v>44641</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>554</v>
+        <v>290</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>555</v>
+        <v>291</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>556</v>
+        <v>292</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>4</v>
+        <v>557</v>
       </c>
     </row>
     <row r="180" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="B180" s="2"/>
       <c r="C180" s="3">
-        <v>44645</v>
+        <v>44642</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E180" s="4" t="s">
-        <v>46</v>
+        <v>554</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>555</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>47</v>
+        <v>556</v>
       </c>
       <c r="G180" s="1" t="s">
         <v>4</v>
@@ -8244,58 +8283,59 @@
       <c r="A181" s="1"/>
       <c r="B181" s="2"/>
       <c r="C181" s="3">
+        <v>44645</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E181" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F181" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G181" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A182" s="1"/>
+      <c r="B182" s="2"/>
+      <c r="C182" s="3">
         <v>44651</v>
       </c>
-      <c r="D181" s="1" t="s">
+      <c r="D182" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="E181" s="4" t="s">
+      <c r="E182" s="4" t="s">
         <v>609</v>
       </c>
-      <c r="F181" s="2" t="s">
+      <c r="F182" s="2" t="s">
         <v>610</v>
       </c>
-      <c r="G181" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B182" s="2" t="s">
+      <c r="G182" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B183" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E182" s="3"/>
-    </row>
-    <row r="183" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B183" s="2"/>
-      <c r="C183" s="3">
-        <v>44666</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="E183" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="F183" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="G183" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="E183" s="3"/>
     </row>
     <row r="184" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B184" s="2"/>
       <c r="C184" s="3">
-        <v>44675</v>
+        <v>44666</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>399</v>
+        <v>263</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>400</v>
+        <v>264</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>401</v>
+        <v>265</v>
       </c>
       <c r="G184" s="1" t="s">
         <v>4</v>
@@ -8304,34 +8344,37 @@
     <row r="185" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B185" s="2"/>
       <c r="C185" s="3">
-        <v>44677</v>
+        <v>44675</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>135</v>
+        <v>399</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>136</v>
+        <v>400</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>137</v>
+        <v>401</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>138</v>
+        <v>4</v>
       </c>
     </row>
     <row r="186" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B186" s="2"/>
       <c r="C186" s="3">
-        <v>44682</v>
+        <v>44677</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F186" s="1" t="s">
-        <v>20</v>
+        <v>135</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F186" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>4</v>
+        <v>138</v>
       </c>
     </row>
     <row r="187" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -8340,13 +8383,10 @@
         <v>44682</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="E187" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="F187" s="2" t="s">
-        <v>226</v>
+        <v>19</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="G187" s="1" t="s">
         <v>4</v>
@@ -8355,16 +8395,16 @@
     <row r="188" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B188" s="2"/>
       <c r="C188" s="3">
-        <v>44692</v>
-      </c>
-      <c r="D188" t="s">
-        <v>249</v>
+        <v>44682</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>224</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>251</v>
+        <v>226</v>
       </c>
       <c r="G188" s="1" t="s">
         <v>4</v>
@@ -8376,13 +8416,13 @@
         <v>44692</v>
       </c>
       <c r="D189" t="s">
-        <v>583</v>
+        <v>249</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>584</v>
+        <v>250</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>585</v>
+        <v>251</v>
       </c>
       <c r="G189" s="1" t="s">
         <v>4</v>
@@ -8391,16 +8431,16 @@
     <row r="190" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B190" s="2"/>
       <c r="C190" s="3">
-        <v>44695</v>
+        <v>44692</v>
       </c>
       <c r="D190" t="s">
-        <v>257</v>
+        <v>583</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>258</v>
+        <v>584</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>259</v>
+        <v>585</v>
       </c>
       <c r="G190" s="1" t="s">
         <v>4</v>
@@ -8409,52 +8449,52 @@
     <row r="191" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B191" s="2"/>
       <c r="C191" s="3">
-        <v>44696</v>
-      </c>
-      <c r="D191" s="1" t="s">
-        <v>198</v>
+        <v>44695</v>
+      </c>
+      <c r="D191" t="s">
+        <v>257</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>199</v>
+        <v>258</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="G191" s="7" t="s">
-        <v>201</v>
+        <v>259</v>
+      </c>
+      <c r="G191" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="192" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B192" s="2"/>
       <c r="C192" s="3">
-        <v>44701</v>
+        <v>44696</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>564</v>
+        <v>198</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>565</v>
+        <v>199</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="G192" s="1" t="s">
-        <v>4</v>
+        <v>200</v>
+      </c>
+      <c r="G192" s="7" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="193" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B193" s="2"/>
       <c r="C193" s="3">
-        <v>44708</v>
+        <v>44701</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>510</v>
+        <v>564</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>509</v>
+        <v>565</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>508</v>
+        <v>566</v>
       </c>
       <c r="G193" s="1" t="s">
         <v>4</v>
@@ -8463,16 +8503,16 @@
     <row r="194" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B194" s="2"/>
       <c r="C194" s="3">
-        <v>44710</v>
+        <v>44708</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>580</v>
+        <v>510</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>581</v>
+        <v>509</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>582</v>
+        <v>508</v>
       </c>
       <c r="G194" s="1" t="s">
         <v>4</v>
@@ -8481,52 +8521,52 @@
     <row r="195" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B195" s="2"/>
       <c r="C195" s="3">
-        <v>44712</v>
+        <v>44710</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>561</v>
+        <v>580</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>562</v>
+        <v>581</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>563</v>
+        <v>582</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>285</v>
+        <v>4</v>
       </c>
     </row>
     <row r="196" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B196" s="2"/>
       <c r="C196" s="3">
-        <v>44717</v>
+        <v>44712</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>662</v>
+        <v>561</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>663</v>
+        <v>562</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>664</v>
+        <v>563</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>4</v>
+        <v>285</v>
       </c>
     </row>
     <row r="197" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B197" s="2"/>
       <c r="C197" s="3">
-        <v>44724</v>
+        <v>44714</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>577</v>
+        <v>688</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>578</v>
+        <v>689</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>579</v>
+        <v>690</v>
       </c>
       <c r="G197" s="1" t="s">
         <v>4</v>
@@ -8535,86 +8575,87 @@
     <row r="198" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B198" s="2"/>
       <c r="C198" s="3">
+        <v>44717</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="F198" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="G198" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="199" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C199" s="3">
+        <v>44724</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="E199" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="F199" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="G199" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="200" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B200" s="2"/>
+      <c r="C200" s="3">
         <v>44734</v>
       </c>
-      <c r="D198" s="1" t="s">
+      <c r="D200" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="E198" s="1" t="s">
+      <c r="E200" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="F198" s="2" t="s">
+      <c r="F200" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="G198" s="1" t="s">
+      <c r="G200" s="1" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="199" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C199" s="3">
+    <row r="201" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C201" s="3">
         <v>44736</v>
       </c>
-      <c r="D199" s="1" t="s">
+      <c r="D201" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E199" s="1" t="s">
+      <c r="E201" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F199" s="1" t="s">
+      <c r="F201" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G199" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="200" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B200" s="2" t="s">
+      <c r="G201" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="202" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B202" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="201" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C201" s="3">
-        <v>44753</v>
-      </c>
-      <c r="D201" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F201" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G201" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="202" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C202" s="3">
-        <v>44756</v>
-      </c>
-      <c r="D202" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="E202" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="F202" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="G202" s="1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="203" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C203" s="3">
-        <v>44760</v>
+        <v>44753</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E203" s="1" t="s">
-        <v>126</v>
+        <v>25</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>127</v>
+        <v>26</v>
       </c>
       <c r="G203" s="1" t="s">
         <v>4</v>
@@ -8622,16 +8663,16 @@
     </row>
     <row r="204" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C204" s="3">
-        <v>44763</v>
+        <v>44756</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>614</v>
+        <v>378</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>615</v>
+        <v>379</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>616</v>
+        <v>380</v>
       </c>
       <c r="G204" s="1" t="s">
         <v>4</v>
@@ -8639,67 +8680,67 @@
     </row>
     <row r="205" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C205" s="3">
+        <v>44760</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F205" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G205" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="206" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C206" s="3">
+        <v>44763</v>
+      </c>
+      <c r="D206" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="F206" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="G206" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="207" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C207" s="3">
         <v>44764</v>
       </c>
-      <c r="D205" s="1" t="s">
+      <c r="D207" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="E205" s="1" t="s">
+      <c r="E207" s="1" t="s">
         <v>612</v>
       </c>
-      <c r="F205" s="2" t="s">
+      <c r="F207" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="G205" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="206" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C206" s="9" t="s">
+      <c r="G207" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="208" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C208" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="D206" s="1" t="s">
+      <c r="D208" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E206" s="1" t="s">
+      <c r="E208" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F206" s="2" t="s">
+      <c r="F208" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="G206" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="207" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C207" s="9">
-        <v>44789</v>
-      </c>
-      <c r="D207" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="E207" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="F207" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="G207" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="208" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C208" s="9">
-        <v>44796</v>
-      </c>
-      <c r="D208" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="E208" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="F208" s="2" t="s">
-        <v>440</v>
       </c>
       <c r="G208" s="1" t="s">
         <v>4</v>
@@ -8707,16 +8748,16 @@
     </row>
     <row r="209" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C209" s="9">
-        <v>44798</v>
+        <v>44789</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>396</v>
+        <v>533</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>397</v>
+        <v>534</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>398</v>
+        <v>535</v>
       </c>
       <c r="G209" s="1" t="s">
         <v>4</v>
@@ -8724,84 +8765,84 @@
     </row>
     <row r="210" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C210" s="9">
+        <v>44796</v>
+      </c>
+      <c r="D210" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="F210" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G210" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C211" s="9">
+        <v>44798</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="F211" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="G211" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="212" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C212" s="9">
         <v>44799</v>
       </c>
-      <c r="D210" s="1" t="s">
+      <c r="D212" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="E210" s="1" t="s">
+      <c r="E212" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="F210" s="2" t="s">
+      <c r="F212" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="G210" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="211" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C211" s="3">
+      <c r="G212" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="213" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C213" s="3">
         <v>44783</v>
       </c>
-      <c r="D211" s="1" t="s">
+      <c r="D213" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E211" s="1" t="s">
+      <c r="E213" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F211" s="2" t="s">
+      <c r="F213" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="G211" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="212" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C212" s="3">
+      <c r="G213" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="214" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C214" s="3">
         <v>44789</v>
       </c>
-      <c r="D212" s="1" t="s">
+      <c r="D214" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E212" s="1" t="s">
+      <c r="E214" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F212" s="2" t="s">
+      <c r="F214" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="G212" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="213" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C213" s="3">
-        <v>44789</v>
-      </c>
-      <c r="D213" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="E213" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F213" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="G213" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="214" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C214" s="3">
-        <v>44797</v>
-      </c>
-      <c r="D214" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="E214" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="F214" s="2" t="s">
-        <v>410</v>
       </c>
       <c r="G214" s="1" t="s">
         <v>4</v>
@@ -8809,16 +8850,16 @@
     </row>
     <row r="215" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C215" s="3">
-        <v>44823</v>
+        <v>44789</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>363</v>
+        <v>117</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>364</v>
+        <v>118</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>365</v>
+        <v>119</v>
       </c>
       <c r="G215" s="1" t="s">
         <v>4</v>
@@ -8826,82 +8867,80 @@
     </row>
     <row r="216" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C216" s="3">
+        <v>44797</v>
+      </c>
+      <c r="D216" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="E216" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="F216" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="G216" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="217" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C217" s="3">
         <v>44823</v>
       </c>
-      <c r="D216" s="1" t="s">
+      <c r="D217" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="E217" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="F217" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="G217" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="218" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C218" s="3">
+        <v>44823</v>
+      </c>
+      <c r="D218" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="E216" s="1" t="s">
+      <c r="E218" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="F216" s="2" t="s">
+      <c r="F218" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="G216" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="217" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B217" s="2" t="s">
+      <c r="G218" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="219" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B219" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C217" s="3"/>
-      <c r="D217" s="2"/>
-      <c r="E217" s="2"/>
-      <c r="F217" s="2"/>
-    </row>
-    <row r="218" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B218" s="2"/>
-    </row>
-    <row r="219" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B219" s="2"/>
-      <c r="C219" s="3">
-        <v>44852</v>
-      </c>
-      <c r="D219" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="E219" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="F219" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="G219" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="C219" s="3"/>
+      <c r="D219" s="2"/>
+      <c r="E219" s="2"/>
+      <c r="F219" s="2"/>
     </row>
     <row r="220" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B220" s="2"/>
-      <c r="C220" s="3">
-        <v>44856</v>
-      </c>
-      <c r="D220" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="E220" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="F220" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="G220" s="1" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="221" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B221" s="2"/>
       <c r="C221" s="3">
-        <v>44856</v>
+        <v>44852</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>567</v>
+        <v>330</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>568</v>
+        <v>331</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>569</v>
+        <v>332</v>
       </c>
       <c r="G221" s="1" t="s">
         <v>4</v>
@@ -8910,16 +8949,16 @@
     <row r="222" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B222" s="2"/>
       <c r="C222" s="3">
-        <v>44858</v>
+        <v>44856</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>105</v>
+        <v>317</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>106</v>
+        <v>318</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>107</v>
+        <v>319</v>
       </c>
       <c r="G222" s="1" t="s">
         <v>4</v>
@@ -8928,16 +8967,16 @@
     <row r="223" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B223" s="2"/>
       <c r="C223" s="3">
-        <v>44859</v>
+        <v>44856</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>108</v>
+        <v>567</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>109</v>
+        <v>568</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>110</v>
+        <v>569</v>
       </c>
       <c r="G223" s="1" t="s">
         <v>4</v>
@@ -8946,16 +8985,16 @@
     <row r="224" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B224" s="2"/>
       <c r="C224" s="3">
-        <v>44862</v>
+        <v>44858</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E224" t="s">
-        <v>120</v>
+        <v>105</v>
+      </c>
+      <c r="E224" s="2" t="s">
+        <v>106</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="G224" s="1" t="s">
         <v>4</v>
@@ -8964,16 +9003,16 @@
     <row r="225" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B225" s="2"/>
       <c r="C225" s="3">
-        <v>44864</v>
+        <v>44859</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>252</v>
+        <v>108</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>253</v>
+        <v>109</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>254</v>
+        <v>110</v>
       </c>
       <c r="G225" s="1" t="s">
         <v>4</v>
@@ -8982,16 +9021,16 @@
     <row r="226" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B226" s="2"/>
       <c r="C226" s="3">
-        <v>44866</v>
+        <v>44862</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E226" s="2" t="s">
-        <v>32</v>
+        <v>108</v>
+      </c>
+      <c r="E226" t="s">
+        <v>120</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>255</v>
+        <v>121</v>
       </c>
       <c r="G226" s="1" t="s">
         <v>4</v>
@@ -9000,16 +9039,16 @@
     <row r="227" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B227" s="2"/>
       <c r="C227" s="3">
-        <v>44866</v>
+        <v>44864</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>149</v>
+        <v>252</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>150</v>
+        <v>253</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>151</v>
+        <v>254</v>
       </c>
       <c r="G227" s="1" t="s">
         <v>4</v>
@@ -9018,16 +9057,16 @@
     <row r="228" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B228" s="2"/>
       <c r="C228" s="3">
-        <v>44868</v>
-      </c>
-      <c r="D228" s="1" t="s">
-        <v>90</v>
+        <v>44866</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>91</v>
+        <v>32</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>92</v>
+        <v>255</v>
       </c>
       <c r="G228" s="1" t="s">
         <v>4</v>
@@ -9036,16 +9075,16 @@
     <row r="229" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B229" s="2"/>
       <c r="C229" s="3">
-        <v>44870</v>
-      </c>
-      <c r="D229" s="1" t="s">
-        <v>375</v>
+        <v>44866</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>149</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>376</v>
+        <v>150</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>377</v>
+        <v>151</v>
       </c>
       <c r="G229" s="1" t="s">
         <v>4</v>
@@ -9054,16 +9093,16 @@
     <row r="230" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B230" s="2"/>
       <c r="C230" s="3">
-        <v>44873</v>
+        <v>44868</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>505</v>
+        <v>90</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>506</v>
+        <v>91</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>507</v>
+        <v>92</v>
       </c>
       <c r="G230" s="1" t="s">
         <v>4</v>
@@ -9072,16 +9111,16 @@
     <row r="231" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B231" s="2"/>
       <c r="C231" s="3">
-        <v>44874</v>
-      </c>
-      <c r="D231" s="2" t="s">
-        <v>33</v>
+        <v>44870</v>
+      </c>
+      <c r="D231" s="1" t="s">
+        <v>375</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>34</v>
+        <v>376</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>256</v>
+        <v>377</v>
       </c>
       <c r="G231" s="1" t="s">
         <v>4</v>
@@ -9090,16 +9129,16 @@
     <row r="232" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B232" s="2"/>
       <c r="C232" s="3">
-        <v>44875</v>
-      </c>
-      <c r="D232" s="2" t="s">
-        <v>93</v>
+        <v>44873</v>
+      </c>
+      <c r="D232" s="1" t="s">
+        <v>505</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>94</v>
+        <v>506</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>95</v>
+        <v>507</v>
       </c>
       <c r="G232" s="1" t="s">
         <v>4</v>
@@ -9108,16 +9147,16 @@
     <row r="233" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B233" s="2"/>
       <c r="C233" s="3">
-        <v>44876</v>
+        <v>44874</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>305</v>
+        <v>33</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>306</v>
+        <v>34</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>307</v>
+        <v>256</v>
       </c>
       <c r="G233" s="1" t="s">
         <v>4</v>
@@ -9126,16 +9165,16 @@
     <row r="234" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B234" s="2"/>
       <c r="C234" s="3">
-        <v>44880</v>
+        <v>44875</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>327</v>
+        <v>93</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>328</v>
+        <v>94</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>329</v>
+        <v>95</v>
       </c>
       <c r="G234" s="1" t="s">
         <v>4</v>
@@ -9144,16 +9183,16 @@
     <row r="235" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B235" s="2"/>
       <c r="C235" s="3">
-        <v>44883</v>
+        <v>44876</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>152</v>
+        <v>305</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>153</v>
+        <v>306</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>154</v>
+        <v>307</v>
       </c>
       <c r="G235" s="1" t="s">
         <v>4</v>
@@ -9162,34 +9201,34 @@
     <row r="236" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B236" s="2"/>
       <c r="C236" s="3">
-        <v>44885</v>
+        <v>44880</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="G236" s="2" t="s">
-        <v>323</v>
+        <v>329</v>
+      </c>
+      <c r="G236" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="237" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B237" s="2"/>
       <c r="C237" s="3">
-        <v>44886</v>
+        <v>44883</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>190</v>
+        <v>153</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>191</v>
+        <v>154</v>
       </c>
       <c r="G237" s="1" t="s">
         <v>4</v>
@@ -9198,50 +9237,52 @@
     <row r="238" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B238" s="2"/>
       <c r="C238" s="3">
+        <v>44885</v>
+      </c>
+      <c r="D238" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="E238" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F238" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="G238" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="239" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B239" s="2"/>
+      <c r="C239" s="3">
+        <v>44886</v>
+      </c>
+      <c r="D239" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E239" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="F239" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="G239" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="240" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B240" s="2"/>
+      <c r="C240" s="3">
         <v>44887</v>
       </c>
-      <c r="D238" s="2" t="s">
+      <c r="D240" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="E238" s="2" t="s">
+      <c r="E240" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="F238" s="2" t="s">
+      <c r="F240" s="2" t="s">
         <v>194</v>
-      </c>
-      <c r="G238" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="239" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C239" s="3">
-        <v>44887</v>
-      </c>
-      <c r="D239" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="E239" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="F239" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="G239" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="240" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C240" s="3">
-        <v>44889</v>
-      </c>
-      <c r="D240" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E240" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F240" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="G240" s="1" t="s">
         <v>4</v>
@@ -9249,16 +9290,16 @@
     </row>
     <row r="241" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C241" s="3">
-        <v>44894</v>
+        <v>44887</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>473</v>
+        <v>411</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>474</v>
+        <v>412</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>475</v>
+        <v>413</v>
       </c>
       <c r="G241" s="1" t="s">
         <v>4</v>
@@ -9266,33 +9307,60 @@
     </row>
     <row r="242" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C242" s="3">
+        <v>44889</v>
+      </c>
+      <c r="D242" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E242" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F242" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="G242" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="243" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C243" s="3">
+        <v>44894</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="E243" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="F243" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="G243" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="244" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C244" s="3">
         <v>44906</v>
       </c>
-      <c r="D242" s="1" t="s">
+      <c r="D244" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E242" s="1" t="s">
+      <c r="E244" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="F242" s="2" t="s">
+      <c r="F244" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="G242" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="243" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="G244" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
     <row r="245" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="246" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="247" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B248" s="1"/>
-    </row>
-    <row r="249" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B249" s="1"/>
-      <c r="C249" s="3"/>
-    </row>
+    <row r="248" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="250" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B250" s="1"/>
     </row>
@@ -9302,7 +9370,6 @@
     </row>
     <row r="252" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B252" s="1"/>
-      <c r="C252" s="3"/>
     </row>
     <row r="253" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B253" s="1"/>
@@ -9310,6 +9377,7 @@
     </row>
     <row r="254" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B254" s="1"/>
+      <c r="C254" s="3"/>
     </row>
     <row r="255" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B255" s="1"/>
@@ -9318,22 +9386,27 @@
     <row r="256" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B256" s="1"/>
     </row>
-    <row r="257" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="272" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B257" s="1"/>
+      <c r="C257" s="3"/>
+    </row>
+    <row r="258" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B258" s="1"/>
+    </row>
+    <row r="259" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="273" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="274" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="275" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9627,6 +9700,8 @@
     <row r="563" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="564" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="565" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Post GE14.xlsx
+++ b/Post GE14.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a960143ed076ae3/Desktop/Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1685" documentId="8_{186D12AC-41E3-418E-AADE-7BB523F94D2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74788708-BDA9-4A75-B8E0-37842F7D905D}"/>
+  <xr:revisionPtr revIDLastSave="1710" documentId="8_{186D12AC-41E3-418E-AADE-7BB523F94D2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E2325D0-9422-49EA-B987-B32E41F08721}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{41795AD5-B7F1-475B-99F5-B3B6FD9E37DE}"/>
+    <workbookView xWindow="-28920" yWindow="1830" windowWidth="29040" windowHeight="15840" xr2:uid="{41795AD5-B7F1-475B-99F5-B3B6FD9E37DE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="691">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="703">
   <si>
     <t>PH gov trying to implement reforms while PAS and UMNO trying to plan things from behind the scene. Prosecute Najib and many corruption allegation from other politicians</t>
   </si>
@@ -4715,6 +4715,87 @@
 “Setakat ini kita di peringkat Shah Alam hubungan kita masih baik, kukuh, majlis dia pun datang, majlis kami pun datang. Jadi masa depan kami ini kita serahkan kepada pucuk pimpinan parti.
 “Seperti mana Pengerusi Perhubungan telah katakan akhirnya nanti tertakluk kepada keputusan di pucuk pimpinan.
 “Sehingga ke hari ini, hubungan kami dengan pihak Pas di bawah MN masih okay lagi, kukuh malah kami masih bersama melaksanakan apa juga program,” katanya. – MalaysiaGazette</t>
+  </si>
+  <si>
+    <t>https://harakahdaily.net/2021/08/aplikasi-baharu-bantu-pengguna-buat-pilihan-telco/</t>
+  </si>
+  <si>
+    <t>Aplikasi baharu bantu pengguna buat pilihan telco</t>
+  </si>
+  <si>
+    <t>PUTRAJAYA: Kerajaan akan melancarkan aplikasi Pemetaan Capaian Internet dalam masa terdekat sebagai panduan kepada pengguna untuk memilih syarikat telekomunikasi (telco) yang menyediakan perkhidmatan Internet terbaik.
+Menteri Komunikasi dan Multimedia Datuk Saifuddin Abdullah berkata aplikasi tersebut menjadi pemudah cara kepada pengguna untuk mendapatkan perkhidmatan berkualiti daripada syarikat telekomunikasi sedia ada di negara ini.
+Menurutnya, pembangunan aplikasi itu adalah hasil dapatan daripada mesyuarat berkala yang diadakan bersama telco yang sering membincangkan mengenai Pelan Jalinan Digital Negara (JENDELA).
+“Justeru, kita akan lancarkan aplikasi ‘Internet Mapping’ yang membolehkan pengguna mengenal pasti telco mana yang menyediakan perkhidmatan capaian Internet terbaik,” katanya pada sidang media selepas program Turun Padang Secara Maya bersama CyberSecurity Malaysia (CSM) hari ini.
+Program itu turut dihadiri lapan ketua jabatan di bawah CSM yang membentangkan laporan gerak kerja Program Pemerkasaan Keselamatan Siber (SiberKASA) sejak dilancarkan pada 23 Mac lepas. – BERNAMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">saifuddin policies
+(https://jendela.my/map/)
+</t>
+  </si>
+  <si>
+    <t>https://harakahdaily.net/2021/08/populisme-dan-jalan-keluar/</t>
+  </si>
+  <si>
+    <t>Populisme dan jalan keluar</t>
+  </si>
+  <si>
+    <t>Populisme adalah satu fahaman yang melonggarkan pemikiran daripada sebarang ikatan ideologi. Fahaman ini sedang subur diterap dalam suasana demokrasi hari ini. Kemunculan ini boleh dilihat melalui gambaran Deniell Bell pada 1960 yang menggambarkan bahawa masa depan politik dunia semakin kompleks, dan akhirnya ideologi yang didukungi itu menjadi sebagai satu bebanan.
+Lalu pada 1969, Ghita Ionescu dan Ernest Gellner menggambarkan bahawa dunia sedang terarah kepada Populisme. Pada 2016, Werner Muller turut menghuraikan ideologi ini secara realiti, apatah lagi Amerika ketika itu dimenangi oleh watak politikus populis, Donald Trump. Dr Moffitt pula menyatakan bahawa pimpinan Populisme biasanya berkelakuan buruk. 
+Secara umumnya, ia adalah kesan daripada kehanyutan dalam politik demokrasi. Iaitu melahirkan politikus yang tidak berpaksikan kepada satu ideologi yang solid, akan tetapi berlakon-lakon semata-mata untuk mengikut kehendak majoriti masyarakat, sekalipun melanggar ideologi pegangannya. 
+Gejala
+Politikus yang membawa penyakit Populisme lebih tertumpu kepada gimik dan berjanji luar daripada kemampuan kerana hanya inginkan sokongan, bukannya untuk laksanakan janjinya itu. Mereka gemar memainkan sentimen, atau emosi masyarakat agar ia dijadikan kayu ukur kebenaran. Kesannya, masyarakat akan hilang daya rasional, teralih ke arah emosi dalam bertindak.
+Dunia Islam juga tidak terhindar daripada wabak Populisme ini. Gerakan-gerakan Islam yang terlibat dalam dunia demokrasi antara yang terdedah dengan penyakit ini. Amilin gerakan Islam yang terjangkit wabak Populisme cenderung membawa sifat seperti menipu, membawa kepalsuan, memanipulasi harapan masyarakat dan sebagainya.
+Akibatnya, sikap pragmatik mula menjadi subur, dan menjadi normal. Pragmatik boleh difahami dengan ‘makan keliling’ dalam keadaan berubah-ubah watak. Kesannya memperlihatkan Gerakan Islam seolah-olah tidak bermoral, tidak konsisten dan hanya mengutamakan gimik. Akhirnya ia mengikis kepercayaan masyarakat terhadap usaha menegakkan Islam.
+Pertarungan Realisme
+Kita perlu sedar, situasi sekarang, kita sangat teruji, sama ada untuk terus mempertahankan prinsip, atau tercair dengan mainan Realisme. Realisme mengikut acuan Machiavelli (The Prince) tidak mengutamakan moral. Sebaliknya mengutamakan kuasa. Biar menipu pun, asal dapat kuasa.
+Dalam situasi politikus yang sedang terhanyut ini, Gerakan Islam perlu pertahankan prinsip, dan tidak tercair atau tidak larut dengan rentak Realisme ini. Ya, nak pertahankan prinsip di kala pertarungan hebat petarung-petarung Realisme bukanlah senang.
+Nabi S.A.W bersabda:
+‎يَأْتِى عَلَى النَّاسِ زَمَانٌ الصَّابِرُ فِيهِمْ عَلَى دِينِهِ كَالْقَابِضِ عَلَى الْجَمْرِ
+“Akan datang kepada manusia suatu zaman, orang yang berpegang teguh pada agamanya seperti orang yang menggenggam bara api.”
+Kita perlu sedar, kepercayaan umat adalah penting untuk mengketengahkan idea-idea Islam. Sekalipun idea itu menarik, tetapi apabila terhakisnya kepercayaan, umat akan melihat pejuang di medan demokrasi hanya sekadar ‘sembang gajah terbang’. Slogan dan laungan akan dihukum hipokrit oleh mereka.
+Di awal kehidupan Nabi S.A.W, Baginda digelar dengan ‘al-Amin’, yang boleh dipercayai. Karakter seperti ini perlu ada pada gerakan Islam. Watak ini juga tidak boleh dibuat-buat atau dilakonkan, sebaliknya ia adalah akhlak yang sudah tersebati.
+Jalan keluar
+Jiwa manusia sebenarnya bertentang dengan Realisme. Ia dianggap satu penipuan. Jiwa manusia inginkan kejujuran bukan lakonan dan inginkan kesungguhan bukan bermain-main. Biarlah petarung-petarung Realisme merebut piala mereka, kita jadilah kita!
+Kita perlu sedar bahawa untuk selamat di zaman penipuan yang disulam dengan Populisme adalah dengan kejujuran.
+Allah S.W.T berfirman:
+‎يَا أَيُّهَا الَّذِينَ آمَنُوا اتَّقُوا اللَّهَ وَكُونُوا مَعَ الصَّادِقِينَ
+“Wahai orang-orang yang beriman! Bertakwalah kamu kepada Allah, dan hendaklah kamu berada bersama-sama orang-orang yang jujur.”
+(at-Taubah: 119)
+Imam Ibn Kathir menafsirkan ayat ini dengan berkata:
+‎اصدقوا والزموا الصدق تكونوا مع أهله وتنجوا من المهالك ويجعل لكم فرجا من أموركم ، ومخرجا ،
+“Jujurlah, dan hendaklah konsisten dengan kejujuran, kamu pasti akan berada bersama orang yang jujur, kamu akan selamat daripada kemusnahan. Allah S.W.T akan berikan jalan penyelesaian bagi urusan kamu, dan jalan keluar.”
+Jadilah diri sendiri, pasti lebih membahagiakan. Tak perlu berlakon-lakon, kerana ia hanyalah menipu diri sendiri:
+‎فَلَوْ صَدَقُوا اللَّهَ لَكَانَ خَيْرًا لَهُمْ
+“Tetapi jikalau mereka berlaku jujur pada Allah, nescaya yang demikian itu lebih baik bagi mereka.”
+(Muhammad: 21)
+MUHAMMAD MUJAHID IR MOHAMMAD FADZIL – HARAKAHDAILY 13/8/2021</t>
+  </si>
+  <si>
+    <t>https://harakahdaily.net/2020/08/cabar-tulisan-jawi-dap-jangan-tunjuk-belang/</t>
+  </si>
+  <si>
+    <t>PARTI Islam Se-Malaysia (PAS) tegas menyatakan kekesalan atas tindakan ADUN Tras, Chow Yu Hui daripada DAP mencabar keputusan Kerajaan Negeri Pahang dalam mewajibkan tulisan Jawi di papan tanda dan iklan di premis perniagaan.
+Kenyataan ADUN Tras itu tidak berasas kerana penggunaan tulisan Jawi telah lama digunakan oleh rakyat Malaysia terutamanya di Kelantan dan Terengganu, bahkan tiada kita melihat isu tidak boleh membaca Jawi dibangkitkan.
+Tulisan Jawi bukan suatu perkara asing di dunia termasuk Malaysia kerana ia adalah tulisan yang telah digunapakai sejak tahun 1300 Masihi, bahkan sejarah turut mencatatkan, Pemasyhuran Kemerdekaan 1957 bagi negara Malaysia juga tertulis dalam abjad Jawi.
+Kerajaan Persekutuan juga telah mengisytiharkan Jumaat sebagai hari menyemarakkan tulisan Jawi. Bagi menyambut seruan tersebut, Harakah turut mengadakan semula kolum tulisan Jawi mulai Ogos 2020 ini.
+Bahkan, DAP juga perlu sedar bahawa selama ini logo Halal bagi barangan Malaysia turut menggunakan tulisan Jawi.
+PAS menyokong usaha Kerajaan Negeri Pahang dalam memperkasakan penggunaan tulisan Jawi, ia seharusnya diikuti kerajaan negeri lain sebagai tanda sokongan memartabatkan penggunaan tulisan Jawi.
+“Islam Memimpin Perpaduan”
+KAMARUZAMAN MOHAMAD
+Ketua Penerangan
+Parti Islam Se-Malaysia (PAS)
+3 Ogos 2020 | 12 Zulhijjah 1441 – HARAKAHDAILY 3/8/2020</t>
+  </si>
+  <si>
+    <t>Cabar tulisan Jawi: DAP jangan tunjuk belang</t>
+  </si>
+  <si>
+    <t>pas blame dap</t>
+  </si>
+  <si>
+    <t>jawi</t>
   </si>
 </sst>
 </file>
@@ -5097,7 +5178,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C8237E3-DA57-49D7-B827-78ACC8405853}">
-  <dimension ref="A1:H567"/>
+  <dimension ref="A1:I571"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23.28515625" customWidth="1"/>
@@ -5836,58 +5917,44 @@
       </c>
       <c r="F45" s="2"/>
     </row>
-    <row r="46" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="2"/>
-      <c r="C46" s="3">
-        <v>43835</v>
-      </c>
-      <c r="D46" t="s">
-        <v>467</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F46" s="2"/>
+    </row>
+    <row r="47" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="2"/>
       <c r="C47" s="3">
-        <v>43836</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>393</v>
+        <v>43835</v>
+      </c>
+      <c r="D47" t="s">
+        <v>467</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>394</v>
+        <v>468</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>395</v>
+        <v>469</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="2"/>
       <c r="C48" s="3">
-        <v>43837</v>
+        <v>43836</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>35</v>
+        <v>393</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>38</v>
+        <v>394</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>36</v>
+        <v>395</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>4</v>
@@ -5897,16 +5964,16 @@
       <c r="A49" s="1"/>
       <c r="B49" s="2"/>
       <c r="C49" s="3">
-        <v>43839</v>
+        <v>43837</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>432</v>
+        <v>35</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>433</v>
+        <v>38</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>434</v>
+        <v>36</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>4</v>
@@ -5916,16 +5983,16 @@
       <c r="A50" s="1"/>
       <c r="B50" s="2"/>
       <c r="C50" s="3">
-        <v>43843</v>
+        <v>43839</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>99</v>
+        <v>432</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>100</v>
+        <v>433</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>101</v>
+        <v>434</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>4</v>
@@ -5935,16 +6002,16 @@
       <c r="A51" s="1"/>
       <c r="B51" s="2"/>
       <c r="C51" s="3">
-        <v>43846</v>
+        <v>43843</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>4</v>
@@ -5954,54 +6021,54 @@
       <c r="A52" s="1"/>
       <c r="B52" s="2"/>
       <c r="C52" s="3">
-        <v>43852</v>
-      </c>
-      <c r="D52" t="s">
-        <v>502</v>
+        <v>43846</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>503</v>
+        <v>103</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>504</v>
+        <v>104</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>350</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="B53" s="2"/>
       <c r="C53" s="3">
-        <v>43860</v>
+        <v>43852</v>
       </c>
       <c r="D53" t="s">
-        <v>539</v>
+        <v>502</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>540</v>
+        <v>503</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>541</v>
+        <v>504</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>4</v>
+        <v>350</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="B54" s="2"/>
       <c r="C54" s="3">
-        <v>43863</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>405</v>
+        <v>43860</v>
+      </c>
+      <c r="D54" t="s">
+        <v>539</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>406</v>
+        <v>540</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>407</v>
+        <v>541</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>4</v>
@@ -6011,38 +6078,38 @@
       <c r="A55" s="1"/>
       <c r="B55" s="2"/>
       <c r="C55" s="3">
-        <v>43885</v>
+        <v>43863</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>266</v>
+        <v>405</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>267</v>
+        <v>406</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>269</v>
+        <v>407</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="B56" s="2"/>
       <c r="C56" s="3">
-        <v>43887</v>
+        <v>43885</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>381</v>
+        <v>266</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>383</v>
+        <v>267</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>4</v>
+        <v>268</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -6052,13 +6119,13 @@
         <v>43887</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>417</v>
+        <v>381</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>418</v>
+        <v>383</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>419</v>
+        <v>382</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>4</v>
@@ -6068,54 +6135,54 @@
       <c r="A58" s="1"/>
       <c r="B58" s="2"/>
       <c r="C58" s="3">
-        <v>43893</v>
+        <v>43887</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>231</v>
+        <v>417</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>232</v>
+        <v>418</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>233</v>
+        <v>419</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>241</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="B59" s="2"/>
       <c r="C59" s="3">
-        <v>43895</v>
+        <v>43893</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>493</v>
+        <v>231</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>494</v>
+        <v>232</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>495</v>
+        <v>233</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>4</v>
+        <v>241</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="B60" s="2"/>
       <c r="C60" s="3">
-        <v>43913</v>
+        <v>43895</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>96</v>
+        <v>493</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>97</v>
+        <v>494</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>98</v>
+        <v>495</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>4</v>
@@ -6125,16 +6192,16 @@
       <c r="A61" s="1"/>
       <c r="B61" s="2"/>
       <c r="C61" s="3">
-        <v>43916</v>
+        <v>43913</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>499</v>
+        <v>96</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>500</v>
+        <v>97</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>501</v>
+        <v>98</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>4</v>
@@ -6144,99 +6211,99 @@
       <c r="A62" s="1"/>
       <c r="B62" s="2"/>
       <c r="C62" s="3">
+        <v>43916</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="1"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="3">
         <v>43921</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="D63" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="E63" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="F62" s="2" t="s">
+      <c r="F63" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="G62" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="1"/>
-      <c r="B63" s="2" t="s">
+      <c r="G63" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="1"/>
+      <c r="B64" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F63" s="2"/>
-    </row>
-    <row r="64" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="1"/>
-      <c r="B64" s="2"/>
-      <c r="C64" s="3">
-        <v>43932</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="F64" s="2"/>
     </row>
     <row r="65" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="B65" s="2"/>
       <c r="C65" s="3">
-        <v>43950</v>
+        <v>43932</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>626</v>
+        <v>524</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>627</v>
+        <v>525</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>628</v>
+        <v>526</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="B66" s="2"/>
       <c r="C66" s="3">
-        <v>43964</v>
+        <v>43950</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>402</v>
+        <v>626</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>403</v>
+        <v>627</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>404</v>
+        <v>628</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>4</v>
+        <v>350</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="B67" s="2"/>
       <c r="C67" s="3">
-        <v>43968</v>
+        <v>43964</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>536</v>
+        <v>402</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>537</v>
+        <v>403</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>538</v>
+        <v>404</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>4</v>
@@ -6246,16 +6313,16 @@
       <c r="A68" s="1"/>
       <c r="B68" s="2"/>
       <c r="C68" s="3">
-        <v>43978</v>
+        <v>43968</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>4</v>
@@ -6265,16 +6332,16 @@
       <c r="A69" s="1"/>
       <c r="B69" s="2"/>
       <c r="C69" s="3">
-        <v>43981</v>
+        <v>43978</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>637</v>
+        <v>527</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>636</v>
+        <v>528</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>635</v>
+        <v>529</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>4</v>
@@ -6284,16 +6351,16 @@
       <c r="A70" s="1"/>
       <c r="B70" s="2"/>
       <c r="C70" s="3">
-        <v>43984</v>
+        <v>43981</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>351</v>
+        <v>637</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>352</v>
+        <v>636</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>353</v>
+        <v>635</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>4</v>
@@ -6303,73 +6370,73 @@
       <c r="A71" s="1"/>
       <c r="B71" s="2"/>
       <c r="C71" s="3">
-        <v>43986</v>
+        <v>43984</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="B72" s="2"/>
       <c r="C72" s="3">
-        <v>43993</v>
+        <v>43986</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>350</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="B73" s="2"/>
       <c r="C73" s="3">
-        <v>44007</v>
+        <v>43993</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>629</v>
+        <v>347</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>630</v>
+        <v>348</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>631</v>
+        <v>349</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>4</v>
+        <v>350</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="2"/>
       <c r="C74" s="3">
-        <v>44010</v>
+        <v>44007</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>596</v>
+        <v>629</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>597</v>
+        <v>630</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>598</v>
+        <v>631</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>4</v>
@@ -6379,16 +6446,16 @@
       <c r="A75" s="1"/>
       <c r="B75" s="2"/>
       <c r="C75" s="3">
-        <v>44012</v>
+        <v>44010</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>384</v>
+        <v>596</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>385</v>
+        <v>597</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>386</v>
+        <v>598</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>4</v>
@@ -6401,102 +6468,102 @@
         <v>44012</v>
       </c>
       <c r="D76" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="1"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="3">
+        <v>44012</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="E76" s="1" t="s">
+      <c r="E77" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="F76" s="2" t="s">
+      <c r="F77" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="G76" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="1"/>
-      <c r="B77" s="2" t="s">
+      <c r="G77" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="1"/>
+      <c r="B78" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F77" s="2"/>
-    </row>
-    <row r="78" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="1"/>
-      <c r="B78" s="2"/>
-      <c r="C78" s="3">
-        <v>44013</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>668</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>669</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F78" s="2"/>
+    </row>
+    <row r="79" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="2"/>
       <c r="C79" s="3">
-        <v>44015</v>
+        <v>44013</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>599</v>
+        <v>668</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>600</v>
+        <v>669</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>601</v>
+        <v>670</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="2"/>
       <c r="C80" s="3">
-        <v>44016</v>
+        <v>44015</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>214</v>
+        <v>599</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>215</v>
+        <v>600</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>216</v>
+        <v>601</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="B81" s="2"/>
       <c r="C81" s="3">
-        <v>44018</v>
+        <v>44016</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>641</v>
+        <v>214</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>642</v>
+        <v>215</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>643</v>
+        <v>216</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="B82" s="2"/>
       <c r="C82" s="3">
@@ -6515,286 +6582,292 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="B83" s="2"/>
       <c r="C83" s="3">
-        <v>44022</v>
+        <v>44018</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>479</v>
+        <v>641</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>480</v>
+        <v>642</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>481</v>
+        <v>643</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="2"/>
       <c r="C84" s="3">
-        <v>44025</v>
+        <v>44022</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>605</v>
+        <v>479</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>606</v>
+        <v>480</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>607</v>
+        <v>481</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="2"/>
       <c r="C85" s="3">
-        <v>44031</v>
+        <v>44025</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>357</v>
+        <v>605</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>358</v>
+        <v>606</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>359</v>
+        <v>607</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="2"/>
-      <c r="C86" s="8">
-        <v>44051</v>
+      <c r="C86" s="3">
+        <v>44031</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="2"/>
       <c r="C87" s="8">
-        <v>44051</v>
+        <v>44050</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>685</v>
+        <v>698</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>686</v>
+        <v>700</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>687</v>
+        <v>699</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="88" spans="1:7" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H87" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="2"/>
       <c r="C88" s="8">
-        <v>44060</v>
+        <v>44051</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>202</v>
+        <v>360</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>203</v>
+        <v>361</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>204</v>
+        <v>362</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="2"/>
       <c r="C89" s="8">
-        <v>44065</v>
+        <v>44051</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>429</v>
+        <v>685</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>430</v>
+        <v>686</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>431</v>
+        <v>687</v>
       </c>
       <c r="G89" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="2"/>
       <c r="C90" s="8">
-        <v>44069</v>
+        <v>44060</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="2"/>
       <c r="C91" s="8">
-        <v>44072</v>
+        <v>44065</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>208</v>
+        <v>429</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>209</v>
+        <v>430</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>210</v>
+        <v>431</v>
       </c>
       <c r="G91" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="2"/>
       <c r="C92" s="8">
-        <v>44072</v>
+        <v>44069</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>340</v>
+        <v>220</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>341</v>
+        <v>221</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>342</v>
+        <v>222</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="2"/>
       <c r="C93" s="8">
-        <v>44076</v>
+        <v>44072</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="G93" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="2"/>
-      <c r="C94" s="3">
-        <v>44078</v>
+      <c r="C94" s="8">
+        <v>44072</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>445</v>
+        <v>340</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>446</v>
+        <v>341</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>447</v>
+        <v>342</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="2"/>
-      <c r="C95" s="3">
-        <v>44084</v>
+      <c r="C95" s="8">
+        <v>44076</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>143</v>
+        <v>205</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>144</v>
+        <v>206</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>145</v>
+        <v>207</v>
       </c>
       <c r="G95" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="2"/>
       <c r="C96" s="3">
-        <v>44084</v>
+        <v>44078</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>372</v>
+        <v>445</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>373</v>
+        <v>446</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>374</v>
+        <v>447</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>4</v>
+        <v>448</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="2"/>
-      <c r="C97" s="8">
-        <v>44085</v>
+      <c r="C97" s="3">
+        <v>44084</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>213</v>
+        <v>143</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>212</v>
+        <v>145</v>
       </c>
       <c r="G97" s="1" t="s">
         <v>4</v>
@@ -6803,161 +6876,161 @@
     <row r="98" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="2"/>
-      <c r="C98" s="8">
-        <v>44087</v>
+      <c r="C98" s="3">
+        <v>44084</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>218</v>
+        <v>372</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>373</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>219</v>
+        <v>374</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>223</v>
+        <v>4</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="2"/>
       <c r="C99" s="8">
-        <v>44090</v>
+        <v>44085</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>245</v>
+        <v>211</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>247</v>
+        <v>212</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>248</v>
+        <v>4</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="2"/>
       <c r="C100" s="8">
-        <v>44096</v>
+        <v>44087</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>623</v>
+        <v>217</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>624</v>
+        <v>218</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>625</v>
+        <v>219</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
-      <c r="B101" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F101" s="2"/>
-    </row>
-    <row r="102" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B101" s="2"/>
+      <c r="C101" s="8">
+        <v>44090</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="2"/>
-    </row>
-    <row r="103" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C102" s="8">
+        <v>44096</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
-      <c r="B103" s="2"/>
-      <c r="C103" s="3">
-        <v>44089</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="F103" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="G103" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="B103" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F103" s="2"/>
     </row>
     <row r="104" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="2"/>
-      <c r="C104" s="3">
-        <v>44106</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="F104" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="G104" s="1" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="105" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="2"/>
       <c r="C105" s="3">
-        <v>44115</v>
+        <v>44089</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>87</v>
+        <v>521</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>88</v>
+        <v>522</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>89</v>
+        <v>523</v>
       </c>
       <c r="G105" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="2"/>
       <c r="C106" s="3">
-        <v>44117</v>
+        <v>44106</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>435</v>
+        <v>545</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>436</v>
+        <v>546</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>437</v>
+        <v>547</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>4</v>
+        <v>350</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="2"/>
       <c r="C107" s="3">
-        <v>44152</v>
+        <v>44115</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G107" s="1" t="s">
         <v>4</v>
@@ -6967,16 +7040,16 @@
       <c r="A108" s="1"/>
       <c r="B108" s="2"/>
       <c r="C108" s="3">
-        <v>44153</v>
+        <v>44117</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>414</v>
+        <v>435</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>416</v>
+        <v>437</v>
       </c>
       <c r="G108" s="1" t="s">
         <v>4</v>
@@ -6986,16 +7059,16 @@
       <c r="A109" s="1"/>
       <c r="B109" s="2"/>
       <c r="C109" s="3">
-        <v>44154</v>
+        <v>44152</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>168</v>
+        <v>75</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>169</v>
+        <v>76</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="G109" s="1" t="s">
         <v>4</v>
@@ -7005,16 +7078,16 @@
       <c r="A110" s="1"/>
       <c r="B110" s="2"/>
       <c r="C110" s="3">
-        <v>44161</v>
+        <v>44153</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>551</v>
+        <v>414</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>552</v>
+        <v>415</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>553</v>
+        <v>416</v>
       </c>
       <c r="G110" s="1" t="s">
         <v>4</v>
@@ -7024,16 +7097,16 @@
       <c r="A111" s="1"/>
       <c r="B111" s="2"/>
       <c r="C111" s="3">
-        <v>44163</v>
+        <v>44154</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>548</v>
+        <v>168</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>549</v>
+        <v>169</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>550</v>
+        <v>170</v>
       </c>
       <c r="G111" s="1" t="s">
         <v>4</v>
@@ -7043,16 +7116,16 @@
       <c r="A112" s="1"/>
       <c r="B112" s="2"/>
       <c r="C112" s="3">
-        <v>44168</v>
+        <v>44161</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>122</v>
+        <v>551</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>123</v>
+        <v>552</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>124</v>
+        <v>553</v>
       </c>
       <c r="G112" s="1" t="s">
         <v>4</v>
@@ -7062,142 +7135,142 @@
       <c r="A113" s="1"/>
       <c r="B113" s="2"/>
       <c r="C113" s="3">
-        <v>44172</v>
+        <v>44163</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>665</v>
+        <v>548</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>666</v>
+        <v>549</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>667</v>
+        <v>550</v>
       </c>
       <c r="G113" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="2"/>
       <c r="C114" s="3">
-        <v>44179</v>
+        <v>44168</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>333</v>
+        <v>122</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>334</v>
+        <v>123</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>335</v>
+        <v>124</v>
       </c>
       <c r="G114" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="2"/>
       <c r="C115" s="3">
-        <v>44187</v>
+        <v>44172</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>67</v>
+        <v>665</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>68</v>
+        <v>666</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>69</v>
+        <v>667</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="2"/>
       <c r="C116" s="3">
-        <v>44189</v>
+        <v>44179</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>586</v>
+        <v>333</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>588</v>
+        <v>334</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>587</v>
+        <v>335</v>
       </c>
       <c r="G116" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A117" s="1">
-        <v>2021</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="1"/>
+      <c r="B117" s="2"/>
+      <c r="C117" s="3">
+        <v>44187</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="2"/>
-    </row>
-    <row r="119" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="1"/>
-      <c r="B119" s="2"/>
-      <c r="C119" s="3">
-        <v>44220</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="F119" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="G119" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C118" s="3">
+        <v>44189</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A119" s="1">
+        <v>2021</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="2"/>
-      <c r="C120" s="3">
-        <v>44225</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="F120" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="G120" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="121" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="2"/>
       <c r="C121" s="3">
-        <v>44229</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>74</v>
+        <v>44220</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>462</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>22</v>
+        <v>463</v>
       </c>
       <c r="G121" s="1" t="s">
         <v>4</v>
@@ -7207,148 +7280,148 @@
       <c r="A122" s="1"/>
       <c r="B122" s="2"/>
       <c r="C122" s="3">
-        <v>44244</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="E122" s="2" t="s">
-        <v>181</v>
+        <v>44225</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>297</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>182</v>
+        <v>298</v>
       </c>
       <c r="G122" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="2"/>
       <c r="C123" s="3">
-        <v>44247</v>
+        <v>44229</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>177</v>
+        <v>21</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>178</v>
+        <v>74</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>179</v>
+        <v>22</v>
       </c>
       <c r="G123" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="124" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="2"/>
       <c r="C124" s="3">
-        <v>44248</v>
+        <v>44244</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>441</v>
+        <v>180</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>442</v>
+        <v>181</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>443</v>
+        <v>182</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>444</v>
+        <v>4</v>
       </c>
     </row>
     <row r="125" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="2"/>
       <c r="C125" s="3">
-        <v>44277</v>
+        <v>44247</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>71</v>
+        <v>177</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>72</v>
+        <v>178</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>73</v>
+        <v>179</v>
       </c>
       <c r="G125" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
-      <c r="B126" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="B126" s="2"/>
       <c r="C126" s="3">
-        <v>44301</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>187</v>
+        <v>44248</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>442</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>188</v>
+        <v>443</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="2"/>
       <c r="C127" s="3">
-        <v>44311</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>12</v>
+        <v>44277</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="G127" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
-      <c r="B128" s="2"/>
+      <c r="B128" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="C128" s="3">
-        <v>44319</v>
+        <v>44301</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>139</v>
+        <v>186</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>140</v>
+        <v>187</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>141</v>
+        <v>188</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="2"/>
       <c r="C129" s="3">
-        <v>44361</v>
+        <v>44311</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>633</v>
+        <v>12</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>634</v>
+        <v>13</v>
       </c>
       <c r="G129" s="1" t="s">
         <v>4</v>
@@ -7358,164 +7431,164 @@
       <c r="A130" s="1"/>
       <c r="B130" s="2"/>
       <c r="C130" s="3">
-        <v>44368</v>
+        <v>44319</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>308</v>
+        <v>139</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>309</v>
+        <v>140</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>310</v>
+        <v>141</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="B131" s="2"/>
       <c r="C131" s="3">
-        <v>44375</v>
+        <v>44361</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>3</v>
+        <v>632</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>633</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>5</v>
+        <v>634</v>
       </c>
       <c r="G131" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
-      <c r="B132" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="B132" s="2"/>
       <c r="C132" s="3">
-        <v>44390</v>
+        <v>44368</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F132" s="1" t="s">
-        <v>7</v>
+        <v>308</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>310</v>
       </c>
       <c r="G132" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133" s="2"/>
       <c r="C133" s="3">
-        <v>44398</v>
+        <v>44375</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>453</v>
+        <v>3</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>454</v>
+        <v>5</v>
       </c>
       <c r="G133" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
-      <c r="B134" s="2"/>
+      <c r="B134" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="C134" s="3">
-        <v>44408</v>
+        <v>44390</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="F134" s="2" t="s">
-        <v>457</v>
+        <v>6</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="G134" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="135" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="B135" s="2"/>
       <c r="C135" s="3">
-        <v>44411</v>
+        <v>44398</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>369</v>
+        <v>452</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>370</v>
+        <v>453</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>371</v>
+        <v>454</v>
       </c>
       <c r="G135" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="136" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="B136" s="2"/>
       <c r="C136" s="3">
-        <v>44411</v>
+        <v>44408</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>476</v>
+        <v>455</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>477</v>
+        <v>456</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>478</v>
+        <v>457</v>
       </c>
       <c r="G136" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="B137" s="2"/>
       <c r="C137" s="3">
-        <v>44413</v>
+        <v>44411</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>78</v>
+        <v>369</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>79</v>
+        <v>370</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>80</v>
+        <v>371</v>
       </c>
       <c r="G137" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="B138" s="2"/>
       <c r="C138" s="3">
-        <v>44422</v>
+        <v>44411</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>650</v>
+        <v>476</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>651</v>
+        <v>477</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>652</v>
+        <v>478</v>
       </c>
       <c r="G138" s="1" t="s">
         <v>4</v>
@@ -7525,16 +7598,16 @@
       <c r="A139" s="1"/>
       <c r="B139" s="2"/>
       <c r="C139" s="3">
-        <v>44443</v>
+        <v>44413</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>487</v>
+        <v>78</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>488</v>
+        <v>79</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>489</v>
+        <v>80</v>
       </c>
       <c r="G139" s="1" t="s">
         <v>4</v>
@@ -7544,155 +7617,153 @@
       <c r="A140" s="1"/>
       <c r="B140" s="2"/>
       <c r="C140" s="3">
-        <v>44454</v>
+        <v>44420</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>299</v>
+        <v>691</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>300</v>
+        <v>692</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="G140" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>693</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
-      <c r="B141" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B141" s="2"/>
+      <c r="C141" s="3"/>
+      <c r="D141" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="F141" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="B142" s="2"/>
       <c r="C142" s="3">
-        <v>44473</v>
+        <v>44422</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>237</v>
+        <v>650</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>238</v>
+        <v>651</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>239</v>
+        <v>652</v>
       </c>
       <c r="G142" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="2"/>
       <c r="C143" s="3">
-        <v>44473</v>
+        <v>44443</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>227</v>
+        <v>487</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>228</v>
+        <v>488</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>229</v>
+        <v>489</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="2"/>
       <c r="C144" s="3">
-        <v>44477</v>
+        <v>44454</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>81</v>
+        <v>299</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>82</v>
+        <v>300</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>83</v>
+        <v>301</v>
       </c>
       <c r="G144" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="145" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
-      <c r="B145" s="2"/>
-      <c r="C145" s="3">
-        <v>44488</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="E145" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="F145" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="G145" s="1" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B145" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="B146" s="2"/>
       <c r="C146" s="3">
-        <v>44497</v>
+        <v>44473</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>174</v>
+        <v>237</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>175</v>
+        <v>238</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>176</v>
+        <v>239</v>
       </c>
       <c r="G146" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="147" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="B147" s="2"/>
       <c r="C147" s="3">
-        <v>44501</v>
+        <v>44473</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>644</v>
+        <v>227</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>645</v>
+        <v>228</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>646</v>
+        <v>229</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>4</v>
+        <v>230</v>
       </c>
     </row>
     <row r="148" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="B148" s="2"/>
       <c r="C148" s="3">
-        <v>44509</v>
+        <v>44477</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>293</v>
+        <v>81</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>294</v>
+        <v>82</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>295</v>
+        <v>83</v>
       </c>
       <c r="G148" s="1" t="s">
         <v>4</v>
@@ -7702,35 +7773,35 @@
       <c r="A149" s="1"/>
       <c r="B149" s="2"/>
       <c r="C149" s="3">
-        <v>44510</v>
+        <v>44488</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>286</v>
+        <v>234</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>287</v>
+        <v>235</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>288</v>
+        <v>236</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>289</v>
+        <v>240</v>
       </c>
     </row>
     <row r="150" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="B150" s="2"/>
       <c r="C150" s="3">
-        <v>44515</v>
+        <v>44497</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G150" s="1" t="s">
         <v>4</v>
@@ -7740,16 +7811,16 @@
       <c r="A151" s="1"/>
       <c r="B151" s="2"/>
       <c r="C151" s="3">
-        <v>44518</v>
+        <v>44501</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>242</v>
+        <v>644</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>243</v>
+        <v>645</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>244</v>
+        <v>646</v>
       </c>
       <c r="G151" s="1" t="s">
         <v>4</v>
@@ -7759,54 +7830,54 @@
       <c r="A152" s="1"/>
       <c r="B152" s="2"/>
       <c r="C152" s="3">
-        <v>44519</v>
+        <v>44509</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>155</v>
+        <v>293</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>156</v>
+        <v>294</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>157</v>
+        <v>295</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>281</v>
+        <v>4</v>
       </c>
     </row>
     <row r="153" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="B153" s="2"/>
       <c r="C153" s="3">
-        <v>44524</v>
+        <v>44510</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>659</v>
+        <v>286</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>660</v>
+        <v>287</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>661</v>
+        <v>288</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>4</v>
+        <v>289</v>
       </c>
     </row>
     <row r="154" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="B154" s="2"/>
       <c r="C154" s="3">
-        <v>44525</v>
+        <v>44515</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>558</v>
+        <v>171</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>559</v>
+        <v>172</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>560</v>
+        <v>173</v>
       </c>
       <c r="G154" s="1" t="s">
         <v>4</v>
@@ -7816,16 +7887,16 @@
       <c r="A155" s="1"/>
       <c r="B155" s="2"/>
       <c r="C155" s="3">
-        <v>44527</v>
+        <v>44518</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>647</v>
+        <v>242</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>648</v>
+        <v>243</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>649</v>
+        <v>244</v>
       </c>
       <c r="G155" s="1" t="s">
         <v>4</v>
@@ -7835,54 +7906,54 @@
       <c r="A156" s="1"/>
       <c r="B156" s="2"/>
       <c r="C156" s="3">
-        <v>44529</v>
+        <v>44519</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>458</v>
+        <v>155</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>459</v>
+        <v>156</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>460</v>
+        <v>157</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>4</v>
+        <v>281</v>
       </c>
     </row>
     <row r="157" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="B157" s="2"/>
       <c r="C157" s="3">
-        <v>44532</v>
+        <v>44524</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>423</v>
+        <v>659</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>424</v>
+        <v>660</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>425</v>
+        <v>661</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>350</v>
+        <v>4</v>
       </c>
     </row>
     <row r="158" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="B158" s="2"/>
       <c r="C158" s="3">
-        <v>44543</v>
+        <v>44525</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>490</v>
+        <v>558</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>491</v>
+        <v>559</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>492</v>
+        <v>560</v>
       </c>
       <c r="G158" s="1" t="s">
         <v>4</v>
@@ -7892,16 +7963,16 @@
       <c r="A159" s="1"/>
       <c r="B159" s="2"/>
       <c r="C159" s="3">
-        <v>44550</v>
+        <v>44527</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>470</v>
+        <v>647</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>471</v>
+        <v>648</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>472</v>
+        <v>649</v>
       </c>
       <c r="G159" s="1" t="s">
         <v>4</v>
@@ -7911,46 +7982,73 @@
       <c r="A160" s="1"/>
       <c r="B160" s="2"/>
       <c r="C160" s="3">
-        <v>44557</v>
+        <v>44529</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>620</v>
+        <v>458</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>621</v>
+        <v>459</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>622</v>
+        <v>460</v>
       </c>
       <c r="G160" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="161" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="1">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="1"/>
+      <c r="B161" s="2"/>
+      <c r="C161" s="3">
+        <v>44532</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="F161" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="G161" s="1" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
-      <c r="B162" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B162" s="2"/>
+      <c r="C162" s="3">
+        <v>44543</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="F162" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="G162" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="B163" s="2"/>
       <c r="C163" s="3">
-        <v>44566</v>
+        <v>44550</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>617</v>
+        <v>470</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>618</v>
+        <v>471</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>619</v>
+        <v>472</v>
       </c>
       <c r="G163" s="1" t="s">
         <v>4</v>
@@ -7960,168 +8058,141 @@
       <c r="A164" s="1"/>
       <c r="B164" s="2"/>
       <c r="C164" s="3">
-        <v>44569</v>
+        <v>44557</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>464</v>
+        <v>620</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>465</v>
+        <v>621</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>466</v>
+        <v>622</v>
       </c>
       <c r="G164" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="165" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="1"/>
-      <c r="B165" s="2"/>
-      <c r="C165" s="3">
-        <v>44577</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E165" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="F165" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G165" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="1">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
-      <c r="B166" s="2"/>
-      <c r="C166" s="3">
-        <v>44577</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="E166" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="F166" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="G166" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B166" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="B167" s="2"/>
       <c r="C167" s="3">
-        <v>44582</v>
+        <v>44566</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>515</v>
+        <v>617</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>516</v>
+        <v>618</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>517</v>
+        <v>619</v>
       </c>
       <c r="G167" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="168" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="B168" s="2"/>
       <c r="C168" s="3">
-        <v>44588</v>
+        <v>44569</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>542</v>
+        <v>464</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>543</v>
+        <v>465</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>544</v>
+        <v>466</v>
       </c>
       <c r="G168" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="169" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="B169" s="2"/>
       <c r="C169" s="3">
-        <v>44595</v>
+        <v>44577</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="E169" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="F169" s="5" t="s">
-        <v>160</v>
+        <v>29</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="F169" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="G169" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="170" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="B170" s="2"/>
       <c r="C170" s="3">
-        <v>44605</v>
+        <v>44577</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="E170" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="F170" s="5" t="s">
-        <v>163</v>
+        <v>513</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="F170" s="2" t="s">
+        <v>514</v>
       </c>
       <c r="G170" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="171" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="B171" s="2"/>
       <c r="C171" s="3">
-        <v>44623</v>
+        <v>44582</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="E171" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="F171" s="5" t="s">
-        <v>338</v>
+        <v>515</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="F171" s="2" t="s">
+        <v>517</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="B172" s="2"/>
       <c r="C172" s="3">
-        <v>44623</v>
+        <v>44588</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="E172" s="6" t="s">
-        <v>421</v>
-      </c>
-      <c r="F172" s="5" t="s">
-        <v>422</v>
+        <v>542</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="F172" s="2" t="s">
+        <v>544</v>
       </c>
       <c r="G172" s="1" t="s">
         <v>4</v>
@@ -8131,168 +8202,168 @@
       <c r="A173" s="1"/>
       <c r="B173" s="2"/>
       <c r="C173" s="3">
-        <v>44634</v>
+        <v>44595</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>674</v>
+        <v>158</v>
       </c>
       <c r="E173" s="6" t="s">
-        <v>675</v>
+        <v>159</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>676</v>
+        <v>160</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>677</v>
+        <v>4</v>
       </c>
     </row>
     <row r="174" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="B174" s="2"/>
       <c r="C174" s="3">
-        <v>44635</v>
+        <v>44605</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>574</v>
+        <v>161</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>575</v>
+        <v>162</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>576</v>
+        <v>163</v>
       </c>
       <c r="G174" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="175" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="B175" s="2"/>
       <c r="C175" s="3">
-        <v>44635</v>
+        <v>44623</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E175" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F175" s="2" t="s">
-        <v>44</v>
+        <v>336</v>
+      </c>
+      <c r="E175" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="F175" s="5" t="s">
+        <v>338</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="B176" s="2"/>
       <c r="C176" s="3">
-        <v>44639</v>
+        <v>44623</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="E176" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="F176" s="2" t="s">
-        <v>284</v>
+        <v>420</v>
+      </c>
+      <c r="E176" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="F176" s="5" t="s">
+        <v>422</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="B177" s="2"/>
       <c r="C177" s="3">
-        <v>44640</v>
+        <v>44634</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="E177" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="F177" s="2" t="s">
-        <v>304</v>
+        <v>674</v>
+      </c>
+      <c r="E177" s="6" t="s">
+        <v>675</v>
+      </c>
+      <c r="F177" s="5" t="s">
+        <v>676</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="B178" s="2"/>
       <c r="C178" s="3">
-        <v>44641</v>
+        <v>44635</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E178" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F178" s="2" t="s">
-        <v>41</v>
+        <v>574</v>
+      </c>
+      <c r="E178" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="F178" s="5" t="s">
+        <v>576</v>
       </c>
       <c r="G178" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="179" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="B179" s="2"/>
       <c r="C179" s="3">
-        <v>44641</v>
+        <v>44635</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>290</v>
+        <v>42</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>291</v>
+        <v>43</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>292</v>
+        <v>44</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="B180" s="2"/>
       <c r="C180" s="3">
-        <v>44642</v>
+        <v>44639</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>554</v>
+        <v>282</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>555</v>
+        <v>283</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>556</v>
+        <v>284</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="B181" s="2"/>
       <c r="C181" s="3">
-        <v>44645</v>
+        <v>44640</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E181" s="4" t="s">
-        <v>46</v>
+        <v>302</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>303</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>47</v>
+        <v>304</v>
       </c>
       <c r="G181" s="1" t="s">
         <v>4</v>
@@ -8302,109 +8373,116 @@
       <c r="A182" s="1"/>
       <c r="B182" s="2"/>
       <c r="C182" s="3">
-        <v>44651</v>
+        <v>44641</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>608</v>
-      </c>
-      <c r="E182" s="4" t="s">
-        <v>609</v>
+        <v>39</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>610</v>
+        <v>41</v>
       </c>
       <c r="G182" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="183" spans="1:7" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B183" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E183" s="3"/>
-    </row>
-    <row r="184" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="1"/>
+      <c r="B183" s="2"/>
+      <c r="C183" s="3">
+        <v>44641</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="F183" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="G183" s="1" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A184" s="1"/>
       <c r="B184" s="2"/>
       <c r="C184" s="3">
-        <v>44666</v>
+        <v>44642</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>263</v>
+        <v>554</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>264</v>
+        <v>555</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>265</v>
+        <v>556</v>
       </c>
       <c r="G184" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="185" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A185" s="1"/>
       <c r="B185" s="2"/>
       <c r="C185" s="3">
-        <v>44675</v>
+        <v>44645</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="E185" s="1" t="s">
-        <v>400</v>
+        <v>45</v>
+      </c>
+      <c r="E185" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>401</v>
+        <v>47</v>
       </c>
       <c r="G185" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="186" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A186" s="1"/>
       <c r="B186" s="2"/>
       <c r="C186" s="3">
-        <v>44677</v>
+        <v>44651</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E186" s="1" t="s">
-        <v>136</v>
+        <v>608</v>
+      </c>
+      <c r="E186" s="4" t="s">
+        <v>609</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>137</v>
+        <v>610</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B187" s="2"/>
-      <c r="C187" s="3">
-        <v>44682</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F187" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G187" s="1" t="s">
-        <v>4</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B187" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E187" s="3"/>
     </row>
     <row r="188" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B188" s="2"/>
       <c r="C188" s="3">
-        <v>44682</v>
+        <v>44666</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>224</v>
+        <v>263</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>225</v>
+        <v>264</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>226</v>
+        <v>265</v>
       </c>
       <c r="G188" s="1" t="s">
         <v>4</v>
@@ -8413,16 +8491,16 @@
     <row r="189" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B189" s="2"/>
       <c r="C189" s="3">
-        <v>44692</v>
-      </c>
-      <c r="D189" t="s">
-        <v>249</v>
+        <v>44675</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>399</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>251</v>
+        <v>401</v>
       </c>
       <c r="G189" s="1" t="s">
         <v>4</v>
@@ -8431,34 +8509,31 @@
     <row r="190" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B190" s="2"/>
       <c r="C190" s="3">
-        <v>44692</v>
-      </c>
-      <c r="D190" t="s">
-        <v>583</v>
+        <v>44677</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>135</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>584</v>
+        <v>136</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>585</v>
+        <v>137</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>4</v>
+        <v>138</v>
       </c>
     </row>
     <row r="191" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B191" s="2"/>
       <c r="C191" s="3">
-        <v>44695</v>
-      </c>
-      <c r="D191" t="s">
-        <v>257</v>
-      </c>
-      <c r="E191" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="F191" s="2" t="s">
-        <v>259</v>
+        <v>44682</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F191" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="G191" s="1" t="s">
         <v>4</v>
@@ -8467,34 +8542,34 @@
     <row r="192" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B192" s="2"/>
       <c r="C192" s="3">
-        <v>44696</v>
+        <v>44682</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>199</v>
+        <v>225</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="G192" s="7" t="s">
-        <v>201</v>
+        <v>226</v>
+      </c>
+      <c r="G192" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="193" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B193" s="2"/>
       <c r="C193" s="3">
-        <v>44701</v>
-      </c>
-      <c r="D193" s="1" t="s">
-        <v>564</v>
+        <v>44692</v>
+      </c>
+      <c r="D193" t="s">
+        <v>249</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>565</v>
+        <v>250</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>566</v>
+        <v>251</v>
       </c>
       <c r="G193" s="1" t="s">
         <v>4</v>
@@ -8503,16 +8578,16 @@
     <row r="194" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B194" s="2"/>
       <c r="C194" s="3">
-        <v>44708</v>
-      </c>
-      <c r="D194" s="1" t="s">
-        <v>510</v>
+        <v>44692</v>
+      </c>
+      <c r="D194" t="s">
+        <v>583</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>509</v>
+        <v>584</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>508</v>
+        <v>585</v>
       </c>
       <c r="G194" s="1" t="s">
         <v>4</v>
@@ -8521,16 +8596,16 @@
     <row r="195" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B195" s="2"/>
       <c r="C195" s="3">
-        <v>44710</v>
-      </c>
-      <c r="D195" s="1" t="s">
-        <v>580</v>
+        <v>44695</v>
+      </c>
+      <c r="D195" t="s">
+        <v>257</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>581</v>
+        <v>258</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>582</v>
+        <v>259</v>
       </c>
       <c r="G195" s="1" t="s">
         <v>4</v>
@@ -8539,34 +8614,34 @@
     <row r="196" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B196" s="2"/>
       <c r="C196" s="3">
-        <v>44712</v>
+        <v>44696</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>561</v>
+        <v>198</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>562</v>
+        <v>199</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="G196" s="1" t="s">
-        <v>285</v>
+        <v>200</v>
+      </c>
+      <c r="G196" s="7" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="197" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B197" s="2"/>
       <c r="C197" s="3">
-        <v>44714</v>
+        <v>44701</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>688</v>
+        <v>564</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>689</v>
+        <v>565</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>690</v>
+        <v>566</v>
       </c>
       <c r="G197" s="1" t="s">
         <v>4</v>
@@ -8575,33 +8650,34 @@
     <row r="198" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B198" s="2"/>
       <c r="C198" s="3">
-        <v>44717</v>
+        <v>44708</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>662</v>
+        <v>510</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>663</v>
+        <v>509</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>664</v>
+        <v>508</v>
       </c>
       <c r="G198" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="199" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B199" s="2"/>
       <c r="C199" s="3">
-        <v>44724</v>
+        <v>44710</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="G199" s="1" t="s">
         <v>4</v>
@@ -8610,409 +8686,408 @@
     <row r="200" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B200" s="2"/>
       <c r="C200" s="3">
-        <v>44734</v>
+        <v>44712</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>653</v>
+        <v>561</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>654</v>
+        <v>562</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>655</v>
+        <v>563</v>
       </c>
       <c r="G200" s="1" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="201" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B201" s="2"/>
       <c r="C201" s="3">
-        <v>44736</v>
+        <v>44714</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>23</v>
+        <v>688</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F201" s="1" t="s">
-        <v>24</v>
+        <v>689</v>
+      </c>
+      <c r="F201" s="2" t="s">
+        <v>690</v>
       </c>
       <c r="G201" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="202" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B202" s="2" t="s">
-        <v>11</v>
+    <row r="202" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B202" s="2"/>
+      <c r="C202" s="3">
+        <v>44717</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="F202" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="G202" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="203" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C203" s="3">
-        <v>44753</v>
+        <v>44724</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>25</v>
+        <v>577</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>578</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>26</v>
+        <v>579</v>
       </c>
       <c r="G203" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="204" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B204" s="2"/>
       <c r="C204" s="3">
-        <v>44756</v>
+        <v>44734</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>378</v>
+        <v>653</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>379</v>
+        <v>654</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>380</v>
+        <v>655</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="205" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="205" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C205" s="3">
-        <v>44760</v>
+        <v>44736</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>125</v>
+        <v>23</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F205" s="2" t="s">
-        <v>127</v>
+        <v>24</v>
+      </c>
+      <c r="F205" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G205" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="206" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C206" s="3">
-        <v>44763</v>
-      </c>
-      <c r="D206" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="E206" s="1" t="s">
-        <v>615</v>
-      </c>
-      <c r="F206" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="G206" s="1" t="s">
-        <v>4</v>
+    <row r="206" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B206" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="207" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C207" s="3">
+        <v>44753</v>
+      </c>
+      <c r="D207" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F207" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G207" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="208" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C208" s="3">
+        <v>44756</v>
+      </c>
+      <c r="D208" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="E208" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="F208" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="G208" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="209" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C209" s="3">
+        <v>44760</v>
+      </c>
+      <c r="D209" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F209" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G209" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="210" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C210" s="3">
+        <v>44763</v>
+      </c>
+      <c r="D210" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="F210" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="G210" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C211" s="3">
         <v>44764</v>
       </c>
-      <c r="D207" s="1" t="s">
+      <c r="D211" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="E207" s="1" t="s">
+      <c r="E211" s="1" t="s">
         <v>612</v>
       </c>
-      <c r="F207" s="2" t="s">
+      <c r="F211" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="G207" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="208" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C208" s="9" t="s">
+      <c r="G211" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="212" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C212" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="D208" s="1" t="s">
+      <c r="D212" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E208" s="1" t="s">
+      <c r="E212" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F208" s="2" t="s">
+      <c r="F212" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="G208" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="209" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C209" s="9">
+      <c r="G212" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="213" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C213" s="9">
         <v>44789</v>
       </c>
-      <c r="D209" s="1" t="s">
+      <c r="D213" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="E209" s="1" t="s">
+      <c r="E213" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="F209" s="2" t="s">
+      <c r="F213" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="G209" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="210" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C210" s="9">
+      <c r="G213" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="214" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C214" s="9">
         <v>44796</v>
       </c>
-      <c r="D210" s="1" t="s">
+      <c r="D214" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="E210" s="1" t="s">
+      <c r="E214" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="F210" s="2" t="s">
+      <c r="F214" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="G210" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="211" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C211" s="9">
+      <c r="G214" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="215" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C215" s="9">
         <v>44798</v>
       </c>
-      <c r="D211" s="1" t="s">
+      <c r="D215" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="E211" s="1" t="s">
+      <c r="E215" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="F211" s="2" t="s">
+      <c r="F215" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="G211" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="212" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C212" s="9">
+      <c r="G215" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="216" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C216" s="9">
         <v>44799</v>
       </c>
-      <c r="D212" s="1" t="s">
+      <c r="D216" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="E212" s="1" t="s">
+      <c r="E216" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="F212" s="2" t="s">
+      <c r="F216" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="G212" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="213" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C213" s="3">
+      <c r="G216" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="217" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C217" s="3">
         <v>44783</v>
       </c>
-      <c r="D213" s="1" t="s">
+      <c r="D217" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E213" s="1" t="s">
+      <c r="E217" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F213" s="2" t="s">
+      <c r="F217" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="G213" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="214" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C214" s="3">
+      <c r="G217" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="218" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C218" s="3">
         <v>44789</v>
       </c>
-      <c r="D214" s="1" t="s">
+      <c r="D218" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E214" s="1" t="s">
+      <c r="E218" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F214" s="2" t="s">
+      <c r="F218" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G214" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="215" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C215" s="3">
+      <c r="G218" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="219" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C219" s="3">
         <v>44789</v>
       </c>
-      <c r="D215" s="1" t="s">
+      <c r="D219" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="E215" s="1" t="s">
+      <c r="E219" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F215" s="2" t="s">
+      <c r="F219" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="G215" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="216" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C216" s="3">
+      <c r="G219" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="220" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C220" s="3">
         <v>44797</v>
       </c>
-      <c r="D216" s="1" t="s">
+      <c r="D220" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="E216" s="1" t="s">
+      <c r="E220" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="F216" s="2" t="s">
+      <c r="F220" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="G216" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="217" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C217" s="3">
+      <c r="G220" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="221" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C221" s="3">
         <v>44823</v>
       </c>
-      <c r="D217" s="1" t="s">
+      <c r="D221" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="E217" s="1" t="s">
+      <c r="E221" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="F217" s="2" t="s">
+      <c r="F221" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="G217" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="218" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C218" s="3">
+      <c r="G221" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="222" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C222" s="3">
         <v>44823</v>
       </c>
-      <c r="D218" s="1" t="s">
+      <c r="D222" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="E218" s="1" t="s">
+      <c r="E222" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="F218" s="2" t="s">
+      <c r="F222" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="G218" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="219" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B219" s="2" t="s">
+      <c r="G222" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="223" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B223" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C219" s="3"/>
-      <c r="D219" s="2"/>
-      <c r="E219" s="2"/>
-      <c r="F219" s="2"/>
-    </row>
-    <row r="220" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B220" s="2"/>
-    </row>
-    <row r="221" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B221" s="2"/>
-      <c r="C221" s="3">
-        <v>44852</v>
-      </c>
-      <c r="D221" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="E221" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="F221" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="G221" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="222" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B222" s="2"/>
-      <c r="C222" s="3">
-        <v>44856</v>
-      </c>
-      <c r="D222" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="E222" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="F222" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="G222" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="223" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B223" s="2"/>
-      <c r="C223" s="3">
-        <v>44856</v>
-      </c>
-      <c r="D223" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="E223" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="F223" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="G223" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="C223" s="3"/>
+      <c r="D223" s="2"/>
+      <c r="E223" s="2"/>
+      <c r="F223" s="2"/>
     </row>
     <row r="224" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B224" s="2"/>
-      <c r="C224" s="3">
-        <v>44858</v>
-      </c>
-      <c r="D224" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E224" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="F224" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G224" s="1" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="225" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B225" s="2"/>
       <c r="C225" s="3">
-        <v>44859</v>
+        <v>44852</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>108</v>
+        <v>330</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>109</v>
+        <v>331</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>110</v>
+        <v>332</v>
       </c>
       <c r="G225" s="1" t="s">
         <v>4</v>
@@ -9021,16 +9096,16 @@
     <row r="226" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B226" s="2"/>
       <c r="C226" s="3">
-        <v>44862</v>
+        <v>44856</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E226" t="s">
-        <v>120</v>
+        <v>317</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>318</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>121</v>
+        <v>319</v>
       </c>
       <c r="G226" s="1" t="s">
         <v>4</v>
@@ -9039,16 +9114,16 @@
     <row r="227" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B227" s="2"/>
       <c r="C227" s="3">
-        <v>44864</v>
+        <v>44856</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>252</v>
+        <v>567</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>253</v>
+        <v>568</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>254</v>
+        <v>569</v>
       </c>
       <c r="G227" s="1" t="s">
         <v>4</v>
@@ -9057,16 +9132,16 @@
     <row r="228" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B228" s="2"/>
       <c r="C228" s="3">
-        <v>44866</v>
+        <v>44858</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>31</v>
+        <v>105</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>32</v>
+        <v>106</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>255</v>
+        <v>107</v>
       </c>
       <c r="G228" s="1" t="s">
         <v>4</v>
@@ -9075,16 +9150,16 @@
     <row r="229" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B229" s="2"/>
       <c r="C229" s="3">
-        <v>44866</v>
+        <v>44859</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>149</v>
+        <v>108</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>150</v>
+        <v>109</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="G229" s="1" t="s">
         <v>4</v>
@@ -9093,16 +9168,16 @@
     <row r="230" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B230" s="2"/>
       <c r="C230" s="3">
-        <v>44868</v>
-      </c>
-      <c r="D230" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E230" s="2" t="s">
-        <v>91</v>
+        <v>44862</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E230" t="s">
+        <v>120</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="G230" s="1" t="s">
         <v>4</v>
@@ -9111,16 +9186,16 @@
     <row r="231" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B231" s="2"/>
       <c r="C231" s="3">
-        <v>44870</v>
-      </c>
-      <c r="D231" s="1" t="s">
-        <v>375</v>
+        <v>44864</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>252</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>376</v>
+        <v>253</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>377</v>
+        <v>254</v>
       </c>
       <c r="G231" s="1" t="s">
         <v>4</v>
@@ -9129,16 +9204,16 @@
     <row r="232" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B232" s="2"/>
       <c r="C232" s="3">
-        <v>44873</v>
-      </c>
-      <c r="D232" s="1" t="s">
-        <v>505</v>
+        <v>44866</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>506</v>
+        <v>32</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>507</v>
+        <v>255</v>
       </c>
       <c r="G232" s="1" t="s">
         <v>4</v>
@@ -9147,16 +9222,16 @@
     <row r="233" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B233" s="2"/>
       <c r="C233" s="3">
-        <v>44874</v>
+        <v>44866</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>33</v>
+        <v>149</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>34</v>
+        <v>150</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>256</v>
+        <v>151</v>
       </c>
       <c r="G233" s="1" t="s">
         <v>4</v>
@@ -9165,16 +9240,16 @@
     <row r="234" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B234" s="2"/>
       <c r="C234" s="3">
-        <v>44875</v>
-      </c>
-      <c r="D234" s="2" t="s">
-        <v>93</v>
+        <v>44868</v>
+      </c>
+      <c r="D234" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G234" s="1" t="s">
         <v>4</v>
@@ -9183,16 +9258,16 @@
     <row r="235" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B235" s="2"/>
       <c r="C235" s="3">
-        <v>44876</v>
-      </c>
-      <c r="D235" s="2" t="s">
-        <v>305</v>
+        <v>44870</v>
+      </c>
+      <c r="D235" s="1" t="s">
+        <v>375</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>306</v>
+        <v>376</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>307</v>
+        <v>377</v>
       </c>
       <c r="G235" s="1" t="s">
         <v>4</v>
@@ -9201,16 +9276,16 @@
     <row r="236" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B236" s="2"/>
       <c r="C236" s="3">
-        <v>44880</v>
-      </c>
-      <c r="D236" s="2" t="s">
-        <v>327</v>
+        <v>44873</v>
+      </c>
+      <c r="D236" s="1" t="s">
+        <v>505</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>328</v>
+        <v>506</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>329</v>
+        <v>507</v>
       </c>
       <c r="G236" s="1" t="s">
         <v>4</v>
@@ -9219,16 +9294,16 @@
     <row r="237" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B237" s="2"/>
       <c r="C237" s="3">
-        <v>44883</v>
+        <v>44874</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>152</v>
+        <v>33</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>153</v>
+        <v>34</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>154</v>
+        <v>256</v>
       </c>
       <c r="G237" s="1" t="s">
         <v>4</v>
@@ -9237,34 +9312,34 @@
     <row r="238" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B238" s="2"/>
       <c r="C238" s="3">
-        <v>44885</v>
+        <v>44875</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>320</v>
+        <v>93</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>321</v>
+        <v>94</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="G238" s="2" t="s">
-        <v>323</v>
+        <v>95</v>
+      </c>
+      <c r="G238" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="239" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B239" s="2"/>
       <c r="C239" s="3">
-        <v>44886</v>
+        <v>44876</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>189</v>
+        <v>305</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>190</v>
+        <v>306</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>191</v>
+        <v>307</v>
       </c>
       <c r="G239" s="1" t="s">
         <v>4</v>
@@ -9273,111 +9348,168 @@
     <row r="240" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B240" s="2"/>
       <c r="C240" s="3">
+        <v>44880</v>
+      </c>
+      <c r="D240" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="E240" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="F240" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="G240" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="241" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B241" s="2"/>
+      <c r="C241" s="3">
+        <v>44883</v>
+      </c>
+      <c r="D241" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E241" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F241" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G241" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="242" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B242" s="2"/>
+      <c r="C242" s="3">
+        <v>44885</v>
+      </c>
+      <c r="D242" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="E242" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F242" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="G242" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="243" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B243" s="2"/>
+      <c r="C243" s="3">
+        <v>44886</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E243" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="F243" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="G243" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="244" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B244" s="2"/>
+      <c r="C244" s="3">
         <v>44887</v>
       </c>
-      <c r="D240" s="2" t="s">
+      <c r="D244" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="E240" s="2" t="s">
+      <c r="E244" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="F240" s="2" t="s">
+      <c r="F244" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="G240" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="241" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C241" s="3">
+      <c r="G244" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="245" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C245" s="3">
         <v>44887</v>
       </c>
-      <c r="D241" s="2" t="s">
+      <c r="D245" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="E241" s="2" t="s">
+      <c r="E245" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="F241" s="2" t="s">
+      <c r="F245" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="G241" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="242" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C242" s="3">
+      <c r="G245" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="246" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C246" s="3">
         <v>44889</v>
       </c>
-      <c r="D242" s="2" t="s">
+      <c r="D246" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E242" s="2" t="s">
+      <c r="E246" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F242" s="2" t="s">
+      <c r="F246" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="G242" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="243" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C243" s="3">
+      <c r="G246" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="247" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C247" s="3">
         <v>44894</v>
       </c>
-      <c r="D243" s="2" t="s">
+      <c r="D247" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="E243" s="2" t="s">
+      <c r="E247" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="F243" s="2" t="s">
+      <c r="F247" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="G243" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="244" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C244" s="3">
+      <c r="G247" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="248" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C248" s="3">
         <v>44906</v>
       </c>
-      <c r="D244" s="1" t="s">
+      <c r="D248" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E244" s="1" t="s">
+      <c r="E248" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="F244" s="2" t="s">
+      <c r="F248" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="G244" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="245" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="G248" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
     <row r="249" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B250" s="1"/>
-    </row>
-    <row r="251" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B251" s="1"/>
-      <c r="C251" s="3"/>
-    </row>
-    <row r="252" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B252" s="1"/>
-    </row>
-    <row r="253" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B253" s="1"/>
-      <c r="C253" s="3"/>
-    </row>
+    <row r="250" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="254" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B254" s="1"/>
-      <c r="C254" s="3"/>
     </row>
     <row r="255" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B255" s="1"/>
@@ -9392,11 +9524,22 @@
     </row>
     <row r="258" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B258" s="1"/>
-    </row>
-    <row r="259" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="C258" s="3"/>
+    </row>
+    <row r="259" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B259" s="1"/>
+      <c r="C259" s="3"/>
+    </row>
+    <row r="260" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B260" s="1"/>
+    </row>
+    <row r="261" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B261" s="1"/>
+      <c r="C261" s="3"/>
+    </row>
+    <row r="262" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B262" s="1"/>
+    </row>
     <row r="263" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="264" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="265" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9702,6 +9845,10 @@
     <row r="565" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="566" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="567" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Post GE14.xlsx
+++ b/Post GE14.xlsx
@@ -1,19 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a960143ed076ae3/Desktop/Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1710" documentId="8_{186D12AC-41E3-418E-AADE-7BB523F94D2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E2325D0-9422-49EA-B987-B32E41F08721}"/>
+  <xr:revisionPtr revIDLastSave="1833" documentId="8_{186D12AC-41E3-418E-AADE-7BB523F94D2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35A87490-1FB5-45FC-A7AC-06DE26CB4443}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1830" windowWidth="29040" windowHeight="15840" xr2:uid="{41795AD5-B7F1-475B-99F5-B3B6FD9E37DE}"/>
+    <workbookView xWindow="-28920" yWindow="1830" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{41795AD5-B7F1-475B-99F5-B3B6FD9E37DE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="pkr internal conflict" sheetId="5" r:id="rId2"/>
+    <sheet name="pkr election 2022" sheetId="6" r:id="rId3"/>
+    <sheet name="ismail sabri prime minister" sheetId="2" r:id="rId4"/>
+    <sheet name="2020 sabah election" sheetId="3" r:id="rId5"/>
+    <sheet name="muhyddin downfall" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="989" uniqueCount="737">
   <si>
     <t>PH gov trying to implement reforms while PAS and UMNO trying to plan things from behind the scene. Prosecute Najib and many corruption allegation from other politicians</t>
   </si>
@@ -4797,6 +4802,143 @@
   <si>
     <t>jawi</t>
   </si>
+  <si>
+    <t>Kisah Sebenar: Wan Ahmad Fayhsal &amp; Krisis Dalam Bersatu | THE ZAID IBRAHIM PODCAST</t>
+  </si>
+  <si>
+    <t>https://youtu.be/NVoXfMg1uIo?si=JSh9K4cHmQG8IGtd&amp;t=1484</t>
+  </si>
+  <si>
+    <t>Wan Wahysal said that after Ismail Sabri become the prime minister, there was a written agreement that the timbalan must be from Bersatu. Azmin didn’t get select so he was very salty. To the point of bringing it up issue to Hamzah and accusing him bringing him down.</t>
+  </si>
+  <si>
+    <t>https://youtu.be/NVoXfMg1uIo?si=WcEdh2YholVmvHCv&amp;t=1570</t>
+  </si>
+  <si>
+    <t>azmin ali fuck up in sabah somehow</t>
+  </si>
+  <si>
+    <t>https://youtu.be/NVoXfMg1uIo?si=4dhkHDdRc-DoCyh-&amp;t=1590</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Kisah Sebenar: Wan Ahmad Fayhsal &amp; Krisis Dalam Bersatu | THE ZAID IBRAHIM PODCAST </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muhyddin last minute attempt to intice PH </t>
+  </si>
+  <si>
+    <t>MESKIPUN telah memasuki tahun 2020, kes pegawai Jabatan Bomba dan Penyelamat, Allahyarham Adib yang terkorban dalam insiden rusuhan di Kuil Sri Maha Mariamman pada November 2018 yang lalu masih lagi tinggal tanda tanya.
+Sewajarnya pihak yang bertanggungjawab segera menyelesaikan siasatan dan memulakan prosiding mahkamah terhadap pesalah yang terlibat. Persoalannya, mengapa ia terus sepi sehingga ke hari ini seolah-olah tiada tindakan lanjut diambil bagi merungkai keadilan buat Allahyarham Adib?
+Tambahan pula, penyelesaian yang diharap terhadap kes ini nampaknya semakin tipis. Sebelum ini pihak Peguam Negara sendiri campur tangan dalam prosiding inkues tanpa sebab yang munasabah sehingga Hakim Mahkamah Koroner mengkritik tindakan Peguam Negara sebagai menyalahi prinsip perundangan.
+Apatah lagi dengan status kes Allahyarham Adib yang masih tergantung sehingga ke hari ini mengesahkan lagi kenyataan Hakim Mahkamah Koroner bahawa semua ini hanyalah permainan wayang pihak tertentu serta tidak menggambarkan keseriusan pihak bertanggungjawab mencari jalan keadilan buat saudara Adib.
+Saya menggesa pihak berkuasa agar segera menyelesaikan siasatan kes ini dan memulakan prosiding mahkamah secepat mungkin. Keadilan buat Allahyarham Adib perlu dijadikan keutamaan semua pihak hari ini.
+Apatah lagi, rakyat juga tertanya-tanya sejauh mana perkembangan kes Allahyarham Adib benar-benar dibawa ke muka pengadilan dan berapa lama lagi masa yang perlu diambil?
+Tambahan lagi, Peguam Negara tidak ada lagi kredibiliti untuk memegang jawatan itu khususnya melibatkan kes Allahyarham Adib disebabkan campur tangan beliau dalam prosiding serta keputusan Mahkamah Koroner sebelum ini. Sewajarnya beliau direhatkan dan diberikan kepada seseorang yang lebih layak untuk jawatan tersebut.
+“Islam Memimpin Perpaduan”
+YB SENATOR DATO’ HAJI HUSAIN AWANG
+Pesuruhjaya PAS Negeri Terengganu
+Ahli Dewan Negara – HARAKAHDAILY 23/1/2020</t>
+  </si>
+  <si>
+    <t>Mengapa pendakwaan kes arwah Adib masih sepi?</t>
+  </si>
+  <si>
+    <t>https://harakahdaily.net/2020/01/mengapa-pendakwaan-kes-arwah-adib-masih-sepi/</t>
+  </si>
+  <si>
+    <t>adib</t>
+  </si>
+  <si>
+    <t>uec</t>
+  </si>
+  <si>
+    <t>https://youtu.be/sTHk4KP8TEs?si=l7B0fMOM_jPDGzfT&amp;t=4725</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> EP179 | Amirudin Bakal Menteri Kabinet?, Perpecahan Dalaman PKR, Belanjawan 2026, Konsesi Parkir </t>
+  </si>
+  <si>
+    <t>Azmin tak nak official kan party congress, tian chua and amirudin kena pujuk dia baru dia pergi</t>
+  </si>
+  <si>
+    <t>https://www.freemalaysiatoday.com/category/bahasa/tempatan/2025/11/21/usah-ulang-lagi-bn-tak-pernah-kalah-pada-warisan-kata-bung</t>
+  </si>
+  <si>
+    <t>Usah ulang lagi, BN tak pernah kalah pada Warisan, kata Bung</t>
+  </si>
+  <si>
+    <t>KOTA KINABALU: Ketua Umno Sabah Bung Moktar Radin membidas Presiden Warisan Shafie Apdal yang terus mengitar semula dakwaan parti itu pernah menewaskan Barisan Nasional (BN) pada PRU 2018.
+Bung menegaskan naratif berkenaan adalah kisah yang diulang-ulang tanpa asas kerana BN ketika itu hanya kehilangan kuasa selepas beberapa Adun mengambil keputusan meninggalkan gabungan itu untuk menyertai Warisan.
+Selepas PRU 2018, BN membentuk kerajaan bersama Parti Solidariti Tanah Airku (STAR) dengan 31 kerusi dan Musa Aman mengangkat sumpah sebagai ketua menteri pada 10 Mei 2018. Bagaimanapun, Warisan yang menang 21 kerusi ditambah lapan DUN dimenangi rakannya ketika itu, Pakatan Harapan (PH) menjadi kerajaan selepas disokong beberapa Adun BN berpaling tadah, dengan Shafie diangkat ketua menteri, menggantikan Musa.
+“Saya ulang banyak kali, bila BN kalah dengan Warisan? Kita kalah sebab Adun lompat. Kalau tidak, Warisan tidak ke mana,” kata Bung kepada FMT mengulas dakwaan Shafie dalam ceramah Warisan di Kota Belud.
+Menurut Bung, tindakan mengangkat PRU 2018 sebagai kejayaan politik Warisan tidak tepat kerana parti itu tidak memperoleh mandat jelas tanpa bergantung kepada wakil rakyat BN berpaling tadah.
+“Ramai sekarang suka tuntut sesuatu yang bukan hak mereka,” katanya.
+Mengulas lanjut kempen Warisan yang sering menonjolkan imej parti itu sebagai ‘penyelamat Sabah’, Bung berkata beliau tidak nampak arah atau asas kepada slogan berkenaan.
+“Kempen Warisan dengan slogan ‘Selamatkan Sabah’, saya tidak nampak apa yang mereka mahu selamatkan. Semua pun parti tempatan. Dengan siapa mereka mahu selamatkan?” katanya.
+Sambil membandingkan rekod lampau BN, Bung berkata gabungan itu pernah membuktikan keupayaannya menstabilkan Sabah, terutama selepas krisis politik pada 1994 yang membuka jalan kepada pembangunan negeri sehingga 2018. “BN terbukti pernah menyelamatkan Sabah daripada krisis politik agak menggerunkan, di mana Umno dan BN datang pada 1994. Dari situ, bermulalah pembangunan sehingga kita tewas pada 2018,” katanya.
+PRN Sabah ke-16 pada 2020 menyaksikan BN hanya memenangi 14 daripada 40 kerusi ditandingi. Pada PRN kali ini, BN mempertaruhkan 45 calon.
+Suruhanjaya Pilihan Raya menetapkan 29 Nov ini sebagai hari pengundian dan pengundian awal pada 25 Nov.</t>
+  </si>
+  <si>
+    <t>https://harakahdaily.net/2021/03/naib-presiden-pkr-xavier-jayakumar-keluar-parti/</t>
+  </si>
+  <si>
+    <t>Naib Presiden PKR Xavier Jayakumar keluar parti</t>
+  </si>
+  <si>
+    <t>SHAH ALAM: Ahli Parlimen Kuala Langat, Datuk Dr Xavier Jayakumar hari ini mengumumkan peletakan jawatan serta-merta sebagai Naib Presiden dan ahli Parti Keadilan Rakyat (PKR).
+Xavier berkata susulan apa yang berlaku pada tahun lepas dan beliau amat kecewa.
+Beliau berkata terdapat parti-parti yang membincangkan mengenai kemungkinan pilihan raya walaupun ini tidak perlu atau dapat dilaksanakan pada masa ini.
+“Keutamaan kita sekarang ini adalah untuk menyokong kerajaan dalam mengekang pandemik Covid19, mewujudkan pekerjaan serta mendapatkan dana untuk membangun semula ekonomi.
+“Perlu sekurang-kurangnya 18 bulan untuk menyelesaikan program vaksinasi dan lebih dua tahun untuk ekonomi pulih sepenuhnya,” katanya dalam kenyataan di akaun Twitter rasminya.
+Beliau berkata usaha kerajaan itu memerlukan sokongan bipartisan bagi memastikannya dapat dilaksanakan dengan jaya.
+“Rakyat mahukan kestabilan untuk memulakan semula sektor ekonomi kita yang teruk. Oleh itu, kita perlu bekerjasama, bukan melawan antara satu sama lain,” katanya.
+Bekas Menteri Air, Tanah dan Sumber Asli itu juga berkata beliau akan berkhidmat di kawasannya dan menyokong kerajaan sebagai Anggota Parlimen Bebas.
+“Saya yakin dapat menunaikan janji pilihan raya saya kepada rakyat Kuala Langat,” tambahnya. – BERNAMA</t>
+  </si>
+  <si>
+    <t>pkr internal conflict</t>
+  </si>
+  <si>
+    <t>https://www.bharian.com.my/berita/kes/2020/11/750421/nasharudin-lepas-tanpa-bebas-tuduhan-pecah-amanah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nasharudin lepas tanpa bebas tuduhan pecah amanah </t>
+  </si>
+  <si>
+    <t>KUALA LUMPUR: Bekas Timbalan Presiden PAS, Datuk Dr Nasharudin Mat Isa, dilepas tanpa dibebaskan oleh Mahkamah Sesyen Shah Alam atas 16 tuduhan pecah amanah berhubung gaji diterimanya ketika memegang jawatan sebagai Pengerusi Yayasan Nassar.
+Hakim Rozilah Salleh membuat keputusan itu pada 22 September lalu selepas Pejabat Peguam Negara menerima representasi dikemukakan Nasharudin.
+Bagaimanapun, Timbalan Pendakwa Raya, Mohd Zaki Mohd Salleh ketika dihubungi, berkata Nasharudin masih berdepan 14 tuduhan pecah amanah berjumlah RM3.65 juta.
+"Nasharudin mengemukakan representasi kepada Pejabat Peguam Negara pada 7 Julai lalu. "Namun, bagi 14 lagi tuduhan pecah amanah, mahkamah menetapkan 20 November ini untuk sebutan semula kes," katanya.
+Pada 22 November 2019, Nasharuddin didakwa atas 30 pertuduhan pecah amanah membabitkan jumlah sebanyak RM3.6 juta.
+Ia bagi pembayaran gajinya sebagai Pengerusi Yayasan Nassar selama 16 bulan, pembelian hartanah di Bandar Puteri Bangi, kos katering perkahwinan, pinjaman dan yuran pengajian anaknya, akaun peribadi dan pembelian saham serta geran penyelidikan.
+Dia dituduh melakukan kesalahan itu antara 2015 hingga 2018 dan semua kesalahan didakwa dilakukan di CIMB Bank Jalan Sinar Pagi, Country Heights, Hulu Langat serta di Maybank cawangan Menara FELDA di KLCC.
+Pendakwaan terhadapnya dibuat mengikut Seksyen 409 Kanun Keseksaan, yang memperuntukkan hukuman penjara maksimum 20 tahun, sebat dan denda.</t>
+  </si>
+  <si>
+    <t>Nasharudin corruption</t>
+  </si>
+  <si>
+    <t>pas corruption</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Eps Hang Nadim - Rejuvenasi Politik &amp; Masa Depan Negara |JPOS5E6 </t>
+  </si>
+  <si>
+    <t>https://youtu.be/fv5XTIE5dWI?si=3l_Rs1Vrhkny-I-p&amp;t=2015</t>
+  </si>
+  <si>
+    <t>shahril hamdan said that ismail and mydin don’t have a strong stable gov to cause them to fall. With ismail don’t even have a strong support from umno themselves</t>
+  </si>
+  <si>
+    <t>https://youtu.be/CcEryIGLnlg?si=OTnv_FeAvgHL96m_&amp;t=8204</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Episod Terakhir 2025: 10 Perkara Yang Kita Tak Boleh Buat-buat Lupa | YBM #28 </t>
+  </si>
+  <si>
+    <t>Anwar openly want saifuddin to win timbalan presiden and called up cabang2 to vote for saifuddin. So when he lost the election, he felt personally hurt. Anwar feels like PKR is his party so people should listen to him.</t>
+  </si>
 </sst>
 </file>
 
@@ -4831,7 +4973,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -4860,6 +5002,10 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5178,7 +5324,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C8237E3-DA57-49D7-B827-78ACC8405853}">
-  <dimension ref="A1:I571"/>
+  <dimension ref="A1:I574"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23.28515625" customWidth="1"/>
@@ -5960,7 +6106,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="B49" s="2"/>
       <c r="C49" s="3">
@@ -5979,7 +6125,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="B50" s="2"/>
       <c r="C50" s="3">
@@ -5998,7 +6144,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="B51" s="2"/>
       <c r="C51" s="3">
@@ -6017,7 +6163,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" s="2"/>
       <c r="C52" s="3">
@@ -6036,7 +6182,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="B53" s="2"/>
       <c r="C53" s="3">
@@ -6055,274 +6201,280 @@
         <v>350</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="B54" s="2"/>
       <c r="C54" s="3">
-        <v>43860</v>
+        <v>43853</v>
       </c>
       <c r="D54" t="s">
-        <v>539</v>
+        <v>713</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>540</v>
+        <v>712</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>541</v>
+        <v>711</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H54" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="B55" s="2"/>
       <c r="C55" s="3">
-        <v>43863</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>405</v>
+        <v>43860</v>
+      </c>
+      <c r="D55" t="s">
+        <v>539</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>406</v>
+        <v>540</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>407</v>
+        <v>541</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H55" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="B56" s="2"/>
       <c r="C56" s="3">
-        <v>43885</v>
+        <v>43863</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>266</v>
+        <v>405</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>267</v>
+        <v>406</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>407</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="B57" s="2"/>
       <c r="C57" s="3">
-        <v>43887</v>
+        <v>43885</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>381</v>
+        <v>266</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>383</v>
+        <v>267</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="B58" s="2"/>
       <c r="C58" s="3">
         <v>43887</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>417</v>
+        <v>381</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>418</v>
+        <v>383</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>419</v>
+        <v>382</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="B59" s="2"/>
       <c r="C59" s="3">
-        <v>43893</v>
+        <v>43887</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>231</v>
+        <v>417</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>232</v>
+        <v>418</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>233</v>
+        <v>419</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="B60" s="2"/>
       <c r="C60" s="3">
-        <v>43895</v>
+        <v>43893</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>493</v>
+        <v>231</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>494</v>
+        <v>232</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>495</v>
+        <v>233</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="B61" s="2"/>
       <c r="C61" s="3">
-        <v>43913</v>
+        <v>43895</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>96</v>
+        <v>493</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>97</v>
+        <v>494</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>98</v>
+        <v>495</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="B62" s="2"/>
       <c r="C62" s="3">
-        <v>43916</v>
+        <v>43913</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>499</v>
+        <v>96</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>500</v>
+        <v>97</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>501</v>
+        <v>98</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="B63" s="2"/>
       <c r="C63" s="3">
+        <v>43916</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="1"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="3">
         <v>43921</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="D64" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="E64" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="F63" s="2" t="s">
+      <c r="F64" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="G63" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="1"/>
-      <c r="B64" s="2" t="s">
+      <c r="G64" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="1"/>
+      <c r="B65" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F64" s="2"/>
-    </row>
-    <row r="65" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="1"/>
-      <c r="B65" s="2"/>
-      <c r="C65" s="3">
-        <v>43932</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="F65" s="2"/>
     </row>
     <row r="66" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="B66" s="2"/>
       <c r="C66" s="3">
-        <v>43950</v>
+        <v>43932</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>626</v>
+        <v>524</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>627</v>
+        <v>525</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>628</v>
+        <v>526</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="B67" s="2"/>
       <c r="C67" s="3">
-        <v>43964</v>
+        <v>43950</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>402</v>
+        <v>626</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>403</v>
+        <v>627</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>404</v>
+        <v>628</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>4</v>
+        <v>350</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="B68" s="2"/>
       <c r="C68" s="3">
-        <v>43968</v>
+        <v>43964</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>536</v>
+        <v>402</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>537</v>
+        <v>403</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>538</v>
+        <v>404</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>4</v>
@@ -6332,16 +6484,16 @@
       <c r="A69" s="1"/>
       <c r="B69" s="2"/>
       <c r="C69" s="3">
-        <v>43978</v>
+        <v>43968</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>4</v>
@@ -6351,16 +6503,16 @@
       <c r="A70" s="1"/>
       <c r="B70" s="2"/>
       <c r="C70" s="3">
-        <v>43981</v>
+        <v>43978</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>637</v>
+        <v>527</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>636</v>
+        <v>528</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>635</v>
+        <v>529</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>4</v>
@@ -6370,16 +6522,16 @@
       <c r="A71" s="1"/>
       <c r="B71" s="2"/>
       <c r="C71" s="3">
-        <v>43984</v>
+        <v>43981</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>351</v>
+        <v>637</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>352</v>
+        <v>636</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>353</v>
+        <v>635</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>4</v>
@@ -6389,73 +6541,73 @@
       <c r="A72" s="1"/>
       <c r="B72" s="2"/>
       <c r="C72" s="3">
-        <v>43986</v>
+        <v>43984</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="B73" s="2"/>
       <c r="C73" s="3">
-        <v>43993</v>
+        <v>43986</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>350</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="2"/>
       <c r="C74" s="3">
-        <v>44007</v>
+        <v>43993</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>629</v>
+        <v>347</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>630</v>
+        <v>348</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>631</v>
+        <v>349</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>4</v>
+        <v>350</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="B75" s="2"/>
       <c r="C75" s="3">
-        <v>44010</v>
+        <v>44007</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>596</v>
+        <v>629</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>597</v>
+        <v>630</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>598</v>
+        <v>631</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>4</v>
@@ -6465,16 +6617,16 @@
       <c r="A76" s="1"/>
       <c r="B76" s="2"/>
       <c r="C76" s="3">
-        <v>44012</v>
+        <v>44010</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>384</v>
+        <v>596</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>385</v>
+        <v>597</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>386</v>
+        <v>598</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>4</v>
@@ -6487,77 +6639,77 @@
         <v>44012</v>
       </c>
       <c r="D77" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="1"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="3">
+        <v>44012</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="E77" s="1" t="s">
+      <c r="E78" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="F77" s="2" t="s">
+      <c r="F78" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="G77" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="1"/>
-      <c r="B78" s="2" t="s">
+      <c r="G78" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="1"/>
+      <c r="B79" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F78" s="2"/>
-    </row>
-    <row r="79" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="1"/>
-      <c r="B79" s="2"/>
-      <c r="C79" s="3">
-        <v>44013</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>668</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>669</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F79" s="2"/>
+    </row>
+    <row r="80" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="2"/>
       <c r="C80" s="3">
-        <v>44015</v>
+        <v>44013</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>599</v>
+        <v>668</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>600</v>
+        <v>669</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>601</v>
+        <v>670</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="B81" s="2"/>
       <c r="C81" s="3">
-        <v>44016</v>
+        <v>44015</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>214</v>
+        <v>599</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>215</v>
+        <v>600</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>216</v>
+        <v>601</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>4</v>
@@ -6567,16 +6719,16 @@
       <c r="A82" s="1"/>
       <c r="B82" s="2"/>
       <c r="C82" s="3">
-        <v>44018</v>
+        <v>44016</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>641</v>
+        <v>214</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>642</v>
+        <v>215</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>643</v>
+        <v>216</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>4</v>
@@ -6605,54 +6757,54 @@
       <c r="A84" s="1"/>
       <c r="B84" s="2"/>
       <c r="C84" s="3">
-        <v>44022</v>
+        <v>44018</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>479</v>
+        <v>641</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>480</v>
+        <v>642</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>481</v>
+        <v>643</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>482</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="2"/>
       <c r="C85" s="3">
-        <v>44025</v>
+        <v>44022</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>605</v>
+        <v>479</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>606</v>
+        <v>480</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>607</v>
+        <v>481</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>4</v>
+        <v>482</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="2"/>
       <c r="C86" s="3">
-        <v>44031</v>
+        <v>44025</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>357</v>
+        <v>605</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>358</v>
+        <v>606</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>359</v>
+        <v>607</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>4</v>
@@ -6661,45 +6813,45 @@
     <row r="87" spans="1:9" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="2"/>
-      <c r="C87" s="8">
-        <v>44050</v>
+      <c r="C87" s="3">
+        <v>44031</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>698</v>
+        <v>357</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>700</v>
+        <v>358</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>699</v>
+        <v>359</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="H87" s="1" t="s">
-        <v>702</v>
-      </c>
-      <c r="I87" s="1" t="s">
-        <v>701</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="2"/>
       <c r="C88" s="8">
-        <v>44051</v>
+        <v>44050</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>360</v>
+        <v>698</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>361</v>
+        <v>700</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>362</v>
+        <v>699</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>4</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>701</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -6709,13 +6861,13 @@
         <v>44051</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>685</v>
+        <v>360</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>686</v>
+        <v>361</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>687</v>
+        <v>362</v>
       </c>
       <c r="G89" s="1" t="s">
         <v>4</v>
@@ -6725,16 +6877,16 @@
       <c r="A90" s="1"/>
       <c r="B90" s="2"/>
       <c r="C90" s="8">
-        <v>44060</v>
+        <v>44051</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>202</v>
+        <v>685</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>203</v>
+        <v>686</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>204</v>
+        <v>687</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>4</v>
@@ -6744,16 +6896,16 @@
       <c r="A91" s="1"/>
       <c r="B91" s="2"/>
       <c r="C91" s="8">
-        <v>44065</v>
+        <v>44060</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>429</v>
+        <v>202</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>430</v>
+        <v>203</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>431</v>
+        <v>204</v>
       </c>
       <c r="G91" s="1" t="s">
         <v>4</v>
@@ -6763,16 +6915,16 @@
       <c r="A92" s="1"/>
       <c r="B92" s="2"/>
       <c r="C92" s="8">
-        <v>44069</v>
+        <v>44065</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>220</v>
+        <v>429</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>221</v>
+        <v>430</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>222</v>
+        <v>431</v>
       </c>
       <c r="G92" s="1" t="s">
         <v>4</v>
@@ -6782,350 +6934,353 @@
       <c r="A93" s="1"/>
       <c r="B93" s="2"/>
       <c r="C93" s="8">
-        <v>44072</v>
+        <v>44069</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="G93" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="2"/>
       <c r="C94" s="8">
         <v>44072</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>340</v>
+        <v>208</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>341</v>
+        <v>209</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>342</v>
+        <v>210</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>343</v>
+        <v>4</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="2"/>
       <c r="C95" s="8">
-        <v>44076</v>
+        <v>44072</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>205</v>
+        <v>340</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>206</v>
+        <v>341</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>207</v>
+        <v>342</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>4</v>
+        <v>343</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="2"/>
-      <c r="C96" s="3">
-        <v>44078</v>
+      <c r="C96" s="8">
+        <v>44076</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>445</v>
+        <v>205</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>446</v>
+        <v>206</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>447</v>
+        <v>207</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="2"/>
       <c r="C97" s="3">
-        <v>44084</v>
+        <v>44078</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>143</v>
+        <v>445</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>144</v>
+        <v>446</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>145</v>
+        <v>447</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="2"/>
       <c r="C98" s="3">
         <v>44084</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>372</v>
+        <v>143</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>373</v>
+        <v>144</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>374</v>
+        <v>145</v>
       </c>
       <c r="G98" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="2"/>
-      <c r="C99" s="8">
-        <v>44085</v>
+      <c r="C99" s="3">
+        <v>44084</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>213</v>
+        <v>372</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>373</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>212</v>
+        <v>374</v>
       </c>
       <c r="G99" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="2"/>
       <c r="C100" s="8">
-        <v>44087</v>
+        <v>44085</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="2"/>
       <c r="C101" s="8">
-        <v>44090</v>
+        <v>44087</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>245</v>
+        <v>217</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>246</v>
+        <v>218</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>247</v>
+        <v>219</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="2"/>
       <c r="C102" s="8">
+        <v>44090</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="1"/>
+      <c r="B103" s="2"/>
+      <c r="C103" s="8">
         <v>44096</v>
       </c>
-      <c r="D102" s="1" t="s">
+      <c r="D103" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="E102" s="2" t="s">
+      <c r="E103" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="F102" s="2" t="s">
+      <c r="F103" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="G102" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A103" s="1"/>
-      <c r="B103" s="2" t="s">
+      <c r="G103" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A104" s="1"/>
+      <c r="B104" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F103" s="2"/>
-    </row>
-    <row r="104" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="1"/>
-      <c r="B104" s="2"/>
-    </row>
-    <row r="105" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F104" s="2"/>
+    </row>
+    <row r="105" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="2"/>
-      <c r="C105" s="3">
-        <v>44089</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="F105" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="G105" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="106" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="2"/>
       <c r="C106" s="3">
-        <v>44106</v>
+        <v>44089</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>545</v>
+        <v>521</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>546</v>
+        <v>522</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>547</v>
+        <v>523</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="2"/>
       <c r="C107" s="3">
-        <v>44115</v>
+        <v>44106</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>87</v>
+        <v>545</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>88</v>
+        <v>546</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>89</v>
+        <v>547</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="2"/>
       <c r="C108" s="3">
-        <v>44117</v>
+        <v>44115</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>435</v>
+        <v>87</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>436</v>
+        <v>88</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>437</v>
+        <v>89</v>
       </c>
       <c r="G108" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="2"/>
       <c r="C109" s="3">
-        <v>44152</v>
+        <v>44117</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>75</v>
+        <v>435</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>76</v>
+        <v>436</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>77</v>
+        <v>437</v>
       </c>
       <c r="G109" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="2"/>
       <c r="C110" s="3">
-        <v>44153</v>
+        <v>44140</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>414</v>
+        <v>726</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>415</v>
+        <v>727</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>416</v>
+        <v>728</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>730</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="2"/>
       <c r="C111" s="3">
-        <v>44154</v>
+        <v>44152</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>168</v>
+        <v>75</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>169</v>
+        <v>76</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="G111" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="2"/>
       <c r="C112" s="3">
-        <v>44161</v>
+        <v>44153</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>551</v>
+        <v>414</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>552</v>
+        <v>415</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>553</v>
+        <v>416</v>
       </c>
       <c r="G112" s="1" t="s">
         <v>4</v>
@@ -7135,16 +7290,16 @@
       <c r="A113" s="1"/>
       <c r="B113" s="2"/>
       <c r="C113" s="3">
-        <v>44163</v>
+        <v>44154</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>548</v>
+        <v>168</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>549</v>
+        <v>169</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>550</v>
+        <v>170</v>
       </c>
       <c r="G113" s="1" t="s">
         <v>4</v>
@@ -7154,16 +7309,16 @@
       <c r="A114" s="1"/>
       <c r="B114" s="2"/>
       <c r="C114" s="3">
-        <v>44168</v>
+        <v>44161</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>122</v>
+        <v>551</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>123</v>
+        <v>552</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>124</v>
+        <v>553</v>
       </c>
       <c r="G114" s="1" t="s">
         <v>4</v>
@@ -7173,142 +7328,142 @@
       <c r="A115" s="1"/>
       <c r="B115" s="2"/>
       <c r="C115" s="3">
-        <v>44172</v>
+        <v>44163</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>665</v>
+        <v>548</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>666</v>
+        <v>549</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>667</v>
+        <v>550</v>
       </c>
       <c r="G115" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="116" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="2"/>
       <c r="C116" s="3">
-        <v>44179</v>
+        <v>44168</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>333</v>
+        <v>122</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>334</v>
+        <v>123</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>335</v>
+        <v>124</v>
       </c>
       <c r="G116" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="2"/>
       <c r="C117" s="3">
-        <v>44187</v>
+        <v>44172</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>67</v>
+        <v>665</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>68</v>
+        <v>666</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>69</v>
+        <v>667</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
     </row>
     <row r="118" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="2"/>
       <c r="C118" s="3">
-        <v>44189</v>
+        <v>44179</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>586</v>
+        <v>333</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>588</v>
+        <v>334</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>587</v>
+        <v>335</v>
       </c>
       <c r="G118" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A119" s="1">
-        <v>2021</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="1"/>
+      <c r="B119" s="2"/>
+      <c r="C119" s="3">
+        <v>44187</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="2"/>
-    </row>
-    <row r="121" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="1"/>
-      <c r="B121" s="2"/>
-      <c r="C121" s="3">
-        <v>44220</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="F121" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="G121" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C120" s="3">
+        <v>44189</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="G120" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A121" s="1">
+        <v>2021</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="2"/>
-      <c r="C122" s="3">
-        <v>44225</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="F122" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="G122" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="123" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="2"/>
       <c r="C123" s="3">
-        <v>44229</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E123" s="2" t="s">
-        <v>74</v>
+        <v>44220</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>462</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>22</v>
+        <v>463</v>
       </c>
       <c r="G123" s="1" t="s">
         <v>4</v>
@@ -7318,509 +7473,512 @@
       <c r="A124" s="1"/>
       <c r="B124" s="2"/>
       <c r="C124" s="3">
-        <v>44244</v>
-      </c>
-      <c r="D124" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="E124" s="2" t="s">
-        <v>181</v>
+        <v>44225</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>297</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>182</v>
+        <v>298</v>
       </c>
       <c r="G124" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="125" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="2"/>
       <c r="C125" s="3">
-        <v>44247</v>
+        <v>44229</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>177</v>
+        <v>21</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>178</v>
+        <v>74</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>179</v>
+        <v>22</v>
       </c>
       <c r="G125" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="2"/>
       <c r="C126" s="3">
-        <v>44248</v>
+        <v>44244</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>441</v>
+        <v>180</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>442</v>
+        <v>181</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>443</v>
+        <v>182</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>444</v>
+        <v>4</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="2"/>
       <c r="C127" s="3">
-        <v>44277</v>
+        <v>44247</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>71</v>
+        <v>177</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>72</v>
+        <v>178</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>73</v>
+        <v>179</v>
       </c>
       <c r="G127" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
-      <c r="B128" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="B128" s="2"/>
       <c r="C128" s="3">
-        <v>44301</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>187</v>
+        <v>44248</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>442</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>188</v>
+        <v>443</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="2"/>
       <c r="C129" s="3">
-        <v>44311</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>12</v>
+        <v>44268</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>723</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>13</v>
+        <v>724</v>
       </c>
       <c r="G129" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="130" spans="1:7" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H129" s="2" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="B130" s="2"/>
       <c r="C130" s="3">
-        <v>44319</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="E130" s="1" t="s">
-        <v>140</v>
+        <v>44277</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>141</v>
+        <v>73</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
-      <c r="B131" s="2"/>
+      <c r="B131" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="C131" s="3">
-        <v>44361</v>
+        <v>44301</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>632</v>
+        <v>186</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>633</v>
+        <v>187</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>634</v>
+        <v>188</v>
       </c>
       <c r="G131" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="B132" s="2"/>
       <c r="C132" s="3">
-        <v>44368</v>
+        <v>44311</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>309</v>
+        <v>12</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>310</v>
+        <v>13</v>
       </c>
       <c r="G132" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133" s="2"/>
       <c r="C133" s="3">
-        <v>44375</v>
+        <v>44319</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>3</v>
+        <v>139</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>5</v>
+        <v>141</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
-      <c r="B134" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="B134" s="2"/>
       <c r="C134" s="3">
-        <v>44390</v>
+        <v>44361</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F134" s="1" t="s">
-        <v>7</v>
+        <v>632</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>634</v>
       </c>
       <c r="G134" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="135" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="B135" s="2"/>
       <c r="C135" s="3">
-        <v>44398</v>
+        <v>44368</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>452</v>
+        <v>308</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>453</v>
+        <v>309</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>454</v>
+        <v>310</v>
       </c>
       <c r="G135" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="136" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="B136" s="2"/>
       <c r="C136" s="3">
-        <v>44408</v>
+        <v>44375</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>456</v>
+        <v>3</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>457</v>
+        <v>5</v>
       </c>
       <c r="G136" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
-      <c r="B137" s="2"/>
+      <c r="B137" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="C137" s="3">
-        <v>44411</v>
+        <v>44390</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="F137" s="2" t="s">
-        <v>371</v>
+        <v>6</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="G137" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="B138" s="2"/>
       <c r="C138" s="3">
-        <v>44411</v>
+        <v>44398</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>476</v>
+        <v>452</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>477</v>
+        <v>453</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>478</v>
+        <v>454</v>
       </c>
       <c r="G138" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="139" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="B139" s="2"/>
       <c r="C139" s="3">
-        <v>44413</v>
+        <v>44408</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>78</v>
+        <v>455</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>79</v>
+        <v>456</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>80</v>
+        <v>457</v>
       </c>
       <c r="G139" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="140" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="B140" s="2"/>
       <c r="C140" s="3">
-        <v>44420</v>
+        <v>44411</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>691</v>
+        <v>369</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>692</v>
+        <v>370</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>693</v>
-      </c>
-      <c r="G140" s="2" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>371</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141" s="2"/>
-      <c r="C141" s="3"/>
+      <c r="C141" s="3">
+        <v>44411</v>
+      </c>
       <c r="D141" s="1" t="s">
-        <v>695</v>
+        <v>476</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>696</v>
+        <v>477</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>697</v>
+        <v>478</v>
       </c>
       <c r="G141" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="142" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="B142" s="2"/>
       <c r="C142" s="3">
-        <v>44422</v>
+        <v>44413</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>650</v>
+        <v>78</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>651</v>
+        <v>79</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>652</v>
+        <v>80</v>
       </c>
       <c r="G142" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="2"/>
       <c r="C143" s="3">
-        <v>44443</v>
+        <v>44420</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>487</v>
+        <v>691</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>488</v>
+        <v>692</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="G143" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>693</v>
+      </c>
+      <c r="G143" s="2" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="2"/>
-      <c r="C144" s="3">
-        <v>44454</v>
-      </c>
+      <c r="C144" s="3"/>
       <c r="D144" s="1" t="s">
-        <v>299</v>
+        <v>695</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>300</v>
+        <v>696</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>301</v>
+        <v>697</v>
       </c>
       <c r="G144" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="145" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
-      <c r="B145" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B145" s="2"/>
+      <c r="C145" s="3">
+        <v>44422</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="F145" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="G145" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="B146" s="2"/>
       <c r="C146" s="3">
-        <v>44473</v>
+        <v>44443</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>237</v>
+        <v>487</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>238</v>
+        <v>488</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>239</v>
+        <v>489</v>
       </c>
       <c r="G146" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="147" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="B147" s="2"/>
       <c r="C147" s="3">
-        <v>44473</v>
+        <v>44454</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>227</v>
+        <v>299</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>228</v>
+        <v>300</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>229</v>
+        <v>301</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
-      <c r="B148" s="2"/>
-      <c r="C148" s="3">
-        <v>44477</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E148" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F148" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G148" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B148" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="B149" s="2"/>
       <c r="C149" s="3">
-        <v>44488</v>
+        <v>44473</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="B150" s="2"/>
       <c r="C150" s="3">
-        <v>44497</v>
+        <v>44473</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>174</v>
+        <v>227</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>175</v>
+        <v>228</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>176</v>
+        <v>229</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>4</v>
+        <v>230</v>
       </c>
     </row>
     <row r="151" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="B151" s="2"/>
       <c r="C151" s="3">
-        <v>44501</v>
+        <v>44477</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>644</v>
+        <v>81</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>645</v>
+        <v>82</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>646</v>
+        <v>83</v>
       </c>
       <c r="G151" s="1" t="s">
         <v>4</v>
@@ -7830,54 +7988,54 @@
       <c r="A152" s="1"/>
       <c r="B152" s="2"/>
       <c r="C152" s="3">
-        <v>44509</v>
+        <v>44488</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>293</v>
+        <v>234</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>294</v>
+        <v>235</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>295</v>
+        <v>236</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>4</v>
+        <v>240</v>
       </c>
     </row>
     <row r="153" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="B153" s="2"/>
       <c r="C153" s="3">
-        <v>44510</v>
+        <v>44497</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>286</v>
+        <v>174</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>287</v>
+        <v>175</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>288</v>
+        <v>176</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>289</v>
+        <v>4</v>
       </c>
     </row>
     <row r="154" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="B154" s="2"/>
       <c r="C154" s="3">
-        <v>44515</v>
+        <v>44501</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>171</v>
+        <v>644</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>172</v>
+        <v>645</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>173</v>
+        <v>646</v>
       </c>
       <c r="G154" s="1" t="s">
         <v>4</v>
@@ -7887,16 +8045,16 @@
       <c r="A155" s="1"/>
       <c r="B155" s="2"/>
       <c r="C155" s="3">
-        <v>44518</v>
+        <v>44509</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>242</v>
+        <v>293</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>243</v>
+        <v>294</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>244</v>
+        <v>295</v>
       </c>
       <c r="G155" s="1" t="s">
         <v>4</v>
@@ -7906,35 +8064,35 @@
       <c r="A156" s="1"/>
       <c r="B156" s="2"/>
       <c r="C156" s="3">
-        <v>44519</v>
+        <v>44510</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>155</v>
+        <v>286</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>156</v>
+        <v>287</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>157</v>
+        <v>288</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
     </row>
     <row r="157" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="B157" s="2"/>
       <c r="C157" s="3">
-        <v>44524</v>
+        <v>44515</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>659</v>
+        <v>171</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>660</v>
+        <v>172</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>661</v>
+        <v>173</v>
       </c>
       <c r="G157" s="1" t="s">
         <v>4</v>
@@ -7944,16 +8102,16 @@
       <c r="A158" s="1"/>
       <c r="B158" s="2"/>
       <c r="C158" s="3">
-        <v>44525</v>
+        <v>44518</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>558</v>
+        <v>242</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>559</v>
+        <v>243</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>560</v>
+        <v>244</v>
       </c>
       <c r="G158" s="1" t="s">
         <v>4</v>
@@ -7963,35 +8121,35 @@
       <c r="A159" s="1"/>
       <c r="B159" s="2"/>
       <c r="C159" s="3">
-        <v>44527</v>
+        <v>44519</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>647</v>
+        <v>155</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>648</v>
+        <v>156</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>649</v>
+        <v>157</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>4</v>
+        <v>281</v>
       </c>
     </row>
     <row r="160" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="B160" s="2"/>
       <c r="C160" s="3">
-        <v>44529</v>
+        <v>44524</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>458</v>
+        <v>659</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>459</v>
+        <v>660</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>460</v>
+        <v>661</v>
       </c>
       <c r="G160" s="1" t="s">
         <v>4</v>
@@ -8001,35 +8159,35 @@
       <c r="A161" s="1"/>
       <c r="B161" s="2"/>
       <c r="C161" s="3">
-        <v>44532</v>
+        <v>44525</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>423</v>
+        <v>558</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>424</v>
+        <v>559</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>425</v>
+        <v>560</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>350</v>
+        <v>4</v>
       </c>
     </row>
     <row r="162" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="B162" s="2"/>
       <c r="C162" s="3">
-        <v>44543</v>
+        <v>44527</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>490</v>
+        <v>647</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>491</v>
+        <v>648</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>492</v>
+        <v>649</v>
       </c>
       <c r="G162" s="1" t="s">
         <v>4</v>
@@ -8039,16 +8197,16 @@
       <c r="A163" s="1"/>
       <c r="B163" s="2"/>
       <c r="C163" s="3">
-        <v>44550</v>
+        <v>44529</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="G163" s="1" t="s">
         <v>4</v>
@@ -8058,122 +8216,122 @@
       <c r="A164" s="1"/>
       <c r="B164" s="2"/>
       <c r="C164" s="3">
-        <v>44557</v>
+        <v>44532</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>620</v>
+        <v>423</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>621</v>
+        <v>424</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>622</v>
+        <v>425</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="1">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="1"/>
+      <c r="B165" s="2"/>
+      <c r="C165" s="3">
+        <v>44543</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="G165" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
-      <c r="B166" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B166" s="2"/>
+      <c r="C166" s="3">
+        <v>44550</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="F166" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="G166" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="B167" s="2"/>
       <c r="C167" s="3">
-        <v>44566</v>
+        <v>44557</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="G167" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="168" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="1"/>
-      <c r="B168" s="2"/>
-      <c r="C168" s="3">
-        <v>44569</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="E168" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="F168" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="G168" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="1">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
-      <c r="B169" s="2"/>
-      <c r="C169" s="3">
-        <v>44577</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E169" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="F169" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G169" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B169" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="B170" s="2"/>
       <c r="C170" s="3">
-        <v>44577</v>
+        <v>44566</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>513</v>
+        <v>617</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>512</v>
+        <v>618</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>514</v>
+        <v>619</v>
       </c>
       <c r="G170" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="171" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="B171" s="2"/>
       <c r="C171" s="3">
-        <v>44582</v>
+        <v>44569</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>515</v>
+        <v>464</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>516</v>
+        <v>465</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>517</v>
+        <v>466</v>
       </c>
       <c r="G171" s="1" t="s">
         <v>4</v>
@@ -8183,92 +8341,92 @@
       <c r="A172" s="1"/>
       <c r="B172" s="2"/>
       <c r="C172" s="3">
-        <v>44588</v>
+        <v>44577</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>542</v>
+        <v>29</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>543</v>
+        <v>511</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>544</v>
+        <v>30</v>
       </c>
       <c r="G172" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="173" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="B173" s="2"/>
       <c r="C173" s="3">
-        <v>44595</v>
+        <v>44577</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="E173" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="F173" s="5" t="s">
-        <v>160</v>
+        <v>513</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="F173" s="2" t="s">
+        <v>514</v>
       </c>
       <c r="G173" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="174" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="B174" s="2"/>
       <c r="C174" s="3">
-        <v>44605</v>
+        <v>44582</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="E174" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="F174" s="5" t="s">
-        <v>163</v>
+        <v>515</v>
+      </c>
+      <c r="E174" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="F174" s="2" t="s">
+        <v>517</v>
       </c>
       <c r="G174" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="175" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="B175" s="2"/>
       <c r="C175" s="3">
-        <v>44623</v>
+        <v>44588</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="E175" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="F175" s="5" t="s">
-        <v>338</v>
+        <v>542</v>
+      </c>
+      <c r="E175" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="F175" s="2" t="s">
+        <v>544</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>339</v>
+        <v>4</v>
       </c>
     </row>
     <row r="176" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="B176" s="2"/>
       <c r="C176" s="3">
-        <v>44623</v>
+        <v>44595</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>420</v>
+        <v>158</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>421</v>
+        <v>159</v>
       </c>
       <c r="F176" s="5" t="s">
-        <v>422</v>
+        <v>160</v>
       </c>
       <c r="G176" s="1" t="s">
         <v>4</v>
@@ -8278,149 +8436,149 @@
       <c r="A177" s="1"/>
       <c r="B177" s="2"/>
       <c r="C177" s="3">
-        <v>44634</v>
+        <v>44605</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>674</v>
+        <v>161</v>
       </c>
       <c r="E177" s="6" t="s">
-        <v>675</v>
+        <v>162</v>
       </c>
       <c r="F177" s="5" t="s">
-        <v>676</v>
+        <v>163</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>677</v>
+        <v>4</v>
       </c>
     </row>
     <row r="178" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="B178" s="2"/>
       <c r="C178" s="3">
-        <v>44635</v>
+        <v>44623</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>574</v>
+        <v>336</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>575</v>
+        <v>337</v>
       </c>
       <c r="F178" s="5" t="s">
-        <v>576</v>
+        <v>338</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="B179" s="2"/>
       <c r="C179" s="3">
-        <v>44635</v>
+        <v>44623</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E179" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F179" s="2" t="s">
-        <v>44</v>
+        <v>420</v>
+      </c>
+      <c r="E179" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="F179" s="5" t="s">
+        <v>422</v>
       </c>
       <c r="G179" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="180" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="B180" s="2"/>
       <c r="C180" s="3">
-        <v>44639</v>
+        <v>44634</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="E180" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="F180" s="2" t="s">
-        <v>284</v>
+        <v>674</v>
+      </c>
+      <c r="E180" s="6" t="s">
+        <v>675</v>
+      </c>
+      <c r="F180" s="5" t="s">
+        <v>676</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="B181" s="2"/>
       <c r="C181" s="3">
-        <v>44640</v>
+        <v>44635</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="E181" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="F181" s="2" t="s">
-        <v>304</v>
+        <v>574</v>
+      </c>
+      <c r="E181" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="F181" s="5" t="s">
+        <v>576</v>
       </c>
       <c r="G181" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="182" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="B182" s="2"/>
       <c r="C182" s="3">
-        <v>44641</v>
+        <v>44635</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G182" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="183" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="B183" s="2"/>
       <c r="C183" s="3">
-        <v>44641</v>
+        <v>44639</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="B184" s="2"/>
       <c r="C184" s="3">
-        <v>44642</v>
+        <v>44640</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>554</v>
+        <v>302</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>555</v>
+        <v>303</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>556</v>
+        <v>304</v>
       </c>
       <c r="G184" s="1" t="s">
         <v>4</v>
@@ -8430,16 +8588,16 @@
       <c r="A185" s="1"/>
       <c r="B185" s="2"/>
       <c r="C185" s="3">
-        <v>44645</v>
+        <v>44641</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E185" s="4" t="s">
-        <v>46</v>
+        <v>39</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G185" s="1" t="s">
         <v>4</v>
@@ -8449,91 +8607,97 @@
       <c r="A186" s="1"/>
       <c r="B186" s="2"/>
       <c r="C186" s="3">
-        <v>44651</v>
+        <v>44641</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>608</v>
-      </c>
-      <c r="E186" s="4" t="s">
-        <v>609</v>
+        <v>290</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>291</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>610</v>
+        <v>292</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B187" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E187" s="3"/>
-    </row>
-    <row r="188" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A187" s="1"/>
+      <c r="B187" s="2"/>
+      <c r="C187" s="3">
+        <v>44642</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="F187" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="G187" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A188" s="1"/>
       <c r="B188" s="2"/>
       <c r="C188" s="3">
-        <v>44666</v>
+        <v>44645</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="E188" s="1" t="s">
-        <v>264</v>
+        <v>45</v>
+      </c>
+      <c r="E188" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>265</v>
+        <v>47</v>
       </c>
       <c r="G188" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="189" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A189" s="1"/>
       <c r="B189" s="2"/>
       <c r="C189" s="3">
-        <v>44675</v>
+        <v>44651</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="E189" s="1" t="s">
-        <v>400</v>
+        <v>608</v>
+      </c>
+      <c r="E189" s="4" t="s">
+        <v>609</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>401</v>
+        <v>610</v>
       </c>
       <c r="G189" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="190" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B190" s="2"/>
-      <c r="C190" s="3">
-        <v>44677</v>
-      </c>
-      <c r="D190" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E190" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="F190" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G190" s="1" t="s">
-        <v>138</v>
-      </c>
+    <row r="190" spans="1:7" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B190" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E190" s="3"/>
     </row>
     <row r="191" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B191" s="2"/>
       <c r="C191" s="3">
-        <v>44682</v>
+        <v>44666</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F191" s="1" t="s">
-        <v>20</v>
+        <v>263</v>
+      </c>
+      <c r="E191" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="F191" s="2" t="s">
+        <v>265</v>
       </c>
       <c r="G191" s="1" t="s">
         <v>4</v>
@@ -8542,16 +8706,16 @@
     <row r="192" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B192" s="2"/>
       <c r="C192" s="3">
-        <v>44682</v>
+        <v>44675</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>224</v>
+        <v>399</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>225</v>
+        <v>400</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>226</v>
+        <v>401</v>
       </c>
       <c r="G192" s="1" t="s">
         <v>4</v>
@@ -8560,34 +8724,31 @@
     <row r="193" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B193" s="2"/>
       <c r="C193" s="3">
-        <v>44692</v>
-      </c>
-      <c r="D193" t="s">
-        <v>249</v>
+        <v>44677</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>135</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>250</v>
+        <v>136</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>251</v>
+        <v>137</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>4</v>
+        <v>138</v>
       </c>
     </row>
     <row r="194" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B194" s="2"/>
       <c r="C194" s="3">
-        <v>44692</v>
-      </c>
-      <c r="D194" t="s">
-        <v>583</v>
-      </c>
-      <c r="E194" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="F194" s="2" t="s">
-        <v>585</v>
+        <v>44682</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F194" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="G194" s="1" t="s">
         <v>4</v>
@@ -8596,16 +8757,16 @@
     <row r="195" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B195" s="2"/>
       <c r="C195" s="3">
-        <v>44695</v>
-      </c>
-      <c r="D195" t="s">
-        <v>257</v>
+        <v>44682</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>224</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>258</v>
+        <v>225</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>259</v>
+        <v>226</v>
       </c>
       <c r="G195" s="1" t="s">
         <v>4</v>
@@ -8614,34 +8775,34 @@
     <row r="196" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B196" s="2"/>
       <c r="C196" s="3">
-        <v>44696</v>
-      </c>
-      <c r="D196" s="1" t="s">
-        <v>198</v>
+        <v>44692</v>
+      </c>
+      <c r="D196" t="s">
+        <v>249</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>199</v>
+        <v>250</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="G196" s="7" t="s">
-        <v>201</v>
+        <v>251</v>
+      </c>
+      <c r="G196" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="197" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B197" s="2"/>
       <c r="C197" s="3">
-        <v>44701</v>
-      </c>
-      <c r="D197" s="1" t="s">
-        <v>564</v>
+        <v>44692</v>
+      </c>
+      <c r="D197" t="s">
+        <v>583</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>565</v>
+        <v>584</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>566</v>
+        <v>585</v>
       </c>
       <c r="G197" s="1" t="s">
         <v>4</v>
@@ -8650,16 +8811,16 @@
     <row r="198" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B198" s="2"/>
       <c r="C198" s="3">
-        <v>44708</v>
-      </c>
-      <c r="D198" s="1" t="s">
-        <v>510</v>
+        <v>44695</v>
+      </c>
+      <c r="D198" t="s">
+        <v>257</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>509</v>
+        <v>258</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>508</v>
+        <v>259</v>
       </c>
       <c r="G198" s="1" t="s">
         <v>4</v>
@@ -8668,52 +8829,52 @@
     <row r="199" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B199" s="2"/>
       <c r="C199" s="3">
-        <v>44710</v>
+        <v>44696</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>580</v>
+        <v>198</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>581</v>
+        <v>199</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="G199" s="1" t="s">
-        <v>4</v>
+        <v>200</v>
+      </c>
+      <c r="G199" s="7" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="200" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B200" s="2"/>
       <c r="C200" s="3">
-        <v>44712</v>
+        <v>44701</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>285</v>
+        <v>4</v>
       </c>
     </row>
     <row r="201" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B201" s="2"/>
       <c r="C201" s="3">
-        <v>44714</v>
+        <v>44708</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>688</v>
+        <v>510</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>689</v>
+        <v>509</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>690</v>
+        <v>508</v>
       </c>
       <c r="G201" s="1" t="s">
         <v>4</v>
@@ -8722,138 +8883,141 @@
     <row r="202" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B202" s="2"/>
       <c r="C202" s="3">
-        <v>44717</v>
+        <v>44710</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>662</v>
+        <v>580</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>663</v>
+        <v>581</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>664</v>
+        <v>582</v>
       </c>
       <c r="G202" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="203" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B203" s="2"/>
       <c r="C203" s="3">
-        <v>44724</v>
+        <v>44712</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>577</v>
+        <v>561</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>578</v>
+        <v>562</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>579</v>
+        <v>563</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>4</v>
+        <v>285</v>
       </c>
     </row>
     <row r="204" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B204" s="2"/>
       <c r="C204" s="3">
+        <v>44714</v>
+      </c>
+      <c r="D204" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="F204" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="G204" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="205" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B205" s="2"/>
+      <c r="C205" s="3">
+        <v>44717</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="F205" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="G205" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="206" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C206" s="3">
+        <v>44724</v>
+      </c>
+      <c r="D206" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="F206" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="G206" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="207" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B207" s="2"/>
+      <c r="C207" s="3">
         <v>44734</v>
       </c>
-      <c r="D204" s="1" t="s">
+      <c r="D207" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="E204" s="1" t="s">
+      <c r="E207" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="F204" s="2" t="s">
+      <c r="F207" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="G204" s="1" t="s">
+      <c r="G207" s="1" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="205" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C205" s="3">
+    <row r="208" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C208" s="3">
         <v>44736</v>
       </c>
-      <c r="D205" s="1" t="s">
+      <c r="D208" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E205" s="1" t="s">
+      <c r="E208" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F205" s="1" t="s">
+      <c r="F208" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G205" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="206" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B206" s="2" t="s">
+      <c r="G208" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="209" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B209" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="207" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C207" s="3">
-        <v>44753</v>
-      </c>
-      <c r="D207" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F207" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G207" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="208" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C208" s="3">
-        <v>44756</v>
-      </c>
-      <c r="D208" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="E208" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="F208" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="G208" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="209" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C209" s="3">
-        <v>44760</v>
-      </c>
-      <c r="D209" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E209" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F209" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="G209" s="1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="210" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C210" s="3">
-        <v>44763</v>
+        <v>44753</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="E210" s="1" t="s">
-        <v>615</v>
+        <v>25</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>616</v>
+        <v>26</v>
       </c>
       <c r="G210" s="1" t="s">
         <v>4</v>
@@ -8861,84 +9025,84 @@
     </row>
     <row r="211" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C211" s="3">
+        <v>44756</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="F211" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="G211" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="212" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C212" s="3">
+        <v>44760</v>
+      </c>
+      <c r="D212" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E212" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F212" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G212" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="213" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C213" s="3">
+        <v>44763</v>
+      </c>
+      <c r="D213" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="E213" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="F213" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="G213" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="214" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C214" s="3">
         <v>44764</v>
       </c>
-      <c r="D211" s="1" t="s">
+      <c r="D214" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="E211" s="1" t="s">
+      <c r="E214" s="1" t="s">
         <v>612</v>
       </c>
-      <c r="F211" s="2" t="s">
+      <c r="F214" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="G211" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="212" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C212" s="9" t="s">
+      <c r="G214" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="215" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C215" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="D212" s="1" t="s">
+      <c r="D215" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E212" s="1" t="s">
+      <c r="E215" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F212" s="2" t="s">
+      <c r="F215" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="G212" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="213" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C213" s="9">
-        <v>44789</v>
-      </c>
-      <c r="D213" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="E213" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="F213" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="G213" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="214" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C214" s="9">
-        <v>44796</v>
-      </c>
-      <c r="D214" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="E214" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="F214" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="G214" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="215" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C215" s="9">
-        <v>44798</v>
-      </c>
-      <c r="D215" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="E215" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="F215" s="2" t="s">
-        <v>398</v>
       </c>
       <c r="G215" s="1" t="s">
         <v>4</v>
@@ -8946,101 +9110,101 @@
     </row>
     <row r="216" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C216" s="9">
+        <v>44789</v>
+      </c>
+      <c r="D216" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="E216" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="F216" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="G216" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="217" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C217" s="9">
+        <v>44796</v>
+      </c>
+      <c r="D217" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="E217" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="F217" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G217" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="218" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C218" s="9">
+        <v>44798</v>
+      </c>
+      <c r="D218" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="E218" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="F218" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="G218" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="219" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C219" s="9">
         <v>44799</v>
       </c>
-      <c r="D216" s="1" t="s">
+      <c r="D219" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="E216" s="1" t="s">
+      <c r="E219" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="F216" s="2" t="s">
+      <c r="F219" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="G216" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="217" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C217" s="3">
+      <c r="G219" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="220" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C220" s="3">
         <v>44783</v>
       </c>
-      <c r="D217" s="1" t="s">
+      <c r="D220" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E217" s="1" t="s">
+      <c r="E220" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F217" s="2" t="s">
+      <c r="F220" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="G217" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="218" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C218" s="3">
+      <c r="G220" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="221" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C221" s="3">
         <v>44789</v>
       </c>
-      <c r="D218" s="1" t="s">
+      <c r="D221" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E218" s="1" t="s">
+      <c r="E221" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F218" s="2" t="s">
+      <c r="F221" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="G218" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="219" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C219" s="3">
-        <v>44789</v>
-      </c>
-      <c r="D219" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="E219" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F219" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="G219" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="220" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C220" s="3">
-        <v>44797</v>
-      </c>
-      <c r="D220" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="E220" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="F220" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="G220" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="221" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C221" s="3">
-        <v>44823</v>
-      </c>
-      <c r="D221" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="E221" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="F221" s="2" t="s">
-        <v>365</v>
       </c>
       <c r="G221" s="1" t="s">
         <v>4</v>
@@ -9048,100 +9212,97 @@
     </row>
     <row r="222" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C222" s="3">
+        <v>44789</v>
+      </c>
+      <c r="D222" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E222" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F222" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G222" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="223" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C223" s="3">
+        <v>44797</v>
+      </c>
+      <c r="D223" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="E223" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="F223" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="G223" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="224" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C224" s="3">
         <v>44823</v>
       </c>
-      <c r="D222" s="1" t="s">
+      <c r="D224" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="E224" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="F224" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="G224" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="225" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C225" s="3">
+        <v>44823</v>
+      </c>
+      <c r="D225" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="E222" s="1" t="s">
+      <c r="E225" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="F222" s="2" t="s">
+      <c r="F225" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="G222" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="223" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B223" s="2" t="s">
+      <c r="G225" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="226" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B226" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C223" s="3"/>
-      <c r="D223" s="2"/>
-      <c r="E223" s="2"/>
-      <c r="F223" s="2"/>
-    </row>
-    <row r="224" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B224" s="2"/>
-    </row>
-    <row r="225" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B225" s="2"/>
-      <c r="C225" s="3">
-        <v>44852</v>
-      </c>
-      <c r="D225" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="E225" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="F225" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="G225" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="226" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B226" s="2"/>
-      <c r="C226" s="3">
-        <v>44856</v>
-      </c>
-      <c r="D226" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="E226" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="F226" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="G226" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="C226" s="3"/>
+      <c r="D226" s="2"/>
+      <c r="E226" s="2"/>
+      <c r="F226" s="2"/>
     </row>
     <row r="227" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B227" s="2"/>
-      <c r="C227" s="3">
-        <v>44856</v>
-      </c>
-      <c r="D227" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="E227" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="F227" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="G227" s="1" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="228" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B228" s="2"/>
       <c r="C228" s="3">
-        <v>44858</v>
+        <v>44852</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>105</v>
+        <v>330</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>106</v>
+        <v>331</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>107</v>
+        <v>332</v>
       </c>
       <c r="G228" s="1" t="s">
         <v>4</v>
@@ -9150,16 +9311,16 @@
     <row r="229" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B229" s="2"/>
       <c r="C229" s="3">
-        <v>44859</v>
+        <v>44856</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>108</v>
+        <v>317</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>109</v>
+        <v>318</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>110</v>
+        <v>319</v>
       </c>
       <c r="G229" s="1" t="s">
         <v>4</v>
@@ -9168,16 +9329,16 @@
     <row r="230" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B230" s="2"/>
       <c r="C230" s="3">
-        <v>44862</v>
+        <v>44856</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E230" t="s">
-        <v>120</v>
+        <v>567</v>
+      </c>
+      <c r="E230" s="2" t="s">
+        <v>568</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>121</v>
+        <v>569</v>
       </c>
       <c r="G230" s="1" t="s">
         <v>4</v>
@@ -9186,16 +9347,16 @@
     <row r="231" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B231" s="2"/>
       <c r="C231" s="3">
-        <v>44864</v>
+        <v>44858</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>252</v>
+        <v>105</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>253</v>
+        <v>106</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>254</v>
+        <v>107</v>
       </c>
       <c r="G231" s="1" t="s">
         <v>4</v>
@@ -9204,16 +9365,16 @@
     <row r="232" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B232" s="2"/>
       <c r="C232" s="3">
-        <v>44866</v>
+        <v>44859</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>31</v>
+        <v>108</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>32</v>
+        <v>109</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>255</v>
+        <v>110</v>
       </c>
       <c r="G232" s="1" t="s">
         <v>4</v>
@@ -9222,16 +9383,16 @@
     <row r="233" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B233" s="2"/>
       <c r="C233" s="3">
-        <v>44866</v>
+        <v>44862</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E233" s="2" t="s">
-        <v>150</v>
+        <v>108</v>
+      </c>
+      <c r="E233" t="s">
+        <v>120</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="G233" s="1" t="s">
         <v>4</v>
@@ -9240,16 +9401,16 @@
     <row r="234" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B234" s="2"/>
       <c r="C234" s="3">
-        <v>44868</v>
-      </c>
-      <c r="D234" s="1" t="s">
-        <v>90</v>
+        <v>44864</v>
+      </c>
+      <c r="D234" s="2" t="s">
+        <v>252</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>91</v>
+        <v>253</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>92</v>
+        <v>254</v>
       </c>
       <c r="G234" s="1" t="s">
         <v>4</v>
@@ -9258,16 +9419,16 @@
     <row r="235" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B235" s="2"/>
       <c r="C235" s="3">
-        <v>44870</v>
-      </c>
-      <c r="D235" s="1" t="s">
-        <v>375</v>
+        <v>44866</v>
+      </c>
+      <c r="D235" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>376</v>
+        <v>32</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>377</v>
+        <v>255</v>
       </c>
       <c r="G235" s="1" t="s">
         <v>4</v>
@@ -9276,16 +9437,16 @@
     <row r="236" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B236" s="2"/>
       <c r="C236" s="3">
-        <v>44873</v>
-      </c>
-      <c r="D236" s="1" t="s">
-        <v>505</v>
+        <v>44866</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>149</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>506</v>
+        <v>150</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>507</v>
+        <v>151</v>
       </c>
       <c r="G236" s="1" t="s">
         <v>4</v>
@@ -9294,16 +9455,16 @@
     <row r="237" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B237" s="2"/>
       <c r="C237" s="3">
-        <v>44874</v>
-      </c>
-      <c r="D237" s="2" t="s">
-        <v>33</v>
+        <v>44868</v>
+      </c>
+      <c r="D237" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>256</v>
+        <v>92</v>
       </c>
       <c r="G237" s="1" t="s">
         <v>4</v>
@@ -9312,16 +9473,16 @@
     <row r="238" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B238" s="2"/>
       <c r="C238" s="3">
-        <v>44875</v>
-      </c>
-      <c r="D238" s="2" t="s">
-        <v>93</v>
+        <v>44870</v>
+      </c>
+      <c r="D238" s="1" t="s">
+        <v>375</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>94</v>
+        <v>376</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>95</v>
+        <v>377</v>
       </c>
       <c r="G238" s="1" t="s">
         <v>4</v>
@@ -9330,16 +9491,16 @@
     <row r="239" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B239" s="2"/>
       <c r="C239" s="3">
-        <v>44876</v>
-      </c>
-      <c r="D239" s="2" t="s">
-        <v>305</v>
+        <v>44873</v>
+      </c>
+      <c r="D239" s="1" t="s">
+        <v>505</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>306</v>
+        <v>506</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>307</v>
+        <v>507</v>
       </c>
       <c r="G239" s="1" t="s">
         <v>4</v>
@@ -9348,16 +9509,16 @@
     <row r="240" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B240" s="2"/>
       <c r="C240" s="3">
-        <v>44880</v>
+        <v>44874</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>327</v>
+        <v>33</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>328</v>
+        <v>34</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>329</v>
+        <v>256</v>
       </c>
       <c r="G240" s="1" t="s">
         <v>4</v>
@@ -9366,16 +9527,16 @@
     <row r="241" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B241" s="2"/>
       <c r="C241" s="3">
-        <v>44883</v>
+        <v>44875</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>152</v>
+        <v>93</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>153</v>
+        <v>94</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>154</v>
+        <v>95</v>
       </c>
       <c r="G241" s="1" t="s">
         <v>4</v>
@@ -9384,34 +9545,34 @@
     <row r="242" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B242" s="2"/>
       <c r="C242" s="3">
-        <v>44885</v>
+        <v>44876</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="G242" s="2" t="s">
-        <v>323</v>
+        <v>307</v>
+      </c>
+      <c r="G242" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="243" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B243" s="2"/>
       <c r="C243" s="3">
-        <v>44886</v>
+        <v>44880</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>189</v>
+        <v>327</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>190</v>
+        <v>328</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>191</v>
+        <v>329</v>
       </c>
       <c r="G243" s="1" t="s">
         <v>4</v>
@@ -9420,67 +9581,70 @@
     <row r="244" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B244" s="2"/>
       <c r="C244" s="3">
+        <v>44883</v>
+      </c>
+      <c r="D244" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E244" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F244" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G244" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="245" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B245" s="2"/>
+      <c r="C245" s="3">
+        <v>44885</v>
+      </c>
+      <c r="D245" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="E245" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F245" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="G245" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="246" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B246" s="2"/>
+      <c r="C246" s="3">
+        <v>44886</v>
+      </c>
+      <c r="D246" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E246" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="F246" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="G246" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="247" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B247" s="2"/>
+      <c r="C247" s="3">
         <v>44887</v>
       </c>
-      <c r="D244" s="2" t="s">
+      <c r="D247" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="E244" s="2" t="s">
+      <c r="E247" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="F244" s="2" t="s">
+      <c r="F247" s="2" t="s">
         <v>194</v>
-      </c>
-      <c r="G244" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="245" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C245" s="3">
-        <v>44887</v>
-      </c>
-      <c r="D245" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="E245" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="F245" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="G245" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="246" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C246" s="3">
-        <v>44889</v>
-      </c>
-      <c r="D246" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E246" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F246" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="G246" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="247" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C247" s="3">
-        <v>44894</v>
-      </c>
-      <c r="D247" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="E247" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="F247" s="2" t="s">
-        <v>475</v>
       </c>
       <c r="G247" s="1" t="s">
         <v>4</v>
@@ -9488,39 +9652,79 @@
     </row>
     <row r="248" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C248" s="3">
+        <v>44887</v>
+      </c>
+      <c r="D248" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E248" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="F248" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="G248" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="249" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C249" s="3">
+        <v>44889</v>
+      </c>
+      <c r="D249" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E249" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F249" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="G249" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="250" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C250" s="3">
+        <v>44894</v>
+      </c>
+      <c r="D250" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="E250" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="F250" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="G250" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="251" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C251" s="3">
         <v>44906</v>
       </c>
-      <c r="D248" s="1" t="s">
+      <c r="D251" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E248" s="1" t="s">
+      <c r="E251" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="F248" s="2" t="s">
+      <c r="F251" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="G248" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="249" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="G251" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
     <row r="252" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="253" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B254" s="1"/>
-    </row>
-    <row r="255" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B255" s="1"/>
-      <c r="C255" s="3"/>
-    </row>
-    <row r="256" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B256" s="1"/>
-    </row>
+    <row r="254" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" spans="2:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="257" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B257" s="1"/>
-      <c r="C257" s="3"/>
     </row>
     <row r="258" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B258" s="1"/>
@@ -9528,10 +9732,10 @@
     </row>
     <row r="259" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B259" s="1"/>
-      <c r="C259" s="3"/>
     </row>
     <row r="260" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B260" s="1"/>
+      <c r="C260" s="3"/>
     </row>
     <row r="261" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B261" s="1"/>
@@ -9539,10 +9743,18 @@
     </row>
     <row r="262" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B262" s="1"/>
-    </row>
-    <row r="263" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="C262" s="3"/>
+    </row>
+    <row r="263" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B263" s="1"/>
+    </row>
+    <row r="264" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B264" s="1"/>
+      <c r="C264" s="3"/>
+    </row>
+    <row r="265" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B265" s="1"/>
+    </row>
     <row r="266" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="267" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="268" spans="2:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9849,8 +10061,309 @@
     <row r="569" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="570" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="571" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C88C7AE-D150-45A8-A056-E0AEECBDC0CC}">
+  <dimension ref="B2:F4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="11">
+        <v>45982</v>
+      </c>
+      <c r="C4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D4" t="s">
+        <v>717</v>
+      </c>
+      <c r="E4" t="s">
+        <v>718</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E45F2673-CE32-49F4-BC1B-F8FBE93D26B7}">
+  <dimension ref="B2:F3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="12.42578125" customWidth="1"/>
+    <col min="4" max="4" width="49.28515625" customWidth="1"/>
+    <col min="5" max="5" width="79.140625" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B3" s="10">
+        <v>46017</v>
+      </c>
+      <c r="C3" t="s">
+        <v>734</v>
+      </c>
+      <c r="D3" t="s">
+        <v>735</v>
+      </c>
+      <c r="E3" t="s">
+        <v>736</v>
+      </c>
+      <c r="F3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FF6046A-9FE6-4DC2-8015-EF798175DC70}">
+  <dimension ref="B2:F4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="10.7109375" customWidth="1"/>
+    <col min="4" max="4" width="51.28515625" customWidth="1"/>
+    <col min="5" max="5" width="98.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="10">
+        <v>45950</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="10">
+        <v>45952</v>
+      </c>
+      <c r="C4" t="s">
+        <v>732</v>
+      </c>
+      <c r="D4" t="s">
+        <v>731</v>
+      </c>
+      <c r="E4" t="s">
+        <v>733</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A788997-D424-4F88-B4C0-01C1D6C62543}">
+  <dimension ref="B2:F4"/>
+  <sheetFormatPr defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" customWidth="1"/>
+    <col min="4" max="5" width="57.5703125" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="10">
+        <v>45950</v>
+      </c>
+      <c r="C3" t="s">
+        <v>706</v>
+      </c>
+      <c r="D3" t="s">
+        <v>703</v>
+      </c>
+      <c r="E3" t="s">
+        <v>707</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="10">
+        <v>45982</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D193941-8655-427B-A14E-6D2F37E087A4}">
+  <dimension ref="B2:F4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="14.140625" customWidth="1"/>
+    <col min="4" max="4" width="40.28515625" customWidth="1"/>
+    <col min="5" max="5" width="63" customWidth="1"/>
+    <col min="6" max="6" width="25.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B3" s="10">
+        <v>45950</v>
+      </c>
+      <c r="C3" t="s">
+        <v>708</v>
+      </c>
+      <c r="D3" t="s">
+        <v>709</v>
+      </c>
+      <c r="E3" t="s">
+        <v>710</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="10">
+        <v>45952</v>
+      </c>
+      <c r="C4" t="s">
+        <v>732</v>
+      </c>
+      <c r="D4" t="s">
+        <v>731</v>
+      </c>
+      <c r="E4" t="s">
+        <v>733</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>